--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="416" documentId="13_ncr:1_{1CCB16D9-864A-481B-A34B-A3476BEF7488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB971FD3-34E2-43C3-A6AD-0787B42B6B5A}"/>
+  <xr:revisionPtr revIDLastSave="430" documentId="13_ncr:1_{1CCB16D9-864A-481B-A34B-A3476BEF7488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD5BCDD4-E43E-4426-A868-90B9CA7468B4}"/>
   <bookViews>
-    <workbookView xWindow="6450" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="10" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">国内株式_信用!$A$1:$AA$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">国内株式_特定!$A$1:$N$539</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">国内株式_特定_配当!$A$1:$K$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">投資信託!$A$1:$K$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">投資信託!$A$1:$K$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">米国株式!$A$1:$R$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">米国株式_配当!$A$1:$K$65</definedName>
   </definedNames>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4710" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4755" uniqueCount="311">
   <si>
     <t>約定日</t>
   </si>
@@ -1390,6 +1390,30 @@
     <t>NISA</t>
     <phoneticPr fontId="18"/>
   </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>日本製鉄</t>
+    <rPh sb="0" eb="2">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイテツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大和工業</t>
+    <rPh sb="0" eb="2">
+      <t>ダイワ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウギョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
 </sst>
 </file>
 
@@ -2097,7 +2121,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2280,9 +2304,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2696,7 +2717,7 @@
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>5158828</v>
+        <v>5197828</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
@@ -2708,11 +2729,11 @@
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>2904724</v>
+        <v>2943724</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>2314629.3193999999</v>
+        <v>2345706.4693999998</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -2748,7 +2769,7 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>4685008.6790999994</v>
+        <v>4716085.8290999997</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.7">
@@ -2772,11 +2793,11 @@
         <v>160060</v>
       </c>
       <c r="F5" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$1000,国内株式_特定!$B$2:$B$1000,"&gt;=2021/1/1",国内株式_特定!$B$2:$B$1000,"&lt;=2021/12/31",国内株式_特定!$N$2:$N$1000,"&gt;=0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$999,国内株式_特定!$B$2:$B$999,"&gt;=2021/1/1",国内株式_特定!$B$2:$B$999,"&lt;=2021/12/31",国内株式_特定!$N$2:$N$999,"&gt;=0")</f>
         <v>630746</v>
       </c>
       <c r="G5" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$1000,国内株式_特定!$B$2:$B$1000,"&gt;=2021/1/1",国内株式_特定!$B$2:$B$1000,"&lt;=2021/12/31",国内株式_特定!$N$2:$N$1000,"&lt;0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$999,国内株式_特定!$B$2:$B$999,"&gt;=2021/1/1",国内株式_特定!$B$2:$B$999,"&lt;=2021/12/31",国内株式_特定!$N$2:$N$999,"&lt;0")</f>
         <v>-601144</v>
       </c>
       <c r="H5" s="19">
@@ -2808,11 +2829,11 @@
         <v>-68778</v>
       </c>
       <c r="O5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1000,投資信託!$B$2:$B$1000,"&gt;=2021/1/1",投資信託!$B$2:$B$1000,"&lt;=2021/12/31",投資信託!$K$2:$K$1000,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1001,投資信託!$B$2:$B$1001,"&gt;=2021/1/1",投資信託!$B$2:$B$1001,"&lt;=2021/12/31",投資信託!$K$2:$K$1001,"&gt;=0")</f>
         <v>7366</v>
       </c>
       <c r="P5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1000,投資信託!$B$2:$B$1000,"&gt;=2021/1/1",投資信託!$B$2:$B$1000,"&lt;=2021/12/31",投資信託!$K$2:$K$1000,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1001,投資信託!$B$2:$B$1001,"&gt;=2021/1/1",投資信託!$B$2:$B$1001,"&lt;=2021/12/31",投資信託!$K$2:$K$1001,"&lt;0")</f>
         <v>-1498</v>
       </c>
       <c r="Q5" s="35">
@@ -2849,11 +2870,11 @@
         <v>35720</v>
       </c>
       <c r="F6" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$1000,国内株式_特定!$B$2:$B$1000,"&gt;=2022/1/1",国内株式_特定!$B$2:$B$1000,"&lt;=2022/12/31",国内株式_特定!$N$2:$N$1000,"&gt;=0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$999,国内株式_特定!$B$2:$B$999,"&gt;=2022/1/1",国内株式_特定!$B$2:$B$999,"&lt;=2022/12/31",国内株式_特定!$N$2:$N$999,"&gt;=0")</f>
         <v>619915</v>
       </c>
       <c r="G6" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$1000,国内株式_特定!$B$2:$B$1000,"&gt;=2022/1/1",国内株式_特定!$B$2:$B$1000,"&lt;=2022/12/31",国内株式_特定!$N$2:$N$1000,"&lt;0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$999,国内株式_特定!$B$2:$B$999,"&gt;=2022/1/1",国内株式_特定!$B$2:$B$999,"&lt;=2022/12/31",国内株式_特定!$N$2:$N$999,"&lt;0")</f>
         <v>-699020</v>
       </c>
       <c r="H6" s="19">
@@ -2885,11 +2906,11 @@
         <v>-106573</v>
       </c>
       <c r="O6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1000,投資信託!$B$2:$B$1000,"&gt;=2022/1/1",投資信託!$B$2:$B$1000,"&lt;=2022/12/31",投資信託!$K$2:$K$1000,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1001,投資信託!$B$2:$B$1001,"&gt;=2022/1/1",投資信託!$B$2:$B$1001,"&lt;=2022/12/31",投資信託!$K$2:$K$1001,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1000,投資信託!$B$2:$B$1000,"&gt;=2022/1/1",投資信託!$B$2:$B$1000,"&lt;=2022/12/31",投資信託!$K$2:$K$1000,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1001,投資信託!$B$2:$B$1001,"&gt;=2022/1/1",投資信託!$B$2:$B$1001,"&lt;=2022/12/31",投資信託!$K$2:$K$1001,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q6" s="35">
@@ -2926,11 +2947,11 @@
         <v>214320</v>
       </c>
       <c r="F7" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$1000,国内株式_特定!$B$2:$B$1000,"&gt;=2023/1/1",国内株式_特定!$B$2:$B$1000,"&lt;=2023/12/31",国内株式_特定!$N$2:$N$1000,"&gt;=0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$999,国内株式_特定!$B$2:$B$999,"&gt;=2023/1/1",国内株式_特定!$B$2:$B$999,"&lt;=2023/12/31",国内株式_特定!$N$2:$N$999,"&gt;=0")</f>
         <v>1679057</v>
       </c>
       <c r="G7" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$1000,国内株式_特定!$B$2:$B$1000,"&gt;=2023/1/1",国内株式_特定!$B$2:$B$1000,"&lt;=2023/12/31",国内株式_特定!$N$2:$N$1000,"&lt;0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$999,国内株式_特定!$B$2:$B$999,"&gt;=2023/1/1",国内株式_特定!$B$2:$B$999,"&lt;=2023/12/31",国内株式_特定!$N$2:$N$999,"&lt;0")</f>
         <v>-402270</v>
       </c>
       <c r="H7" s="19">
@@ -2962,11 +2983,11 @@
         <v>-50703</v>
       </c>
       <c r="O7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1000,投資信託!$B$2:$B$1000,"&gt;=2023/1/1",投資信託!$B$2:$B$1000,"&lt;=2023/12/31",投資信託!$K$2:$K$1000,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1001,投資信託!$B$2:$B$1001,"&gt;=2023/1/1",投資信託!$B$2:$B$1001,"&lt;=2023/12/31",投資信託!$K$2:$K$1001,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1000,投資信託!$B$2:$B$1000,"&gt;=2023/1/1",投資信託!$B$2:$B$1000,"&lt;=2023/12/31",投資信託!$K$2:$K$1000,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1001,投資信託!$B$2:$B$1001,"&gt;=2023/1/1",投資信託!$B$2:$B$1001,"&lt;=2023/12/31",投資信託!$K$2:$K$1001,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q7" s="35">
@@ -3003,11 +3024,11 @@
         <v>111775</v>
       </c>
       <c r="F8" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$1000,国内株式_特定!$B$2:$B$1000,"&gt;=2024/1/1",国内株式_特定!$B$2:$B$1000,"&lt;=2024/12/31",国内株式_特定!$N$2:$N$1000,"&gt;=0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$999,国内株式_特定!$B$2:$B$999,"&gt;=2024/1/1",国内株式_特定!$B$2:$B$999,"&lt;=2024/12/31",国内株式_特定!$N$2:$N$999,"&gt;=0")</f>
         <v>2059210</v>
       </c>
       <c r="G8" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$1000,国内株式_特定!$B$2:$B$1000,"&gt;=2024/1/1",国内株式_特定!$B$2:$B$1000,"&lt;=2024/12/31",国内株式_特定!$N$2:$N$1000,"&lt;0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$999,国内株式_特定!$B$2:$B$999,"&gt;=2024/1/1",国内株式_特定!$B$2:$B$999,"&lt;=2024/12/31",国内株式_特定!$N$2:$N$999,"&lt;0")</f>
         <v>-1123620</v>
       </c>
       <c r="H8" s="19">
@@ -3039,11 +3060,11 @@
         <v>-247960</v>
       </c>
       <c r="O8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1000,投資信託!$B$2:$B$1000,"&gt;=2024/1/1",投資信託!$B$2:$B$1000,"&lt;=2024/12/31",投資信託!$K$2:$K$1000,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1001,投資信託!$B$2:$B$1001,"&gt;=2024/1/1",投資信託!$B$2:$B$1001,"&lt;=2024/12/31",投資信託!$K$2:$K$1001,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1000,投資信託!$B$2:$B$1000,"&gt;=2024/1/1",投資信託!$B$2:$B$1000,"&lt;=2024/12/31",投資信託!$K$2:$K$1000,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1001,投資信託!$B$2:$B$1001,"&gt;=2024/1/1",投資信託!$B$2:$B$1001,"&lt;=2024/12/31",投資信託!$K$2:$K$1001,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q8" s="35">
@@ -3080,11 +3101,11 @@
         <v>2279200</v>
       </c>
       <c r="F9" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$1000,国内株式_特定!$B$2:$B$1000,"&gt;=2025/1/1",国内株式_特定!$B$2:$B$1000,"&lt;=2025/12/31",国内株式_特定!$N$2:$N$1000,"&gt;=0")</f>
-        <v>169900</v>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$999,国内株式_特定!$B$2:$B$999,"&gt;=2025/1/1",国内株式_特定!$B$2:$B$999,"&lt;=2025/12/31",国内株式_特定!$N$2:$N$999,"&gt;=0")</f>
+        <v>208900</v>
       </c>
       <c r="G9" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$1000,国内株式_特定!$B$2:$B$1000,"&gt;=2025/1/1",国内株式_特定!$B$2:$B$1000,"&lt;=2025/12/31",国内株式_特定!$N$2:$N$1000,"&lt;0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$999,国内株式_特定!$B$2:$B$999,"&gt;=2025/1/1",国内株式_特定!$B$2:$B$999,"&lt;=2025/12/31",国内株式_特定!$N$2:$N$999,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="H9" s="19">
@@ -3093,11 +3114,11 @@
       </c>
       <c r="I9" s="35">
         <f t="shared" ref="I9" si="10">SUM(F9:H9)</f>
-        <v>169900</v>
+        <v>208900</v>
       </c>
       <c r="J9" s="36">
         <f>IF(I9&gt;0,I9-I9*0.20315,I9)</f>
-        <v>135384.815</v>
+        <v>166461.965</v>
       </c>
       <c r="K9" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2025/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2025/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -3116,11 +3137,11 @@
         <v>0</v>
       </c>
       <c r="O9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1000,投資信託!$B$2:$B$1000,"&gt;=2025/1/1",投資信託!$B$2:$B$1000,"&lt;=2025/12/31",投資信託!$K$2:$K$1000,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1001,投資信託!$B$2:$B$1001,"&gt;=2025/1/1",投資信託!$B$2:$B$1001,"&lt;=2025/12/31",投資信託!$K$2:$K$1001,"&gt;=0")</f>
         <v>48494</v>
       </c>
       <c r="P9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1000,投資信託!$B$2:$B$1000,"&gt;=2025/1/1",投資信託!$B$2:$B$1000,"&lt;=2025/12/31",投資信託!$K$2:$K$1000,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1001,投資信託!$B$2:$B$1001,"&gt;=2025/1/1",投資信託!$B$2:$B$1001,"&lt;=2025/12/31",投資信託!$K$2:$K$1001,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q9" s="35">
@@ -3133,7 +3154,7 @@
       </c>
       <c r="S9" s="38">
         <f>SUM(E9,J9,N9,R9)</f>
-        <v>2453227.2588999998</v>
+        <v>2484304.4088999997</v>
       </c>
     </row>
   </sheetData>
@@ -3168,7 +3189,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="2" width="11.3125" style="1" customWidth="1"/>
@@ -3255,10 +3276,10 @@
       <c r="I2" s="25">
         <v>875</v>
       </c>
-      <c r="J2" s="61">
-        <v>0</v>
-      </c>
-      <c r="K2" s="61">
+      <c r="J2" s="19">
+        <v>0</v>
+      </c>
+      <c r="K2" s="19">
         <v>0</v>
       </c>
       <c r="L2" s="25" t="s">
@@ -3300,10 +3321,10 @@
       <c r="I3" s="25">
         <v>925</v>
       </c>
-      <c r="J3" s="61">
-        <v>0</v>
-      </c>
-      <c r="K3" s="61">
+      <c r="J3" s="19">
+        <v>0</v>
+      </c>
+      <c r="K3" s="19">
         <v>0</v>
       </c>
       <c r="L3" s="25" t="s">
@@ -3345,10 +3366,10 @@
       <c r="I4" s="25">
         <v>1094</v>
       </c>
-      <c r="J4" s="61">
-        <v>0</v>
-      </c>
-      <c r="K4" s="61">
+      <c r="J4" s="19">
+        <v>0</v>
+      </c>
+      <c r="K4" s="19">
         <v>0</v>
       </c>
       <c r="L4" s="25" t="s">
@@ -3390,10 +3411,10 @@
       <c r="I5" s="25">
         <v>1307</v>
       </c>
-      <c r="J5" s="61">
-        <v>0</v>
-      </c>
-      <c r="K5" s="61">
+      <c r="J5" s="19">
+        <v>0</v>
+      </c>
+      <c r="K5" s="19">
         <v>0</v>
       </c>
       <c r="L5" s="25" t="s">
@@ -3435,10 +3456,10 @@
       <c r="I6" s="25">
         <v>1506.6</v>
       </c>
-      <c r="J6" s="61">
-        <v>0</v>
-      </c>
-      <c r="K6" s="61">
+      <c r="J6" s="19">
+        <v>0</v>
+      </c>
+      <c r="K6" s="19">
         <v>0</v>
       </c>
       <c r="L6" s="25" t="s">
@@ -3480,10 +3501,10 @@
       <c r="I7" s="25">
         <v>1635</v>
       </c>
-      <c r="J7" s="61">
-        <v>0</v>
-      </c>
-      <c r="K7" s="61">
+      <c r="J7" s="19">
+        <v>0</v>
+      </c>
+      <c r="K7" s="19">
         <v>0</v>
       </c>
       <c r="L7" s="25" t="s">
@@ -3525,10 +3546,10 @@
       <c r="I8" s="25">
         <v>580</v>
       </c>
-      <c r="J8" s="61">
-        <v>0</v>
-      </c>
-      <c r="K8" s="61">
+      <c r="J8" s="19">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19">
         <v>0</v>
       </c>
       <c r="L8" s="25" t="s">
@@ -3570,10 +3591,10 @@
       <c r="I9" s="25">
         <v>700</v>
       </c>
-      <c r="J9" s="61">
-        <v>0</v>
-      </c>
-      <c r="K9" s="61">
+      <c r="J9" s="19">
+        <v>0</v>
+      </c>
+      <c r="K9" s="19">
         <v>0</v>
       </c>
       <c r="L9" s="25" t="s">
@@ -3615,10 +3636,10 @@
       <c r="I10" s="25">
         <v>4170</v>
       </c>
-      <c r="J10" s="61">
-        <v>0</v>
-      </c>
-      <c r="K10" s="61">
+      <c r="J10" s="19">
+        <v>0</v>
+      </c>
+      <c r="K10" s="19">
         <v>0</v>
       </c>
       <c r="L10" s="25" t="s">
@@ -3660,10 +3681,10 @@
       <c r="I11" s="25">
         <v>4615</v>
       </c>
-      <c r="J11" s="61">
-        <v>0</v>
-      </c>
-      <c r="K11" s="61">
+      <c r="J11" s="19">
+        <v>0</v>
+      </c>
+      <c r="K11" s="19">
         <v>0</v>
       </c>
       <c r="L11" s="25" t="s">
@@ -3705,10 +3726,10 @@
       <c r="I12" s="25">
         <v>4440</v>
       </c>
-      <c r="J12" s="61">
-        <v>0</v>
-      </c>
-      <c r="K12" s="61">
+      <c r="J12" s="19">
+        <v>0</v>
+      </c>
+      <c r="K12" s="19">
         <v>0</v>
       </c>
       <c r="L12" s="25" t="s">
@@ -3750,10 +3771,10 @@
       <c r="I13" s="25">
         <v>4530</v>
       </c>
-      <c r="J13" s="61">
-        <v>0</v>
-      </c>
-      <c r="K13" s="61">
+      <c r="J13" s="19">
+        <v>0</v>
+      </c>
+      <c r="K13" s="19">
         <v>0</v>
       </c>
       <c r="L13" s="25" t="s">
@@ -3795,10 +3816,10 @@
       <c r="I14" s="25">
         <v>3115</v>
       </c>
-      <c r="J14" s="61">
-        <v>0</v>
-      </c>
-      <c r="K14" s="61">
+      <c r="J14" s="19">
+        <v>0</v>
+      </c>
+      <c r="K14" s="19">
         <v>0</v>
       </c>
       <c r="L14" s="25" t="s">
@@ -3840,10 +3861,10 @@
       <c r="I15" s="25">
         <v>4405</v>
       </c>
-      <c r="J15" s="61">
-        <v>0</v>
-      </c>
-      <c r="K15" s="61">
+      <c r="J15" s="19">
+        <v>0</v>
+      </c>
+      <c r="K15" s="19">
         <v>0</v>
       </c>
       <c r="L15" s="25" t="s">
@@ -3885,10 +3906,10 @@
       <c r="I16" s="25">
         <v>1703.8</v>
       </c>
-      <c r="J16" s="61">
-        <v>0</v>
-      </c>
-      <c r="K16" s="61">
+      <c r="J16" s="19">
+        <v>0</v>
+      </c>
+      <c r="K16" s="19">
         <v>0</v>
       </c>
       <c r="L16" s="25" t="s">
@@ -3930,10 +3951,10 @@
       <c r="I17" s="25">
         <v>1790</v>
       </c>
-      <c r="J17" s="61">
-        <v>0</v>
-      </c>
-      <c r="K17" s="61">
+      <c r="J17" s="19">
+        <v>0</v>
+      </c>
+      <c r="K17" s="19">
         <v>0</v>
       </c>
       <c r="L17" s="25" t="s">
@@ -3975,10 +3996,10 @@
       <c r="I18" s="25">
         <v>2988.5</v>
       </c>
-      <c r="J18" s="61">
-        <v>0</v>
-      </c>
-      <c r="K18" s="61">
+      <c r="J18" s="19">
+        <v>0</v>
+      </c>
+      <c r="K18" s="19">
         <v>0</v>
       </c>
       <c r="L18" s="25" t="s">
@@ -4018,10 +4039,10 @@
       <c r="I19" s="25">
         <v>597.70000000000005</v>
       </c>
-      <c r="J19" s="61">
-        <v>0</v>
-      </c>
-      <c r="K19" s="61">
+      <c r="J19" s="19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="19">
         <v>0</v>
       </c>
       <c r="L19" s="25" t="s">
@@ -4062,10 +4083,10 @@
       <c r="I20" s="25">
         <v>4620</v>
       </c>
-      <c r="J20" s="61">
-        <v>0</v>
-      </c>
-      <c r="K20" s="61">
+      <c r="J20" s="19">
+        <v>0</v>
+      </c>
+      <c r="K20" s="19">
         <v>0</v>
       </c>
       <c r="L20" s="25" t="s">
@@ -4107,10 +4128,10 @@
       <c r="I21" s="25">
         <v>3818</v>
       </c>
-      <c r="J21" s="61">
-        <v>0</v>
-      </c>
-      <c r="K21" s="61">
+      <c r="J21" s="19">
+        <v>0</v>
+      </c>
+      <c r="K21" s="19">
         <v>0</v>
       </c>
       <c r="L21" s="25" t="s">
@@ -4152,10 +4173,10 @@
       <c r="I22" s="25">
         <v>3954</v>
       </c>
-      <c r="J22" s="61">
-        <v>0</v>
-      </c>
-      <c r="K22" s="61">
+      <c r="J22" s="19">
+        <v>0</v>
+      </c>
+      <c r="K22" s="19">
         <v>0</v>
       </c>
       <c r="L22" s="25" t="s">
@@ -4197,10 +4218,10 @@
       <c r="I23" s="25">
         <v>2590</v>
       </c>
-      <c r="J23" s="61">
-        <v>0</v>
-      </c>
-      <c r="K23" s="61">
+      <c r="J23" s="19">
+        <v>0</v>
+      </c>
+      <c r="K23" s="19">
         <v>0</v>
       </c>
       <c r="L23" s="25" t="s">
@@ -4240,10 +4261,10 @@
       <c r="I24" s="25">
         <v>259</v>
       </c>
-      <c r="J24" s="61">
-        <v>0</v>
-      </c>
-      <c r="K24" s="61">
+      <c r="J24" s="19">
+        <v>0</v>
+      </c>
+      <c r="K24" s="19">
         <v>0</v>
       </c>
       <c r="L24" s="25" t="s">
@@ -4282,10 +4303,10 @@
       <c r="I25" s="25">
         <v>259</v>
       </c>
-      <c r="J25" s="61">
-        <v>0</v>
-      </c>
-      <c r="K25" s="61">
+      <c r="J25" s="19">
+        <v>0</v>
+      </c>
+      <c r="K25" s="19">
         <v>0</v>
       </c>
       <c r="L25" s="25" t="s">
@@ -4324,10 +4345,10 @@
       <c r="I26" s="25">
         <v>259</v>
       </c>
-      <c r="J26" s="61">
-        <v>0</v>
-      </c>
-      <c r="K26" s="61">
+      <c r="J26" s="19">
+        <v>0</v>
+      </c>
+      <c r="K26" s="19">
         <v>0</v>
       </c>
       <c r="L26" s="25" t="s">
@@ -4368,10 +4389,10 @@
       <c r="I27" s="25">
         <v>2009</v>
       </c>
-      <c r="J27" s="61">
-        <v>0</v>
-      </c>
-      <c r="K27" s="61">
+      <c r="J27" s="19">
+        <v>0</v>
+      </c>
+      <c r="K27" s="19">
         <v>0</v>
       </c>
       <c r="L27" s="25" t="s">
@@ -4411,10 +4432,10 @@
       <c r="I28" s="25">
         <v>2009</v>
       </c>
-      <c r="J28" s="61">
-        <v>0</v>
-      </c>
-      <c r="K28" s="61">
+      <c r="J28" s="19">
+        <v>0</v>
+      </c>
+      <c r="K28" s="19">
         <v>0</v>
       </c>
       <c r="L28" s="25" t="s">
@@ -4455,17 +4476,17 @@
       <c r="I29" s="25">
         <v>895</v>
       </c>
-      <c r="J29" s="61">
-        <v>0</v>
-      </c>
-      <c r="K29" s="61">
+      <c r="J29" s="19">
+        <v>0</v>
+      </c>
+      <c r="K29" s="19">
         <v>0</v>
       </c>
       <c r="L29" s="25" t="s">
         <v>306</v>
       </c>
       <c r="M29" s="19">
-        <f t="shared" ref="M29:M47" si="1">H29*I29</f>
+        <f t="shared" ref="M29:M49" si="1">H29*I29</f>
         <v>89500</v>
       </c>
       <c r="N29" s="14">
@@ -4500,10 +4521,10 @@
       <c r="I30" s="25">
         <v>1047</v>
       </c>
-      <c r="J30" s="61">
-        <v>0</v>
-      </c>
-      <c r="K30" s="61">
+      <c r="J30" s="19">
+        <v>0</v>
+      </c>
+      <c r="K30" s="19">
         <v>0</v>
       </c>
       <c r="L30" s="25" t="s">
@@ -4545,10 +4566,10 @@
       <c r="I31" s="25">
         <v>1890</v>
       </c>
-      <c r="J31" s="61">
-        <v>0</v>
-      </c>
-      <c r="K31" s="61">
+      <c r="J31" s="19">
+        <v>0</v>
+      </c>
+      <c r="K31" s="19">
         <v>0</v>
       </c>
       <c r="L31" s="25" t="s">
@@ -4590,10 +4611,10 @@
       <c r="I32" s="25">
         <v>2325</v>
       </c>
-      <c r="J32" s="61">
-        <v>0</v>
-      </c>
-      <c r="K32" s="61">
+      <c r="J32" s="19">
+        <v>0</v>
+      </c>
+      <c r="K32" s="19">
         <v>0</v>
       </c>
       <c r="L32" s="25" t="s">
@@ -4635,10 +4656,10 @@
       <c r="I33" s="25">
         <v>2686</v>
       </c>
-      <c r="J33" s="61">
-        <v>0</v>
-      </c>
-      <c r="K33" s="61">
+      <c r="J33" s="19">
+        <v>0</v>
+      </c>
+      <c r="K33" s="19">
         <v>0</v>
       </c>
       <c r="L33" s="25" t="s">
@@ -4680,10 +4701,10 @@
       <c r="I34" s="25">
         <v>454</v>
       </c>
-      <c r="J34" s="61">
-        <v>0</v>
-      </c>
-      <c r="K34" s="61">
+      <c r="J34" s="19">
+        <v>0</v>
+      </c>
+      <c r="K34" s="19">
         <v>0</v>
       </c>
       <c r="L34" s="25" t="s">
@@ -4725,10 +4746,10 @@
       <c r="I35" s="25">
         <v>593</v>
       </c>
-      <c r="J35" s="61">
-        <v>0</v>
-      </c>
-      <c r="K35" s="61">
+      <c r="J35" s="19">
+        <v>0</v>
+      </c>
+      <c r="K35" s="19">
         <v>0</v>
       </c>
       <c r="L35" s="25" t="s">
@@ -4770,10 +4791,10 @@
       <c r="I36" s="25">
         <v>688</v>
       </c>
-      <c r="J36" s="61">
-        <v>0</v>
-      </c>
-      <c r="K36" s="61">
+      <c r="J36" s="19">
+        <v>0</v>
+      </c>
+      <c r="K36" s="19">
         <v>0</v>
       </c>
       <c r="L36" s="25" t="s">
@@ -4815,10 +4836,10 @@
       <c r="I37" s="25">
         <v>763.4</v>
       </c>
-      <c r="J37" s="61">
-        <v>0</v>
-      </c>
-      <c r="K37" s="61">
+      <c r="J37" s="19">
+        <v>0</v>
+      </c>
+      <c r="K37" s="19">
         <v>0</v>
       </c>
       <c r="L37" s="25" t="s">
@@ -4860,10 +4881,10 @@
       <c r="I38" s="25">
         <v>1008</v>
       </c>
-      <c r="J38" s="61">
-        <v>0</v>
-      </c>
-      <c r="K38" s="61">
+      <c r="J38" s="19">
+        <v>0</v>
+      </c>
+      <c r="K38" s="19">
         <v>0</v>
       </c>
       <c r="L38" s="25" t="s">
@@ -4905,10 +4926,10 @@
       <c r="I39" s="25">
         <v>2713.4</v>
       </c>
-      <c r="J39" s="61">
-        <v>0</v>
-      </c>
-      <c r="K39" s="61">
+      <c r="J39" s="19">
+        <v>0</v>
+      </c>
+      <c r="K39" s="19">
         <v>0</v>
       </c>
       <c r="L39" s="25" t="s">
@@ -4950,10 +4971,10 @@
       <c r="I40" s="25">
         <v>3004.6</v>
       </c>
-      <c r="J40" s="61">
-        <v>0</v>
-      </c>
-      <c r="K40" s="61">
+      <c r="J40" s="19">
+        <v>0</v>
+      </c>
+      <c r="K40" s="19">
         <v>0</v>
       </c>
       <c r="L40" s="25" t="s">
@@ -4995,10 +5016,10 @@
       <c r="I41" s="25">
         <v>4775</v>
       </c>
-      <c r="J41" s="61">
-        <v>0</v>
-      </c>
-      <c r="K41" s="61">
+      <c r="J41" s="19">
+        <v>0</v>
+      </c>
+      <c r="K41" s="19">
         <v>0</v>
       </c>
       <c r="L41" s="25" t="s">
@@ -5040,10 +5061,10 @@
       <c r="I42" s="25">
         <v>4282</v>
       </c>
-      <c r="J42" s="61">
-        <v>0</v>
-      </c>
-      <c r="K42" s="61">
+      <c r="J42" s="19">
+        <v>0</v>
+      </c>
+      <c r="K42" s="19">
         <v>0</v>
       </c>
       <c r="L42" s="25" t="s">
@@ -5085,10 +5106,10 @@
       <c r="I43" s="25">
         <v>3869.4</v>
       </c>
-      <c r="J43" s="61">
-        <v>0</v>
-      </c>
-      <c r="K43" s="61">
+      <c r="J43" s="19">
+        <v>0</v>
+      </c>
+      <c r="K43" s="19">
         <v>0</v>
       </c>
       <c r="L43" s="25" t="s">
@@ -5130,10 +5151,10 @@
       <c r="I44" s="25">
         <v>4312</v>
       </c>
-      <c r="J44" s="61">
-        <v>0</v>
-      </c>
-      <c r="K44" s="61">
+      <c r="J44" s="19">
+        <v>0</v>
+      </c>
+      <c r="K44" s="19">
         <v>0</v>
       </c>
       <c r="L44" s="25" t="s">
@@ -5175,10 +5196,10 @@
       <c r="I45" s="25">
         <v>4600</v>
       </c>
-      <c r="J45" s="61">
-        <v>0</v>
-      </c>
-      <c r="K45" s="61">
+      <c r="J45" s="19">
+        <v>0</v>
+      </c>
+      <c r="K45" s="19">
         <v>0</v>
       </c>
       <c r="L45" s="25" t="s">
@@ -5220,10 +5241,10 @@
       <c r="I46" s="25">
         <v>4620</v>
       </c>
-      <c r="J46" s="61">
-        <v>0</v>
-      </c>
-      <c r="K46" s="61">
+      <c r="J46" s="19">
+        <v>0</v>
+      </c>
+      <c r="K46" s="19">
         <v>0</v>
       </c>
       <c r="L46" s="25" t="s">
@@ -5265,10 +5286,10 @@
       <c r="I47" s="25">
         <v>2457.5</v>
       </c>
-      <c r="J47" s="61">
-        <v>0</v>
-      </c>
-      <c r="K47" s="61">
+      <c r="J47" s="19">
+        <v>0</v>
+      </c>
+      <c r="K47" s="19">
         <v>0</v>
       </c>
       <c r="L47" s="25" t="s">
@@ -5279,6 +5300,96 @@
         <v>245750</v>
       </c>
       <c r="N47" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.7">
+      <c r="A48" s="4">
+        <v>45691</v>
+      </c>
+      <c r="B48" s="4">
+        <v>45693</v>
+      </c>
+      <c r="C48" s="5">
+        <v>4204</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H48" s="5">
+        <v>100</v>
+      </c>
+      <c r="I48" s="25">
+        <v>2535</v>
+      </c>
+      <c r="J48" s="19">
+        <v>0</v>
+      </c>
+      <c r="K48" s="19">
+        <v>0</v>
+      </c>
+      <c r="L48" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="M48" s="19">
+        <f t="shared" si="1"/>
+        <v>253500</v>
+      </c>
+      <c r="N48" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.7">
+      <c r="A49" s="4">
+        <v>45695</v>
+      </c>
+      <c r="B49" s="4">
+        <v>45700</v>
+      </c>
+      <c r="C49" s="5">
+        <v>5444</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H49" s="5">
+        <v>100</v>
+      </c>
+      <c r="I49" s="25">
+        <v>7753</v>
+      </c>
+      <c r="J49" s="19">
+        <v>0</v>
+      </c>
+      <c r="K49" s="19">
+        <v>0</v>
+      </c>
+      <c r="L49" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="M49" s="19">
+        <f t="shared" si="1"/>
+        <v>775300</v>
+      </c>
+      <c r="N49" s="23">
         <v>0</v>
       </c>
     </row>
@@ -6961,7 +7072,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O601"/>
+  <dimension ref="A1:O600"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="11.3125" style="1" bestFit="1" customWidth="1"/>
@@ -30865,7 +30976,7 @@
         <v>276</v>
       </c>
       <c r="M531" s="15">
-        <f t="shared" ref="M531:M570" si="14">IF(G531="買付",H531*I531+SUM(J531:K531),H531*I531-SUM(J531:K531))</f>
+        <f t="shared" ref="M531:M576" si="14">IF(G531="買付",H531*I531+SUM(J531:K531),H531*I531-SUM(J531:K531))</f>
         <v>98750</v>
       </c>
       <c r="N531" s="21">
@@ -32627,69 +32738,335 @@
       </c>
     </row>
     <row r="571" spans="1:14" x14ac:dyDescent="0.7">
-      <c r="I571" s="27"/>
+      <c r="A571" s="4">
+        <v>45691</v>
+      </c>
+      <c r="B571" s="4">
+        <v>45693</v>
+      </c>
+      <c r="C571" s="5">
+        <v>2432</v>
+      </c>
+      <c r="D571" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E571" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F571" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G571" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H571" s="5">
+        <v>100</v>
+      </c>
+      <c r="I571" s="25">
+        <v>2826</v>
+      </c>
+      <c r="J571" s="9">
+        <v>0</v>
+      </c>
+      <c r="K571" s="14">
+        <v>0</v>
+      </c>
+      <c r="L571" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="M571" s="15">
+        <f t="shared" si="14"/>
+        <v>282600</v>
+      </c>
+      <c r="N571" s="19">
+        <v>0</v>
+      </c>
     </row>
     <row r="572" spans="1:14" x14ac:dyDescent="0.7">
-      <c r="I572" s="27"/>
+      <c r="A572" s="4">
+        <v>45691</v>
+      </c>
+      <c r="B572" s="4">
+        <v>45693</v>
+      </c>
+      <c r="C572" s="5">
+        <v>5401</v>
+      </c>
+      <c r="D572" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="E572" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F572" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G572" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H572" s="5">
+        <v>100</v>
+      </c>
+      <c r="I572" s="25">
+        <v>3184</v>
+      </c>
+      <c r="J572" s="9">
+        <v>0</v>
+      </c>
+      <c r="K572" s="14">
+        <v>0</v>
+      </c>
+      <c r="L572" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="M572" s="15">
+        <f t="shared" si="14"/>
+        <v>318400</v>
+      </c>
+      <c r="N572" s="19">
+        <v>0</v>
+      </c>
     </row>
     <row r="573" spans="1:14" x14ac:dyDescent="0.7">
-      <c r="I573" s="27"/>
+      <c r="A573" s="4">
+        <v>45691</v>
+      </c>
+      <c r="B573" s="4">
+        <v>45693</v>
+      </c>
+      <c r="C573" s="5">
+        <v>8316</v>
+      </c>
+      <c r="D573" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E573" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F573" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G573" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H573" s="5">
+        <v>100</v>
+      </c>
+      <c r="I573" s="25">
+        <v>3756</v>
+      </c>
+      <c r="J573" s="9">
+        <v>0</v>
+      </c>
+      <c r="K573" s="14">
+        <v>0</v>
+      </c>
+      <c r="L573" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="M573" s="15">
+        <f t="shared" si="14"/>
+        <v>375600</v>
+      </c>
+      <c r="N573" s="19">
+        <v>0</v>
+      </c>
     </row>
     <row r="574" spans="1:14" x14ac:dyDescent="0.7">
-      <c r="I574" s="27"/>
+      <c r="A574" s="4">
+        <v>45692</v>
+      </c>
+      <c r="B574" s="4">
+        <v>45694</v>
+      </c>
+      <c r="C574" s="5">
+        <v>7867</v>
+      </c>
+      <c r="D574" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="E574" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F574" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G574" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H574" s="5">
+        <v>100</v>
+      </c>
+      <c r="I574" s="25">
+        <v>4241</v>
+      </c>
+      <c r="J574" s="9">
+        <v>0</v>
+      </c>
+      <c r="K574" s="14">
+        <v>0</v>
+      </c>
+      <c r="L574" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="M574" s="15">
+        <f t="shared" si="14"/>
+        <v>424100</v>
+      </c>
+      <c r="N574" s="19">
+        <v>18800</v>
+      </c>
     </row>
     <row r="575" spans="1:14" x14ac:dyDescent="0.7">
-      <c r="I575" s="27"/>
+      <c r="A575" s="4">
+        <v>45692</v>
+      </c>
+      <c r="B575" s="4">
+        <v>45694</v>
+      </c>
+      <c r="C575" s="5">
+        <v>8316</v>
+      </c>
+      <c r="D575" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E575" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F575" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G575" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H575" s="5">
+        <v>100</v>
+      </c>
+      <c r="I575" s="25">
+        <v>3787</v>
+      </c>
+      <c r="J575" s="9">
+        <v>0</v>
+      </c>
+      <c r="K575" s="14">
+        <v>0</v>
+      </c>
+      <c r="L575" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="M575" s="15">
+        <f t="shared" si="14"/>
+        <v>378700</v>
+      </c>
+      <c r="N575" s="19">
+        <v>3100</v>
+      </c>
     </row>
     <row r="576" spans="1:14" x14ac:dyDescent="0.7">
-      <c r="I576" s="27"/>
-    </row>
-    <row r="577" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I577" s="27"/>
-    </row>
-    <row r="578" spans="9:9" x14ac:dyDescent="0.7">
+      <c r="A576" s="4">
+        <v>45695</v>
+      </c>
+      <c r="B576" s="4">
+        <v>45700</v>
+      </c>
+      <c r="C576" s="5">
+        <v>2432</v>
+      </c>
+      <c r="D576" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E576" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F576" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G576" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H576" s="5">
+        <v>300</v>
+      </c>
+      <c r="I576" s="25">
+        <v>3016</v>
+      </c>
+      <c r="J576" s="9">
+        <v>0</v>
+      </c>
+      <c r="K576" s="14">
+        <v>0</v>
+      </c>
+      <c r="L576" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="M576" s="15">
+        <f t="shared" si="14"/>
+        <v>904800</v>
+      </c>
+      <c r="N576" s="19">
+        <f>5700*3</f>
+        <v>17100</v>
+      </c>
+    </row>
+    <row r="577" spans="1:14" x14ac:dyDescent="0.7">
+      <c r="A577" s="6"/>
+      <c r="B577" s="6"/>
+      <c r="C577" s="5"/>
+      <c r="D577" s="9"/>
+      <c r="E577" s="5"/>
+      <c r="F577" s="5"/>
+      <c r="G577" s="5"/>
+      <c r="H577" s="5"/>
+      <c r="I577" s="25"/>
+      <c r="J577" s="9"/>
+      <c r="K577" s="14"/>
+      <c r="L577" s="9"/>
+      <c r="M577" s="15"/>
+      <c r="N577" s="19"/>
+    </row>
+    <row r="578" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I578" s="27"/>
     </row>
-    <row r="579" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="579" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I579" s="27"/>
     </row>
-    <row r="580" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="580" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I580" s="27"/>
     </row>
-    <row r="581" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="581" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I581" s="27"/>
     </row>
-    <row r="582" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="582" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I582" s="27"/>
     </row>
-    <row r="583" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="583" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I583" s="27"/>
     </row>
-    <row r="584" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="584" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I584" s="27"/>
     </row>
-    <row r="585" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="585" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I585" s="27"/>
     </row>
-    <row r="586" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="586" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I586" s="27"/>
     </row>
-    <row r="587" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="587" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I587" s="27"/>
     </row>
-    <row r="588" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="588" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I588" s="27"/>
     </row>
-    <row r="589" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="589" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I589" s="27"/>
     </row>
-    <row r="590" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="590" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I590" s="27"/>
     </row>
-    <row r="591" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="591" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I591" s="27"/>
     </row>
-    <row r="592" spans="9:9" x14ac:dyDescent="0.7">
+    <row r="592" spans="1:14" x14ac:dyDescent="0.7">
       <c r="I592" s="27"/>
     </row>
     <row r="593" spans="9:9" x14ac:dyDescent="0.7">
@@ -32715,9 +33092,6 @@
     </row>
     <row r="600" spans="9:9" x14ac:dyDescent="0.7">
       <c r="I600" s="27"/>
-    </row>
-    <row r="601" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I601" s="27"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N539" xr:uid="{00000000-0009-0000-0000-000002000000}">
@@ -45054,7 +45428,7 @@
   <sheetPr>
     <tabColor theme="2"/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="2" width="11.3125" style="1" bestFit="1" customWidth="1"/>
@@ -45315,34 +45689,34 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A8" s="4">
-        <v>44368</v>
+        <v>45692</v>
       </c>
       <c r="B8" s="4">
-        <v>44371</v>
+        <v>45698</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>163</v>
+        <v>284</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H8" s="8">
-        <v>21735</v>
-      </c>
-      <c r="I8" s="8">
-        <v>13803</v>
-      </c>
-      <c r="J8" s="8">
-        <v>30000</v>
+        <v>286</v>
+      </c>
+      <c r="H8" s="21">
+        <v>18189</v>
+      </c>
+      <c r="I8" s="21">
+        <v>27489</v>
+      </c>
+      <c r="J8" s="21">
+        <v>50000</v>
       </c>
       <c r="K8" s="21">
         <v>0</v>
@@ -45350,10 +45724,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A9" s="4">
-        <v>44377</v>
+        <v>44368</v>
       </c>
       <c r="B9" s="4">
-        <v>44382</v>
+        <v>44371</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>163</v>
@@ -45371,13 +45745,13 @@
         <v>160</v>
       </c>
       <c r="H9" s="8">
-        <v>7034</v>
+        <v>21735</v>
       </c>
       <c r="I9" s="8">
-        <v>14217</v>
+        <v>13803</v>
       </c>
       <c r="J9" s="8">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="K9" s="21">
         <v>0</v>
@@ -45385,10 +45759,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A10" s="4">
-        <v>44403</v>
+        <v>44377</v>
       </c>
       <c r="B10" s="4">
-        <v>44406</v>
+        <v>44382</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>163</v>
@@ -45397,7 +45771,7 @@
         <v>159</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>67</v>
+        <v>297</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>30</v>
@@ -45406,10 +45780,10 @@
         <v>160</v>
       </c>
       <c r="H10" s="8">
-        <v>7310</v>
+        <v>7034</v>
       </c>
       <c r="I10" s="8">
-        <v>13681</v>
+        <v>14217</v>
       </c>
       <c r="J10" s="8">
         <v>10000</v>
@@ -45420,10 +45794,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A11" s="4">
-        <v>44525</v>
+        <v>44403</v>
       </c>
       <c r="B11" s="4">
-        <v>44530</v>
+        <v>44406</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>163</v>
@@ -45435,28 +45809,30 @@
         <v>67</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="G11" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H11" s="8">
         <v>7310</v>
       </c>
       <c r="I11" s="8">
-        <v>13973</v>
+        <v>13681</v>
       </c>
       <c r="J11" s="8">
-        <v>10214</v>
-      </c>
-      <c r="K11" s="19">
-        <v>214</v>
+        <v>10000</v>
+      </c>
+      <c r="K11" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A12" s="4">
-        <v>44529</v>
+        <v>44525</v>
       </c>
       <c r="B12" s="4">
-        <v>44532</v>
+        <v>44530</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>163</v>
@@ -45465,34 +45841,34 @@
         <v>159</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>297</v>
+        <v>67</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>300</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="8">
-        <v>28769</v>
+        <v>7310</v>
       </c>
       <c r="I12" s="8">
-        <v>13383</v>
+        <v>13973</v>
       </c>
       <c r="J12" s="8">
-        <v>38502</v>
+        <v>10214</v>
       </c>
       <c r="K12" s="19">
-        <v>-1498</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A13" s="4">
-        <v>44165</v>
+        <v>44529</v>
       </c>
       <c r="B13" s="4">
-        <v>44168</v>
+        <v>44532</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>159</v>
@@ -45501,30 +45877,28 @@
         <v>297</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="G13" s="5"/>
       <c r="H13" s="8">
-        <v>3846</v>
+        <v>28769</v>
       </c>
       <c r="I13" s="8">
-        <v>13000</v>
+        <v>13383</v>
       </c>
       <c r="J13" s="8">
-        <v>5000</v>
-      </c>
-      <c r="K13" s="21">
-        <v>0</v>
+        <v>38502</v>
+      </c>
+      <c r="K13" s="19">
+        <v>-1498</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A14" s="4">
-        <v>44201</v>
+        <v>44165</v>
       </c>
       <c r="B14" s="4">
-        <v>44204</v>
+        <v>44168</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>158</v>
@@ -45542,13 +45916,13 @@
         <v>160</v>
       </c>
       <c r="H14" s="8">
-        <v>7604</v>
+        <v>3846</v>
       </c>
       <c r="I14" s="8">
-        <v>13152</v>
+        <v>13000</v>
       </c>
       <c r="J14" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K14" s="21">
         <v>0</v>
@@ -45556,10 +45930,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A15" s="4">
-        <v>44236</v>
+        <v>44201</v>
       </c>
       <c r="B15" s="4">
-        <v>44242</v>
+        <v>44204</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>158</v>
@@ -45577,10 +45951,10 @@
         <v>160</v>
       </c>
       <c r="H15" s="8">
-        <v>7041</v>
+        <v>7604</v>
       </c>
       <c r="I15" s="8">
-        <v>14202</v>
+        <v>13152</v>
       </c>
       <c r="J15" s="8">
         <v>10000</v>
@@ -45591,10 +45965,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A16" s="4">
-        <v>44257</v>
+        <v>44236</v>
       </c>
       <c r="B16" s="4">
-        <v>44260</v>
+        <v>44242</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>158</v>
@@ -45612,10 +45986,10 @@
         <v>160</v>
       </c>
       <c r="H16" s="8">
-        <v>6947</v>
+        <v>7041</v>
       </c>
       <c r="I16" s="8">
-        <v>14394</v>
+        <v>14202</v>
       </c>
       <c r="J16" s="8">
         <v>10000</v>
@@ -45626,10 +46000,10 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A17" s="4">
-        <v>44295</v>
+        <v>44257</v>
       </c>
       <c r="B17" s="4">
-        <v>44300</v>
+        <v>44260</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>158</v>
@@ -45647,10 +46021,10 @@
         <v>160</v>
       </c>
       <c r="H17" s="8">
-        <v>6460</v>
+        <v>6947</v>
       </c>
       <c r="I17" s="8">
-        <v>15481</v>
+        <v>14394</v>
       </c>
       <c r="J17" s="8">
         <v>10000</v>
@@ -45661,10 +46035,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A18" s="4">
-        <v>44327</v>
+        <v>44295</v>
       </c>
       <c r="B18" s="4">
-        <v>44330</v>
+        <v>44300</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>158</v>
@@ -45682,13 +46056,13 @@
         <v>160</v>
       </c>
       <c r="H18" s="8">
-        <v>3167</v>
+        <v>6460</v>
       </c>
       <c r="I18" s="8">
-        <v>15789</v>
+        <v>15481</v>
       </c>
       <c r="J18" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K18" s="21">
         <v>0</v>
@@ -45696,10 +46070,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A19" s="4">
-        <v>44350</v>
+        <v>44327</v>
       </c>
       <c r="B19" s="4">
-        <v>44355</v>
+        <v>44330</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>158</v>
@@ -45717,13 +46091,13 @@
         <v>160</v>
       </c>
       <c r="H19" s="8">
-        <v>6263</v>
+        <v>3167</v>
       </c>
       <c r="I19" s="8">
-        <v>15967</v>
+        <v>15789</v>
       </c>
       <c r="J19" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K19" s="21">
         <v>0</v>
@@ -45731,10 +46105,10 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A20" s="4">
-        <v>44377</v>
+        <v>44350</v>
       </c>
       <c r="B20" s="4">
-        <v>44382</v>
+        <v>44355</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>158</v>
@@ -45752,10 +46126,10 @@
         <v>160</v>
       </c>
       <c r="H20" s="8">
-        <v>6081</v>
+        <v>6263</v>
       </c>
       <c r="I20" s="8">
-        <v>16444</v>
+        <v>15967</v>
       </c>
       <c r="J20" s="8">
         <v>10000</v>
@@ -45766,10 +46140,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A21" s="4">
-        <v>44404</v>
+        <v>44377</v>
       </c>
       <c r="B21" s="4">
-        <v>44407</v>
+        <v>44382</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>158</v>
@@ -45778,7 +46152,7 @@
         <v>159</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>67</v>
+        <v>297</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>30</v>
@@ -45787,13 +46161,13 @@
         <v>160</v>
       </c>
       <c r="H21" s="8">
-        <v>11832</v>
+        <v>6081</v>
       </c>
       <c r="I21" s="8">
-        <v>16903</v>
+        <v>16444</v>
       </c>
       <c r="J21" s="8">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="K21" s="21">
         <v>0</v>
@@ -45801,10 +46175,10 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A22" s="4">
-        <v>44435</v>
+        <v>44404</v>
       </c>
       <c r="B22" s="4">
-        <v>44440</v>
+        <v>44407</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>158</v>
@@ -45816,28 +46190,30 @@
         <v>67</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="G22" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H22" s="8">
         <v>11832</v>
       </c>
       <c r="I22" s="8">
-        <v>17067</v>
+        <v>16903</v>
       </c>
       <c r="J22" s="8">
-        <v>20194</v>
-      </c>
-      <c r="K22" s="19">
-        <v>194</v>
+        <v>20000</v>
+      </c>
+      <c r="K22" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A23" s="4">
-        <v>44921</v>
+        <v>44435</v>
       </c>
       <c r="B23" s="4">
-        <v>44924</v>
+        <v>44440</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>158</v>
@@ -45846,33 +46222,31 @@
         <v>159</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>297</v>
+        <v>67</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="G23" s="5"/>
       <c r="H23" s="8">
-        <v>24940</v>
+        <v>11832</v>
       </c>
       <c r="I23" s="8">
-        <v>17961</v>
+        <v>17067</v>
       </c>
       <c r="J23" s="8">
-        <v>44794</v>
-      </c>
-      <c r="K23" s="21">
-        <v>0</v>
+        <v>20194</v>
+      </c>
+      <c r="K23" s="19">
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A24" s="4">
-        <v>45243</v>
+        <v>44921</v>
       </c>
       <c r="B24" s="4">
-        <v>45246</v>
+        <v>44924</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>158</v>
@@ -45890,13 +46264,13 @@
         <v>160</v>
       </c>
       <c r="H24" s="8">
-        <v>590</v>
+        <v>24940</v>
       </c>
       <c r="I24" s="8">
-        <v>23925</v>
+        <v>17961</v>
       </c>
       <c r="J24" s="8">
-        <v>1410</v>
+        <v>44794</v>
       </c>
       <c r="K24" s="21">
         <v>0</v>
@@ -45904,10 +46278,10 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A25" s="4">
-        <v>45656</v>
+        <v>45243</v>
       </c>
       <c r="B25" s="4">
-        <v>45663</v>
+        <v>45246</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>158</v>
@@ -45919,15 +46293,19 @@
         <v>297</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H25" s="8">
+        <v>590</v>
+      </c>
+      <c r="I25" s="8">
+        <v>23925</v>
+      </c>
+      <c r="J25" s="8">
+        <v>1410</v>
       </c>
       <c r="K25" s="21">
         <v>0</v>
@@ -45947,10 +46325,10 @@
         <v>159</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="21">
@@ -45966,34 +46344,30 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A27" s="4">
-        <v>44188</v>
+        <v>45656</v>
       </c>
       <c r="B27" s="4">
-        <v>44193</v>
+        <v>45663</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H27" s="8">
-        <v>4490</v>
-      </c>
-      <c r="I27" s="8">
-        <v>22273</v>
-      </c>
-      <c r="J27" s="8">
-        <v>10000</v>
+        <v>298</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9">
+        <v>0</v>
       </c>
       <c r="K27" s="21">
         <v>0</v>
@@ -46001,10 +46375,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A28" s="4">
-        <v>44224</v>
+        <v>44188</v>
       </c>
       <c r="B28" s="4">
-        <v>44229</v>
+        <v>44193</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>162</v>
@@ -46022,13 +46396,13 @@
         <v>160</v>
       </c>
       <c r="H28" s="8">
-        <v>2108</v>
+        <v>4490</v>
       </c>
       <c r="I28" s="8">
-        <v>23721</v>
+        <v>22273</v>
       </c>
       <c r="J28" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K28" s="21">
         <v>0</v>
@@ -46036,10 +46410,10 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A29" s="4">
-        <v>44257</v>
+        <v>44224</v>
       </c>
       <c r="B29" s="4">
-        <v>44260</v>
+        <v>44229</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>162</v>
@@ -46057,10 +46431,10 @@
         <v>160</v>
       </c>
       <c r="H29" s="8">
-        <v>1938</v>
+        <v>2108</v>
       </c>
       <c r="I29" s="8">
-        <v>25804</v>
+        <v>23721</v>
       </c>
       <c r="J29" s="8">
         <v>5000</v>
@@ -46071,10 +46445,10 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A30" s="4">
-        <v>44295</v>
+        <v>44257</v>
       </c>
       <c r="B30" s="4">
-        <v>44300</v>
+        <v>44260</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>162</v>
@@ -46092,10 +46466,10 @@
         <v>160</v>
       </c>
       <c r="H30" s="8">
-        <v>1920</v>
+        <v>1938</v>
       </c>
       <c r="I30" s="8">
-        <v>26043</v>
+        <v>25804</v>
       </c>
       <c r="J30" s="8">
         <v>5000</v>
@@ -46106,10 +46480,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A31" s="4">
-        <v>44327</v>
+        <v>44295</v>
       </c>
       <c r="B31" s="4">
-        <v>44330</v>
+        <v>44300</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>162</v>
@@ -46127,13 +46501,13 @@
         <v>160</v>
       </c>
       <c r="H31" s="8">
-        <v>4166</v>
+        <v>1920</v>
       </c>
       <c r="I31" s="8">
-        <v>24007</v>
+        <v>26043</v>
       </c>
       <c r="J31" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K31" s="21">
         <v>0</v>
@@ -46141,10 +46515,10 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A32" s="4">
-        <v>44350</v>
+        <v>44327</v>
       </c>
       <c r="B32" s="4">
-        <v>44355</v>
+        <v>44330</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>162</v>
@@ -46162,13 +46536,13 @@
         <v>160</v>
       </c>
       <c r="H32" s="8">
-        <v>1983</v>
+        <v>4166</v>
       </c>
       <c r="I32" s="8">
-        <v>25216</v>
+        <v>24007</v>
       </c>
       <c r="J32" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K32" s="21">
         <v>0</v>
@@ -46176,10 +46550,10 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A33" s="4">
-        <v>44362</v>
+        <v>44350</v>
       </c>
       <c r="B33" s="4">
-        <v>44365</v>
+        <v>44355</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>162</v>
@@ -46191,31 +46565,33 @@
         <v>297</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="G33" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H33" s="8">
-        <v>16605</v>
+        <v>1983</v>
       </c>
       <c r="I33" s="8">
-        <v>26019</v>
+        <v>25216</v>
       </c>
       <c r="J33" s="8">
-        <v>43205</v>
-      </c>
-      <c r="K33" s="19">
-        <v>3205</v>
+        <v>5000</v>
+      </c>
+      <c r="K33" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A34" s="4">
-        <v>44187</v>
+        <v>44362</v>
       </c>
       <c r="B34" s="4">
-        <v>44190</v>
+        <v>44365</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>159</v>
@@ -46224,30 +46600,28 @@
         <v>297</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="G34" s="5"/>
       <c r="H34" s="8">
-        <v>6447</v>
+        <v>16605</v>
       </c>
       <c r="I34" s="8">
-        <v>15511</v>
+        <v>26019</v>
       </c>
       <c r="J34" s="8">
-        <v>10000</v>
+        <v>43205</v>
       </c>
       <c r="K34" s="19">
-        <v>0</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A35" s="4">
-        <v>44224</v>
+        <v>44187</v>
       </c>
       <c r="B35" s="4">
-        <v>44229</v>
+        <v>44190</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>161</v>
@@ -46265,13 +46639,13 @@
         <v>160</v>
       </c>
       <c r="H35" s="8">
-        <v>3093</v>
+        <v>6447</v>
       </c>
       <c r="I35" s="8">
-        <v>16167</v>
+        <v>15511</v>
       </c>
       <c r="J35" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K35" s="19">
         <v>0</v>
@@ -46279,10 +46653,10 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A36" s="4">
-        <v>44257</v>
+        <v>44224</v>
       </c>
       <c r="B36" s="4">
-        <v>44260</v>
+        <v>44229</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>161</v>
@@ -46300,10 +46674,10 @@
         <v>160</v>
       </c>
       <c r="H36" s="8">
-        <v>2978</v>
+        <v>3093</v>
       </c>
       <c r="I36" s="8">
-        <v>16792</v>
+        <v>16167</v>
       </c>
       <c r="J36" s="8">
         <v>5000</v>
@@ -46314,10 +46688,10 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A37" s="4">
-        <v>44295</v>
+        <v>44257</v>
       </c>
       <c r="B37" s="4">
-        <v>44300</v>
+        <v>44260</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>161</v>
@@ -46335,10 +46709,10 @@
         <v>160</v>
       </c>
       <c r="H37" s="8">
-        <v>2810</v>
+        <v>2978</v>
       </c>
       <c r="I37" s="8">
-        <v>17792</v>
+        <v>16792</v>
       </c>
       <c r="J37" s="8">
         <v>5000</v>
@@ -46349,10 +46723,10 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A38" s="4">
-        <v>44327</v>
+        <v>44295</v>
       </c>
       <c r="B38" s="4">
-        <v>44330</v>
+        <v>44300</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>161</v>
@@ -46370,10 +46744,10 @@
         <v>160</v>
       </c>
       <c r="H38" s="8">
-        <v>2903</v>
+        <v>2810</v>
       </c>
       <c r="I38" s="8">
-        <v>17225</v>
+        <v>17792</v>
       </c>
       <c r="J38" s="8">
         <v>5000</v>
@@ -46384,10 +46758,10 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A39" s="4">
-        <v>44350</v>
+        <v>44327</v>
       </c>
       <c r="B39" s="4">
-        <v>44355</v>
+        <v>44330</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>161</v>
@@ -46405,10 +46779,10 @@
         <v>160</v>
       </c>
       <c r="H39" s="8">
-        <v>2819</v>
+        <v>2903</v>
       </c>
       <c r="I39" s="8">
-        <v>17736</v>
+        <v>17225</v>
       </c>
       <c r="J39" s="8">
         <v>5000</v>
@@ -46419,10 +46793,10 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A40" s="4">
-        <v>44362</v>
+        <v>44350</v>
       </c>
       <c r="B40" s="4">
-        <v>44365</v>
+        <v>44355</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>161</v>
@@ -46434,63 +46808,63 @@
         <v>297</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="G40" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H40" s="8">
-        <v>21050</v>
+        <v>2819</v>
       </c>
       <c r="I40" s="8">
-        <v>18410</v>
+        <v>17736</v>
       </c>
       <c r="J40" s="8">
-        <v>38753</v>
+        <v>5000</v>
       </c>
       <c r="K40" s="19">
-        <v>3753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A41" s="4">
-        <v>45243</v>
+        <v>44362</v>
       </c>
       <c r="B41" s="4">
-        <v>45247</v>
+        <v>44365</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>231</v>
+        <v>161</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>67</v>
+        <v>297</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H41" s="19">
-        <v>180143</v>
-      </c>
-      <c r="I41" s="19">
-        <v>12456</v>
+        <v>300</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="8">
+        <v>21050</v>
+      </c>
+      <c r="I41" s="8">
+        <v>18410</v>
       </c>
       <c r="J41" s="8">
-        <v>224386</v>
-      </c>
-      <c r="K41" s="21">
-        <v>0</v>
+        <v>38753</v>
+      </c>
+      <c r="K41" s="19">
+        <v>3753</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A42" s="4">
-        <v>45664</v>
+        <v>45243</v>
       </c>
       <c r="B42" s="4">
-        <v>45671</v>
+        <v>45247</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>231</v>
@@ -46502,26 +46876,61 @@
         <v>67</v>
       </c>
       <c r="F42" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H42" s="19">
+        <v>180143</v>
+      </c>
+      <c r="I42" s="19">
+        <v>12456</v>
+      </c>
+      <c r="J42" s="8">
+        <v>224386</v>
+      </c>
+      <c r="K42" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="A43" s="4">
+        <v>45664</v>
+      </c>
+      <c r="B43" s="4">
+        <v>45671</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="21">
+      <c r="G43" s="5"/>
+      <c r="H43" s="21">
         <v>180143</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I43" s="21">
         <v>15148</v>
       </c>
-      <c r="J42" s="21">
+      <c r="J43" s="21">
         <v>272881</v>
       </c>
-      <c r="K42" s="19">
+      <c r="K43" s="19">
         <v>48494</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K32" xr:uid="{00000000-0009-0000-0000-000007000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K42">
-      <sortCondition ref="C1:C32"/>
+  <autoFilter ref="A1:K33" xr:uid="{00000000-0009-0000-0000-000007000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K43">
+      <sortCondition ref="C1:C33"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18"/>

--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="365" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24539CEA-6A7E-45CB-BBEB-DED95613756F}"/>
+  <xr:revisionPtr revIDLastSave="477" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7287AF3-870A-4D9C-B4E9-B8D9DE6E7C43}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ_日本" sheetId="10" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">国内株式_信用!$A$1:$AA$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">国内株式_特定!$A$1:$N$852</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">国内株式_特定_配当!$A$1:$K$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">投資信託!$A$1:$K$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">投資信託!$A$1:$K$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">米国株式!$A$1:$S$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">米国株式_配当!$A$1:$K$74</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6669" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6868" uniqueCount="454">
   <si>
     <t>約定日</t>
   </si>
@@ -2024,6 +2024,23 @@
   <si>
     <t>積水ハウス</t>
   </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ｓａｎｔｅｃ　Ｈｏｌｄｉｎｇｓ</t>
+  </si>
+  <si>
+    <t>ディスコ</t>
+  </si>
+  <si>
+    <t>ＡＣＳＬ</t>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="18"/>
+  </si>
 </sst>
 </file>
 
@@ -2744,7 +2761,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2907,25 +2924,19 @@
     <xf numFmtId="40" fontId="0" fillId="39" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2949,6 +2960,12 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2960,6 +2977,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3239,31 +3259,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55" t="s">
         <v>216</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59" t="s">
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55" t="s">
         <v>218</v>
       </c>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="65" t="s">
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="63" t="s">
         <v>302</v>
       </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="67"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="65"/>
       <c r="S1" s="37" t="s">
         <v>219</v>
       </c>
@@ -3275,50 +3295,50 @@
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55" t="s">
+      <c r="C2" s="57"/>
+      <c r="D2" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55" t="s">
+      <c r="G2" s="57"/>
+      <c r="H2" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="55" t="s">
+      <c r="K2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="57" t="s">
+      <c r="L2" s="57"/>
+      <c r="M2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="N2" s="62" t="s">
+      <c r="N2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="O2" s="63" t="s">
+      <c r="O2" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="57" t="s">
+      <c r="P2" s="62"/>
+      <c r="Q2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="R2" s="62" t="s">
+      <c r="R2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="S2" s="61" t="s">
+      <c r="S2" s="59" t="s">
         <v>214</v>
       </c>
       <c r="U2" s="49">
@@ -3326,7 +3346,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46080</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3336,38 +3356,38 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="58"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="55"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
       <c r="K3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
       <c r="O3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="P3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="61"/>
-      <c r="U3" s="59" t="s">
+      <c r="Q3" s="58"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="59"/>
+      <c r="U3" s="55" t="s">
         <v>363</v>
       </c>
-      <c r="V3" s="59"/>
+      <c r="V3" s="55"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="34" t="s">
@@ -3383,47 +3403,47 @@
       </c>
       <c r="D4" s="20">
         <f>SUM(D5:D100)</f>
-        <v>450295</v>
+        <v>455495</v>
       </c>
       <c r="E4" s="35">
         <f>SUM(B4:D4)</f>
-        <v>3169595</v>
+        <v>3174795</v>
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>9570503</v>
+        <v>9647753</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
-        <v>-4108029</v>
+        <v>-4158779</v>
       </c>
       <c r="H4" s="20">
         <f>SUM(H5:H100)</f>
-        <v>802155</v>
+        <v>820330</v>
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>6264629</v>
+        <v>6309304</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>4991969.6186499996</v>
+        <v>5027568.8923999993</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
-        <v>210348</v>
+        <v>474248</v>
       </c>
       <c r="L4" s="20">
         <f>SUM(L5:L100)</f>
-        <v>-674243</v>
+        <v>-678053</v>
       </c>
       <c r="M4" s="35">
         <f>SUM(K4:L4)</f>
-        <v>-463895</v>
+        <v>-203805</v>
       </c>
       <c r="N4" s="35">
         <f>SUM(N5:N100)</f>
-        <v>-465950.67485000001</v>
+        <v>-258697.95835</v>
       </c>
       <c r="O4" s="20">
         <f>SUM(O5:O100)</f>
@@ -3443,13 +3463,13 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>7847189.1570999995</v>
-      </c>
-      <c r="U4" s="60">
+        <v>8095241.1473499993</v>
+      </c>
+      <c r="U4" s="56">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.3013698630136989</v>
-      </c>
-      <c r="V4" s="60"/>
+        <v>5.3890410958904109</v>
+      </c>
+      <c r="V4" s="56"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="34" t="s">
@@ -3508,11 +3528,11 @@
         <v>-68778</v>
       </c>
       <c r="O5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2021/1/1",投資信託!$B$2:$B$1025,"&lt;=2021/12/31",投資信託!$K$2:$K$1025,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2021/1/1",投資信託!$B$2:$B$1027,"&lt;=2021/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
         <v>7366</v>
       </c>
       <c r="P5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2021/1/1",投資信託!$B$2:$B$1025,"&lt;=2021/12/31",投資信託!$K$2:$K$1025,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2021/1/1",投資信託!$B$2:$B$1027,"&lt;=2021/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
         <v>-1498</v>
       </c>
       <c r="Q5" s="35">
@@ -3585,11 +3605,11 @@
         <v>-106573</v>
       </c>
       <c r="O6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2022/1/1",投資信託!$B$2:$B$1025,"&lt;=2022/12/31",投資信託!$K$2:$K$1025,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2022/1/1",投資信託!$B$2:$B$1027,"&lt;=2022/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2022/1/1",投資信託!$B$2:$B$1025,"&lt;=2022/12/31",投資信託!$K$2:$K$1025,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2022/1/1",投資信託!$B$2:$B$1027,"&lt;=2022/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q6" s="35">
@@ -3662,11 +3682,11 @@
         <v>-50703</v>
       </c>
       <c r="O7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2023/1/1",投資信託!$B$2:$B$1025,"&lt;=2023/12/31",投資信託!$K$2:$K$1025,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2023/1/1",投資信託!$B$2:$B$1027,"&lt;=2023/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2023/1/1",投資信託!$B$2:$B$1025,"&lt;=2023/12/31",投資信託!$K$2:$K$1025,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2023/1/1",投資信託!$B$2:$B$1027,"&lt;=2023/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q7" s="35">
@@ -3739,11 +3759,11 @@
         <v>-247960</v>
       </c>
       <c r="O8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2024/1/1",投資信託!$B$2:$B$1025,"&lt;=2024/12/31",投資信託!$K$2:$K$1025,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2024/1/1",投資信託!$B$2:$B$1027,"&lt;=2024/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2024/1/1",投資信託!$B$2:$B$1025,"&lt;=2024/12/31",投資信託!$K$2:$K$1025,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2024/1/1",投資信託!$B$2:$B$1027,"&lt;=2024/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q8" s="35">
@@ -3816,11 +3836,11 @@
         <v>8063.3251500000006</v>
       </c>
       <c r="O9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2025/1/1",投資信託!$B$2:$B$1025,"&lt;=2025/12/31",投資信託!$K$2:$K$1025,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2025/1/1",投資信託!$B$2:$B$1027,"&lt;=2025/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
         <v>185421</v>
       </c>
       <c r="P9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2025/1/1",投資信託!$B$2:$B$1025,"&lt;=2025/12/31",投資信託!$K$2:$K$1025,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2025/1/1",投資信託!$B$2:$B$1027,"&lt;=2025/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
         <v>-1071</v>
       </c>
       <c r="Q9" s="35">
@@ -3850,54 +3870,54 @@
       </c>
       <c r="D10" s="19">
         <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1003,国内株式_NISA_配当!$A$2:$A$1003,"&gt;=2026/1/1",国内株式_NISA_配当!$A$2:$A$1003,"&lt;=2026/12/31")</f>
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="E10" s="35">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="F10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
-        <v>1924110</v>
+        <v>2001360</v>
       </c>
       <c r="G10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
-        <v>-682730</v>
+        <v>-733480</v>
       </c>
       <c r="H10" s="19">
         <f>SUMIFS(国内株式_特定_配当!$H$2:$H$999,国内株式_特定_配当!$A$2:$A$999,"&gt;=2026/1/1",国内株式_特定_配当!$A$2:$A$999,"&lt;=2026/12/31")</f>
-        <v>0</v>
+        <v>18175</v>
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>1241380</v>
+        <v>1286055</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>989193.65299999993</v>
+        <v>1024792.92675</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
-        <v>0</v>
+        <v>263900</v>
       </c>
       <c r="L10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&lt;0")</f>
-        <v>0</v>
+        <v>-3810</v>
       </c>
       <c r="M10" s="35">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>260090</v>
       </c>
       <c r="N10" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>207252.71650000001</v>
       </c>
       <c r="O10" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2026/1/1",投資信託!$B$2:$B$1025,"&lt;=2026/12/31",投資信託!$K$2:$K$1025,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2026/1/1",投資信託!$B$2:$B$1027,"&lt;=2026/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P10" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1025,投資信託!$B$2:$B$1025,"&gt;=2026/1/1",投資信託!$B$2:$B$1025,"&lt;=2026/12/31",投資信託!$K$2:$K$1025,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2026/1/1",投資信託!$B$2:$B$1027,"&lt;=2026/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="35">
@@ -3910,7 +3930,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>989193.65299999993</v>
+        <v>1237245.64325</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -3924,6 +3944,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="H2:H3"/>
@@ -3939,11 +3964,6 @@
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6733,49 +6753,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="55" t="s">
         <v>417</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55" t="s">
         <v>416</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
       <c r="K1" s="69" t="s">
         <v>219</v>
       </c>
       <c r="L1" s="69"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="55"/>
+      <c r="C2" s="57"/>
       <c r="D2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="55"/>
+      <c r="G2" s="57"/>
       <c r="H2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="61" t="s">
+      <c r="K2" s="59" t="s">
         <v>214</v>
       </c>
       <c r="L2" s="70" t="s">
@@ -6789,18 +6809,18 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="58"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="56"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="61"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
       <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -9963,7 +9983,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -12214,6 +12234,44 @@
       <c r="K59" s="19">
         <f t="shared" si="9"/>
         <v>25200</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A60" s="4">
+        <v>46111</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D60" s="5">
+        <v>7984</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F60" s="9">
+        <v>13</v>
+      </c>
+      <c r="G60" s="5">
+        <v>400</v>
+      </c>
+      <c r="H60" s="19">
+        <f t="shared" ref="H60" si="10">F60*G60</f>
+        <v>5200</v>
+      </c>
+      <c r="I60" s="19">
+        <v>0</v>
+      </c>
+      <c r="J60" s="19">
+        <f t="shared" ref="J60" si="11">H60-I60</f>
+        <v>5200</v>
+      </c>
+      <c r="K60" s="19">
+        <f t="shared" ref="K60" si="12">J60</f>
+        <v>5200</v>
       </c>
     </row>
   </sheetData>
@@ -12233,7 +12291,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O852"/>
+  <dimension ref="A1:O872"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -48967,7 +49025,7 @@
         <v>90</v>
       </c>
       <c r="M816" s="15">
-        <f t="shared" ref="M816:M852" si="19">IF(G816="買付",H816*I816+SUM(J816:K816),H816*I816-SUM(J816:K816))</f>
+        <f t="shared" ref="M816:M870" si="19">IF(G816="買付",H816*I816+SUM(J816:K816),H816*I816-SUM(J816:K816))</f>
         <v>372050</v>
       </c>
       <c r="N816" s="19">
@@ -50589,6 +50647,900 @@
         <v>706740</v>
       </c>
       <c r="N852" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A853" s="4">
+        <v>46083</v>
+      </c>
+      <c r="B853" s="4">
+        <v>46085</v>
+      </c>
+      <c r="C853" s="5">
+        <v>7012</v>
+      </c>
+      <c r="D853" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E853" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F853" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G853" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H853" s="5">
+        <v>100</v>
+      </c>
+      <c r="I853" s="7">
+        <v>18465</v>
+      </c>
+      <c r="J853" s="9">
+        <v>0</v>
+      </c>
+      <c r="K853" s="9">
+        <v>0</v>
+      </c>
+      <c r="L853" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M853" s="15">
+        <f t="shared" si="19"/>
+        <v>1846500</v>
+      </c>
+      <c r="N853" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A854" s="4">
+        <v>46083</v>
+      </c>
+      <c r="B854" s="4">
+        <v>46085</v>
+      </c>
+      <c r="C854" s="5">
+        <v>9101</v>
+      </c>
+      <c r="D854" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E854" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F854" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G854" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H854" s="5">
+        <v>100</v>
+      </c>
+      <c r="I854" s="7">
+        <v>5490</v>
+      </c>
+      <c r="J854" s="9">
+        <v>0</v>
+      </c>
+      <c r="K854" s="9">
+        <v>0</v>
+      </c>
+      <c r="L854" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M854" s="15">
+        <f t="shared" si="19"/>
+        <v>549000</v>
+      </c>
+      <c r="N854" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A855" s="4">
+        <v>46091</v>
+      </c>
+      <c r="B855" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C855" s="5">
+        <v>5801</v>
+      </c>
+      <c r="D855" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E855" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F855" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G855" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H855" s="5">
+        <v>100</v>
+      </c>
+      <c r="I855" s="7">
+        <v>28100</v>
+      </c>
+      <c r="J855" s="9">
+        <v>0</v>
+      </c>
+      <c r="K855" s="9">
+        <v>0</v>
+      </c>
+      <c r="L855" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M855" s="15">
+        <f t="shared" si="19"/>
+        <v>2810000</v>
+      </c>
+      <c r="N855" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A856" s="4">
+        <v>46091</v>
+      </c>
+      <c r="B856" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C856" s="5">
+        <v>5801</v>
+      </c>
+      <c r="D856" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E856" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F856" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G856" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H856" s="5">
+        <v>100</v>
+      </c>
+      <c r="I856" s="7">
+        <v>27640.5</v>
+      </c>
+      <c r="J856" s="9">
+        <v>0</v>
+      </c>
+      <c r="K856" s="9">
+        <v>0</v>
+      </c>
+      <c r="L856" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M856" s="15">
+        <f t="shared" si="19"/>
+        <v>2764050</v>
+      </c>
+      <c r="N856" s="19">
+        <v>-45950</v>
+      </c>
+    </row>
+    <row r="857" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A857" s="4">
+        <v>46092</v>
+      </c>
+      <c r="B857" s="4">
+        <v>46094</v>
+      </c>
+      <c r="C857" s="5">
+        <v>1540</v>
+      </c>
+      <c r="D857" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="E857" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F857" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G857" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H857" s="5">
+        <v>10</v>
+      </c>
+      <c r="I857" s="7">
+        <v>24790</v>
+      </c>
+      <c r="J857" s="9">
+        <v>0</v>
+      </c>
+      <c r="K857" s="9">
+        <v>0</v>
+      </c>
+      <c r="L857" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M857" s="15">
+        <f t="shared" si="19"/>
+        <v>247900</v>
+      </c>
+      <c r="N857" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A858" s="4">
+        <v>46092</v>
+      </c>
+      <c r="B858" s="4">
+        <v>46094</v>
+      </c>
+      <c r="C858" s="5">
+        <v>5016</v>
+      </c>
+      <c r="D858" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E858" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F858" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G858" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H858" s="5">
+        <v>100</v>
+      </c>
+      <c r="I858" s="7">
+        <v>4326</v>
+      </c>
+      <c r="J858" s="9">
+        <v>0</v>
+      </c>
+      <c r="K858" s="9">
+        <v>0</v>
+      </c>
+      <c r="L858" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M858" s="15">
+        <f t="shared" si="19"/>
+        <v>432600</v>
+      </c>
+      <c r="N858" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A859" s="4">
+        <v>46092</v>
+      </c>
+      <c r="B859" s="4">
+        <v>46094</v>
+      </c>
+      <c r="C859" s="5">
+        <v>5801</v>
+      </c>
+      <c r="D859" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E859" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F859" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G859" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H859" s="5">
+        <v>100</v>
+      </c>
+      <c r="I859" s="7">
+        <v>30580</v>
+      </c>
+      <c r="J859" s="9">
+        <v>0</v>
+      </c>
+      <c r="K859" s="9">
+        <v>0</v>
+      </c>
+      <c r="L859" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M859" s="15">
+        <f t="shared" si="19"/>
+        <v>3058000</v>
+      </c>
+      <c r="N859" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A860" s="4">
+        <v>46092</v>
+      </c>
+      <c r="B860" s="4">
+        <v>46094</v>
+      </c>
+      <c r="C860" s="5">
+        <v>6965</v>
+      </c>
+      <c r="D860" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="E860" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F860" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G860" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H860" s="5">
+        <v>100</v>
+      </c>
+      <c r="I860" s="7">
+        <v>2109.4</v>
+      </c>
+      <c r="J860" s="9">
+        <v>0</v>
+      </c>
+      <c r="K860" s="9">
+        <v>0</v>
+      </c>
+      <c r="L860" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M860" s="15">
+        <f t="shared" si="19"/>
+        <v>210940</v>
+      </c>
+      <c r="N860" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A861" s="4">
+        <v>46093</v>
+      </c>
+      <c r="B861" s="4">
+        <v>46097</v>
+      </c>
+      <c r="C861" s="5">
+        <v>6777</v>
+      </c>
+      <c r="D861" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="E861" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F861" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G861" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H861" s="5">
+        <v>100</v>
+      </c>
+      <c r="I861" s="7">
+        <v>23500</v>
+      </c>
+      <c r="J861" s="9">
+        <v>0</v>
+      </c>
+      <c r="K861" s="9">
+        <v>0</v>
+      </c>
+      <c r="L861" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M861" s="15">
+        <f t="shared" si="19"/>
+        <v>2350000</v>
+      </c>
+      <c r="N861" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A862" s="4">
+        <v>46097</v>
+      </c>
+      <c r="B862" s="4">
+        <v>46099</v>
+      </c>
+      <c r="C862" s="5">
+        <v>6777</v>
+      </c>
+      <c r="D862" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="E862" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F862" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G862" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H862" s="5">
+        <v>100</v>
+      </c>
+      <c r="I862" s="7">
+        <v>23520</v>
+      </c>
+      <c r="J862" s="9">
+        <v>0</v>
+      </c>
+      <c r="K862" s="9">
+        <v>0</v>
+      </c>
+      <c r="L862" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M862" s="15">
+        <f t="shared" si="19"/>
+        <v>2352000</v>
+      </c>
+      <c r="N862" s="19">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="863" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A863" s="4">
+        <v>46098</v>
+      </c>
+      <c r="B863" s="4">
+        <v>46100</v>
+      </c>
+      <c r="C863" s="5">
+        <v>2556</v>
+      </c>
+      <c r="D863" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="E863" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F863" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G863" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H863" s="5">
+        <v>50</v>
+      </c>
+      <c r="I863" s="7">
+        <v>2048</v>
+      </c>
+      <c r="J863" s="9">
+        <v>0</v>
+      </c>
+      <c r="K863" s="9">
+        <v>0</v>
+      </c>
+      <c r="L863" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M863" s="15">
+        <f t="shared" si="19"/>
+        <v>102400</v>
+      </c>
+      <c r="N863" s="19">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="864" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A864" s="4">
+        <v>46098</v>
+      </c>
+      <c r="B864" s="4">
+        <v>46100</v>
+      </c>
+      <c r="C864" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D864" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E864" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F864" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G864" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H864" s="5">
+        <v>100</v>
+      </c>
+      <c r="I864" s="7">
+        <v>22535</v>
+      </c>
+      <c r="J864" s="9">
+        <v>0</v>
+      </c>
+      <c r="K864" s="9">
+        <v>0</v>
+      </c>
+      <c r="L864" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M864" s="15">
+        <f t="shared" si="19"/>
+        <v>2253500</v>
+      </c>
+      <c r="N864" s="19">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="865" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A865" s="4">
+        <v>46098</v>
+      </c>
+      <c r="B865" s="4">
+        <v>46100</v>
+      </c>
+      <c r="C865" s="5">
+        <v>9101</v>
+      </c>
+      <c r="D865" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E865" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F865" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G865" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H865" s="5">
+        <v>100</v>
+      </c>
+      <c r="I865" s="7">
+        <v>6032</v>
+      </c>
+      <c r="J865" s="9">
+        <v>0</v>
+      </c>
+      <c r="K865" s="9">
+        <v>0</v>
+      </c>
+      <c r="L865" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M865" s="15">
+        <f t="shared" si="19"/>
+        <v>603200</v>
+      </c>
+      <c r="N865" s="19">
+        <v>54200</v>
+      </c>
+    </row>
+    <row r="866" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A866" s="4">
+        <v>46099</v>
+      </c>
+      <c r="B866" s="4">
+        <v>46104</v>
+      </c>
+      <c r="C866" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D866" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E866" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F866" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G866" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H866" s="5">
+        <v>200</v>
+      </c>
+      <c r="I866" s="7">
+        <v>1222</v>
+      </c>
+      <c r="J866" s="9">
+        <v>0</v>
+      </c>
+      <c r="K866" s="9">
+        <v>0</v>
+      </c>
+      <c r="L866" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M866" s="15">
+        <f t="shared" si="19"/>
+        <v>244400</v>
+      </c>
+      <c r="N866" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A867" s="4">
+        <v>46099</v>
+      </c>
+      <c r="B867" s="4">
+        <v>46104</v>
+      </c>
+      <c r="C867" s="5">
+        <v>6232</v>
+      </c>
+      <c r="D867" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="E867" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F867" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G867" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H867" s="5">
+        <v>100</v>
+      </c>
+      <c r="I867" s="7">
+        <v>1657</v>
+      </c>
+      <c r="J867" s="9">
+        <v>0</v>
+      </c>
+      <c r="K867" s="9">
+        <v>0</v>
+      </c>
+      <c r="L867" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M867" s="15">
+        <f t="shared" si="19"/>
+        <v>165700</v>
+      </c>
+      <c r="N867" s="19">
+        <v>-4800</v>
+      </c>
+    </row>
+    <row r="868" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A868" s="4">
+        <v>46099</v>
+      </c>
+      <c r="B868" s="4">
+        <v>46104</v>
+      </c>
+      <c r="C868" s="5">
+        <v>7003</v>
+      </c>
+      <c r="D868" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E868" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F868" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G868" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H868" s="5">
+        <v>100</v>
+      </c>
+      <c r="I868" s="7">
+        <v>6714</v>
+      </c>
+      <c r="J868" s="9">
+        <v>0</v>
+      </c>
+      <c r="K868" s="9">
+        <v>0</v>
+      </c>
+      <c r="L868" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M868" s="15">
+        <f t="shared" si="19"/>
+        <v>671400</v>
+      </c>
+      <c r="N868" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="869" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A869" s="4">
+        <v>46099</v>
+      </c>
+      <c r="B869" s="4">
+        <v>46104</v>
+      </c>
+      <c r="C869" s="5">
+        <v>8766</v>
+      </c>
+      <c r="D869" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E869" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F869" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G869" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H869" s="5">
+        <v>100</v>
+      </c>
+      <c r="I869" s="7">
+        <v>6067</v>
+      </c>
+      <c r="J869" s="9">
+        <v>0</v>
+      </c>
+      <c r="K869" s="9">
+        <v>0</v>
+      </c>
+      <c r="L869" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M869" s="15">
+        <f t="shared" si="19"/>
+        <v>606700</v>
+      </c>
+      <c r="N869" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A870" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B870" s="4">
+        <v>46108</v>
+      </c>
+      <c r="C870" s="5">
+        <v>5801</v>
+      </c>
+      <c r="D870" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E870" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F870" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G870" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H870" s="5">
+        <v>100</v>
+      </c>
+      <c r="I870" s="7">
+        <v>30680</v>
+      </c>
+      <c r="J870" s="9">
+        <v>0</v>
+      </c>
+      <c r="K870" s="9">
+        <v>0</v>
+      </c>
+      <c r="L870" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M870" s="15">
+        <f t="shared" si="19"/>
+        <v>3068000</v>
+      </c>
+      <c r="N870" s="19">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="871" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A871" s="4">
+        <v>46108</v>
+      </c>
+      <c r="B871" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C871" s="5">
+        <v>7012</v>
+      </c>
+      <c r="D871" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E871" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F871" s="5"/>
+      <c r="G871" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H871" s="5">
+        <v>400</v>
+      </c>
+      <c r="I871" s="72">
+        <v>3693</v>
+      </c>
+      <c r="J871" s="9">
+        <v>0</v>
+      </c>
+      <c r="K871" s="9">
+        <v>0</v>
+      </c>
+      <c r="L871" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M871" s="15">
+        <v>0</v>
+      </c>
+      <c r="N871" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A872" s="4">
+        <v>46108</v>
+      </c>
+      <c r="B872" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C872" s="5">
+        <v>8136</v>
+      </c>
+      <c r="D872" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="E872" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F872" s="5"/>
+      <c r="G872" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H872" s="5">
+        <v>400</v>
+      </c>
+      <c r="I872" s="72">
+        <v>1462.2</v>
+      </c>
+      <c r="J872" s="9">
+        <v>0</v>
+      </c>
+      <c r="K872" s="9">
+        <v>0</v>
+      </c>
+      <c r="L872" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M872" s="15">
+        <v>0</v>
+      </c>
+      <c r="N872" s="19">
         <v>0</v>
       </c>
     </row>
@@ -50609,7 +51561,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -52698,7 +53650,7 @@
         <v>100</v>
       </c>
       <c r="H55" s="19">
-        <f t="shared" ref="H55:H84" si="11">F55*G55</f>
+        <f t="shared" ref="H55:H86" si="11">F55*G55</f>
         <v>9700</v>
       </c>
       <c r="I55" s="19">
@@ -53655,11 +54607,11 @@
         <v>1218</v>
       </c>
       <c r="J80" s="19">
-        <f t="shared" ref="J80:J84" si="16">H80-I80</f>
+        <f t="shared" ref="J80:J88" si="16">H80-I80</f>
         <v>4782</v>
       </c>
       <c r="K80" s="19">
-        <f t="shared" ref="K80:K84" si="17">J80</f>
+        <f t="shared" ref="K80:K88" si="17">J80</f>
         <v>4782</v>
       </c>
     </row>
@@ -53813,6 +54765,158 @@
       <c r="K84" s="19">
         <f t="shared" si="17"/>
         <v>922</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A85" s="4">
+        <v>46100</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" s="5">
+        <v>1343</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="F85" s="9">
+        <v>25.5</v>
+      </c>
+      <c r="G85" s="5">
+        <v>50</v>
+      </c>
+      <c r="H85" s="19">
+        <f t="shared" si="11"/>
+        <v>1275</v>
+      </c>
+      <c r="I85" s="19">
+        <v>258</v>
+      </c>
+      <c r="J85" s="19">
+        <f t="shared" si="16"/>
+        <v>1017</v>
+      </c>
+      <c r="K85" s="19">
+        <f t="shared" si="17"/>
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A86" s="4">
+        <v>46108</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" s="5">
+        <v>4493</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="F86" s="9">
+        <v>5</v>
+      </c>
+      <c r="G86" s="5">
+        <v>100</v>
+      </c>
+      <c r="H86" s="19">
+        <f t="shared" si="11"/>
+        <v>500</v>
+      </c>
+      <c r="I86" s="19">
+        <v>101</v>
+      </c>
+      <c r="J86" s="19">
+        <f t="shared" si="16"/>
+        <v>399</v>
+      </c>
+      <c r="K86" s="19">
+        <f t="shared" si="17"/>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A87" s="4">
+        <v>46111</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" s="5">
+        <v>7751</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F87" s="9">
+        <v>80</v>
+      </c>
+      <c r="G87" s="5">
+        <v>100</v>
+      </c>
+      <c r="H87" s="19">
+        <f t="shared" ref="H87:H88" si="18">F87*G87</f>
+        <v>8000</v>
+      </c>
+      <c r="I87" s="19">
+        <v>1625</v>
+      </c>
+      <c r="J87" s="19">
+        <f t="shared" si="16"/>
+        <v>6375</v>
+      </c>
+      <c r="K87" s="19">
+        <f t="shared" si="17"/>
+        <v>6375</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A88" s="4">
+        <v>46111</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" s="5">
+        <v>1911</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="F88" s="9">
+        <v>28</v>
+      </c>
+      <c r="G88" s="5">
+        <v>300</v>
+      </c>
+      <c r="H88" s="19">
+        <f t="shared" si="18"/>
+        <v>8400</v>
+      </c>
+      <c r="I88" s="19">
+        <v>1706</v>
+      </c>
+      <c r="J88" s="19">
+        <f t="shared" si="16"/>
+        <v>6694</v>
+      </c>
+      <c r="K88" s="19">
+        <f t="shared" si="17"/>
+        <v>6694</v>
       </c>
     </row>
   </sheetData>
@@ -53828,7 +54932,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:AA67"/>
+  <dimension ref="A1:AA77"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -59104,7 +60208,7 @@
       <c r="Q64" s="4">
         <v>45398</v>
       </c>
-      <c r="R64" s="9">
+      <c r="R64" s="19">
         <v>7523</v>
       </c>
       <c r="S64" s="9">
@@ -59323,7 +60427,7 @@
       <c r="Q67" s="4">
         <v>45937</v>
       </c>
-      <c r="R67" s="9">
+      <c r="R67" s="19">
         <v>7140</v>
       </c>
       <c r="S67" s="9">
@@ -59351,6 +60455,834 @@
         <v>0</v>
       </c>
       <c r="AA67" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A68" s="4">
+        <v>46084</v>
+      </c>
+      <c r="B68" s="4">
+        <v>46086</v>
+      </c>
+      <c r="C68" s="5">
+        <v>6861</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J68" s="5">
+        <v>100</v>
+      </c>
+      <c r="K68" s="7">
+        <v>62760</v>
+      </c>
+      <c r="L68" s="9">
+        <v>0</v>
+      </c>
+      <c r="M68" s="9">
+        <v>0</v>
+      </c>
+      <c r="N68" s="9">
+        <v>0</v>
+      </c>
+      <c r="O68" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="P68" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="R68" s="9">
+        <v>0</v>
+      </c>
+      <c r="S68" s="9">
+        <v>0</v>
+      </c>
+      <c r="T68" s="9">
+        <v>0</v>
+      </c>
+      <c r="U68" s="9">
+        <v>0</v>
+      </c>
+      <c r="V68" s="9">
+        <v>0</v>
+      </c>
+      <c r="W68" s="9">
+        <v>0</v>
+      </c>
+      <c r="X68" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A69" s="4">
+        <v>46085</v>
+      </c>
+      <c r="B69" s="4">
+        <v>46087</v>
+      </c>
+      <c r="C69" s="5">
+        <v>6861</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J69" s="5">
+        <v>100</v>
+      </c>
+      <c r="K69" s="7">
+        <v>61160</v>
+      </c>
+      <c r="L69" s="9">
+        <v>0</v>
+      </c>
+      <c r="M69" s="9">
+        <v>0</v>
+      </c>
+      <c r="N69" s="9">
+        <v>483</v>
+      </c>
+      <c r="O69" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P69" s="31">
+        <v>159517</v>
+      </c>
+      <c r="Q69" s="4">
+        <v>46084</v>
+      </c>
+      <c r="R69" s="54">
+        <v>62760</v>
+      </c>
+      <c r="S69" s="9">
+        <v>0</v>
+      </c>
+      <c r="T69" s="9">
+        <v>0</v>
+      </c>
+      <c r="U69" s="9">
+        <v>0</v>
+      </c>
+      <c r="V69" s="9">
+        <v>0</v>
+      </c>
+      <c r="W69" s="9">
+        <v>105</v>
+      </c>
+      <c r="X69" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="9">
+        <v>378</v>
+      </c>
+      <c r="Z69" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A70" s="4">
+        <v>46091</v>
+      </c>
+      <c r="B70" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C70" s="5">
+        <v>5801</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J70" s="5">
+        <v>100</v>
+      </c>
+      <c r="K70" s="7">
+        <v>27406</v>
+      </c>
+      <c r="L70" s="9">
+        <v>0</v>
+      </c>
+      <c r="M70" s="9">
+        <v>0</v>
+      </c>
+      <c r="N70" s="9">
+        <v>83</v>
+      </c>
+      <c r="O70" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P70" s="8">
+        <v>18867</v>
+      </c>
+      <c r="Q70" s="49">
+        <v>46091</v>
+      </c>
+      <c r="R70" s="7">
+        <v>27595.5</v>
+      </c>
+      <c r="S70" s="9">
+        <v>0</v>
+      </c>
+      <c r="T70" s="9">
+        <v>0</v>
+      </c>
+      <c r="U70" s="9">
+        <v>0</v>
+      </c>
+      <c r="V70" s="9">
+        <v>0</v>
+      </c>
+      <c r="W70" s="9">
+        <v>0</v>
+      </c>
+      <c r="X70" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="9">
+        <v>83</v>
+      </c>
+      <c r="Z70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A71" s="4">
+        <v>46091</v>
+      </c>
+      <c r="B71" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C71" s="5">
+        <v>5801</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J71" s="5">
+        <v>100</v>
+      </c>
+      <c r="K71" s="7">
+        <v>27595.5</v>
+      </c>
+      <c r="L71" s="9">
+        <v>0</v>
+      </c>
+      <c r="M71" s="9">
+        <v>0</v>
+      </c>
+      <c r="N71" s="9">
+        <v>0</v>
+      </c>
+      <c r="O71" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P71" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R71" s="9">
+        <v>0</v>
+      </c>
+      <c r="S71" s="9">
+        <v>0</v>
+      </c>
+      <c r="T71" s="9">
+        <v>0</v>
+      </c>
+      <c r="U71" s="9">
+        <v>0</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A72" s="4">
+        <v>46091</v>
+      </c>
+      <c r="B72" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C72" s="5">
+        <v>5803</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J72" s="5">
+        <v>100</v>
+      </c>
+      <c r="K72" s="7">
+        <v>23965</v>
+      </c>
+      <c r="L72" s="9">
+        <v>0</v>
+      </c>
+      <c r="M72" s="9">
+        <v>0</v>
+      </c>
+      <c r="N72" s="9">
+        <v>73</v>
+      </c>
+      <c r="O72" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P72" s="8">
+        <v>39427</v>
+      </c>
+      <c r="Q72" s="49">
+        <v>46091</v>
+      </c>
+      <c r="R72" s="7">
+        <v>24360</v>
+      </c>
+      <c r="S72" s="9">
+        <v>0</v>
+      </c>
+      <c r="T72" s="9">
+        <v>0</v>
+      </c>
+      <c r="U72" s="9">
+        <v>0</v>
+      </c>
+      <c r="V72" s="9">
+        <v>0</v>
+      </c>
+      <c r="W72" s="9">
+        <v>0</v>
+      </c>
+      <c r="X72" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="9">
+        <v>73</v>
+      </c>
+      <c r="Z72" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A73" s="4">
+        <v>46091</v>
+      </c>
+      <c r="B73" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C73" s="5">
+        <v>5803</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J73" s="5">
+        <v>100</v>
+      </c>
+      <c r="K73" s="7">
+        <v>24360</v>
+      </c>
+      <c r="L73" s="9">
+        <v>0</v>
+      </c>
+      <c r="M73" s="9">
+        <v>0</v>
+      </c>
+      <c r="N73" s="9">
+        <v>0</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P73" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R73" s="9">
+        <v>0</v>
+      </c>
+      <c r="S73" s="9">
+        <v>0</v>
+      </c>
+      <c r="T73" s="9">
+        <v>0</v>
+      </c>
+      <c r="U73" s="9">
+        <v>0</v>
+      </c>
+      <c r="V73" s="9">
+        <v>0</v>
+      </c>
+      <c r="W73" s="9">
+        <v>0</v>
+      </c>
+      <c r="X73" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A74" s="4">
+        <v>46091</v>
+      </c>
+      <c r="B74" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C74" s="5">
+        <v>6146</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J74" s="5">
+        <v>100</v>
+      </c>
+      <c r="K74" s="7">
+        <v>69580</v>
+      </c>
+      <c r="L74" s="9">
+        <v>0</v>
+      </c>
+      <c r="M74" s="9">
+        <v>0</v>
+      </c>
+      <c r="N74" s="9">
+        <v>211</v>
+      </c>
+      <c r="O74" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P74" s="8">
+        <v>46089</v>
+      </c>
+      <c r="Q74" s="49">
+        <v>46091</v>
+      </c>
+      <c r="R74" s="7">
+        <v>70043</v>
+      </c>
+      <c r="S74" s="9">
+        <v>0</v>
+      </c>
+      <c r="T74" s="9">
+        <v>0</v>
+      </c>
+      <c r="U74" s="9">
+        <v>0</v>
+      </c>
+      <c r="V74" s="9">
+        <v>0</v>
+      </c>
+      <c r="W74" s="9">
+        <v>0</v>
+      </c>
+      <c r="X74" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="9">
+        <v>211</v>
+      </c>
+      <c r="Z74" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A75" s="4">
+        <v>46091</v>
+      </c>
+      <c r="B75" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C75" s="5">
+        <v>6146</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J75" s="5">
+        <v>100</v>
+      </c>
+      <c r="K75" s="7">
+        <v>70043</v>
+      </c>
+      <c r="L75" s="9">
+        <v>0</v>
+      </c>
+      <c r="M75" s="9">
+        <v>0</v>
+      </c>
+      <c r="N75" s="9">
+        <v>0</v>
+      </c>
+      <c r="O75" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R75" s="9">
+        <v>0</v>
+      </c>
+      <c r="S75" s="9">
+        <v>0</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A76" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B76" s="4">
+        <v>46107</v>
+      </c>
+      <c r="C76" s="5">
+        <v>6146</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J76" s="5">
+        <v>100</v>
+      </c>
+      <c r="K76" s="7">
+        <v>67240</v>
+      </c>
+      <c r="L76" s="9">
+        <v>0</v>
+      </c>
+      <c r="M76" s="9">
+        <v>0</v>
+      </c>
+      <c r="N76" s="9">
+        <v>0</v>
+      </c>
+      <c r="O76" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="P76" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="R76" s="7">
+        <v>0</v>
+      </c>
+      <c r="S76" s="9">
+        <v>0</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A77" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B77" s="4">
+        <v>46108</v>
+      </c>
+      <c r="C77" s="5">
+        <v>6146</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J77" s="5">
+        <v>100</v>
+      </c>
+      <c r="K77" s="7">
+        <v>67270</v>
+      </c>
+      <c r="L77" s="9">
+        <v>0</v>
+      </c>
+      <c r="M77" s="9">
+        <v>0</v>
+      </c>
+      <c r="N77" s="9">
+        <v>810</v>
+      </c>
+      <c r="O77" s="9"/>
+      <c r="P77" s="21">
+        <v>-3810</v>
+      </c>
+      <c r="Q77" s="4">
+        <v>46106</v>
+      </c>
+      <c r="R77" s="9">
+        <v>67240</v>
+      </c>
+      <c r="S77" s="9">
+        <v>0</v>
+      </c>
+      <c r="T77" s="9">
+        <v>0</v>
+      </c>
+      <c r="U77" s="9">
+        <v>0</v>
+      </c>
+      <c r="V77" s="9">
+        <v>0</v>
+      </c>
+      <c r="W77" s="9">
+        <v>0</v>
+      </c>
+      <c r="X77" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="9">
+        <v>810</v>
+      </c>
+      <c r="Z77" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="9">
         <v>0</v>
       </c>
     </row>
@@ -59367,7 +61299,7 @@
   <sheetPr>
     <tabColor theme="2"/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -60241,7 +62173,7 @@
       <c r="G25" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="H25" s="54">
+      <c r="H25" s="21">
         <v>8992</v>
       </c>
       <c r="I25" s="21">
@@ -60256,13 +62188,13 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" s="4">
-        <v>45945</v>
+        <v>46094</v>
       </c>
       <c r="B26" s="4">
-        <v>45950</v>
+        <v>46100</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>377</v>
+        <v>282</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>159</v>
@@ -60277,13 +62209,13 @@
         <v>284</v>
       </c>
       <c r="H26" s="21">
-        <v>40242</v>
+        <v>8935</v>
       </c>
       <c r="I26" s="21">
-        <v>17395</v>
+        <v>33579</v>
       </c>
       <c r="J26" s="21">
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="K26" s="21">
         <v>0</v>
@@ -60291,10 +62223,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" s="4">
-        <v>45974</v>
+        <v>45945</v>
       </c>
       <c r="B27" s="4">
-        <v>45979</v>
+        <v>45950</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>377</v>
@@ -60312,10 +62244,10 @@
         <v>284</v>
       </c>
       <c r="H27" s="21">
-        <v>38038</v>
+        <v>40242</v>
       </c>
       <c r="I27" s="21">
-        <v>18403</v>
+        <v>17395</v>
       </c>
       <c r="J27" s="21">
         <v>70000</v>
@@ -60326,10 +62258,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" s="4">
-        <v>46006</v>
+        <v>45974</v>
       </c>
       <c r="B28" s="4">
-        <v>46009</v>
+        <v>45979</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>377</v>
@@ -60347,10 +62279,10 @@
         <v>284</v>
       </c>
       <c r="H28" s="21">
-        <v>37910</v>
+        <v>38038</v>
       </c>
       <c r="I28" s="21">
-        <v>18465</v>
+        <v>18403</v>
       </c>
       <c r="J28" s="21">
         <v>70000</v>
@@ -60361,10 +62293,10 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" s="4">
-        <v>46036</v>
+        <v>46006</v>
       </c>
       <c r="B29" s="4">
-        <v>46041</v>
+        <v>46009</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>377</v>
@@ -60382,10 +62314,10 @@
         <v>284</v>
       </c>
       <c r="H29" s="21">
-        <v>35338</v>
+        <v>37910</v>
       </c>
       <c r="I29" s="21">
-        <v>19809</v>
+        <v>18465</v>
       </c>
       <c r="J29" s="21">
         <v>70000</v>
@@ -60396,10 +62328,10 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" s="4">
-        <v>46066</v>
+        <v>46036</v>
       </c>
       <c r="B30" s="4">
-        <v>46071</v>
+        <v>46041</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>377</v>
@@ -60417,10 +62349,10 @@
         <v>284</v>
       </c>
       <c r="H30" s="21">
-        <v>34978</v>
+        <v>35338</v>
       </c>
       <c r="I30" s="21">
-        <v>20013</v>
+        <v>19809</v>
       </c>
       <c r="J30" s="21">
         <v>70000</v>
@@ -60431,34 +62363,34 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" s="4">
-        <v>44368</v>
+        <v>46066</v>
       </c>
       <c r="B31" s="4">
-        <v>44371</v>
+        <v>46071</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>163</v>
+        <v>377</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H31" s="8">
-        <v>21735</v>
-      </c>
-      <c r="I31" s="8">
-        <v>13803</v>
-      </c>
-      <c r="J31" s="8">
-        <v>30000</v>
+        <v>284</v>
+      </c>
+      <c r="H31" s="21">
+        <v>34978</v>
+      </c>
+      <c r="I31" s="21">
+        <v>20013</v>
+      </c>
+      <c r="J31" s="21">
+        <v>70000</v>
       </c>
       <c r="K31" s="21">
         <v>0</v>
@@ -60466,34 +62398,34 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" s="4">
-        <v>44377</v>
+        <v>46094</v>
       </c>
       <c r="B32" s="4">
-        <v>44382</v>
+        <v>46099</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>163</v>
+        <v>377</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H32" s="8">
-        <v>7034</v>
-      </c>
-      <c r="I32" s="8">
-        <v>14217</v>
-      </c>
-      <c r="J32" s="8">
-        <v>10000</v>
+        <v>284</v>
+      </c>
+      <c r="H32" s="21">
+        <v>35624</v>
+      </c>
+      <c r="I32" s="21">
+        <v>19650</v>
+      </c>
+      <c r="J32" s="21">
+        <v>70000</v>
       </c>
       <c r="K32" s="21">
         <v>0</v>
@@ -60501,10 +62433,10 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="4">
-        <v>44529</v>
+        <v>44368</v>
       </c>
       <c r="B33" s="4">
-        <v>44532</v>
+        <v>44371</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>163</v>
@@ -60516,28 +62448,30 @@
         <v>295</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G33" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H33" s="8">
-        <v>28769</v>
+        <v>21735</v>
       </c>
       <c r="I33" s="8">
-        <v>13383</v>
+        <v>13803</v>
       </c>
       <c r="J33" s="8">
-        <v>38502</v>
-      </c>
-      <c r="K33" s="19">
-        <v>-1498</v>
+        <v>30000</v>
+      </c>
+      <c r="K33" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="4">
-        <v>44403</v>
+        <v>44377</v>
       </c>
       <c r="B34" s="4">
-        <v>44406</v>
+        <v>44382</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>163</v>
@@ -60546,7 +62480,7 @@
         <v>159</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>30</v>
@@ -60555,10 +62489,10 @@
         <v>160</v>
       </c>
       <c r="H34" s="8">
-        <v>7310</v>
+        <v>7034</v>
       </c>
       <c r="I34" s="8">
-        <v>13681</v>
+        <v>14217</v>
       </c>
       <c r="J34" s="8">
         <v>10000</v>
@@ -60569,10 +62503,10 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="4">
-        <v>44525</v>
+        <v>44529</v>
       </c>
       <c r="B35" s="4">
-        <v>44530</v>
+        <v>44532</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>163</v>
@@ -60581,40 +62515,40 @@
         <v>159</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="8">
-        <v>7310</v>
+        <v>28769</v>
       </c>
       <c r="I35" s="8">
-        <v>13973</v>
+        <v>13383</v>
       </c>
       <c r="J35" s="8">
-        <v>10214</v>
+        <v>38502</v>
       </c>
       <c r="K35" s="19">
-        <v>214</v>
+        <v>-1498</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="4">
-        <v>44165</v>
+        <v>44403</v>
       </c>
       <c r="B36" s="4">
-        <v>44168</v>
+        <v>44406</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>295</v>
+        <v>67</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>30</v>
@@ -60623,13 +62557,13 @@
         <v>160</v>
       </c>
       <c r="H36" s="8">
-        <v>3846</v>
+        <v>7310</v>
       </c>
       <c r="I36" s="8">
-        <v>13000</v>
+        <v>13681</v>
       </c>
       <c r="J36" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K36" s="21">
         <v>0</v>
@@ -60637,45 +62571,43 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="4">
-        <v>44201</v>
+        <v>44525</v>
       </c>
       <c r="B37" s="4">
-        <v>44204</v>
+        <v>44530</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>295</v>
+        <v>67</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="G37" s="5"/>
       <c r="H37" s="8">
-        <v>7604</v>
+        <v>7310</v>
       </c>
       <c r="I37" s="8">
-        <v>13152</v>
+        <v>13973</v>
       </c>
       <c r="J37" s="8">
-        <v>10000</v>
-      </c>
-      <c r="K37" s="21">
-        <v>0</v>
+        <v>10214</v>
+      </c>
+      <c r="K37" s="19">
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="4">
-        <v>44236</v>
+        <v>44165</v>
       </c>
       <c r="B38" s="4">
-        <v>44242</v>
+        <v>44168</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>158</v>
@@ -60693,13 +62625,13 @@
         <v>160</v>
       </c>
       <c r="H38" s="8">
-        <v>7041</v>
+        <v>3846</v>
       </c>
       <c r="I38" s="8">
-        <v>14202</v>
+        <v>13000</v>
       </c>
       <c r="J38" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K38" s="21">
         <v>0</v>
@@ -60707,10 +62639,10 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="4">
-        <v>44257</v>
+        <v>44201</v>
       </c>
       <c r="B39" s="4">
-        <v>44260</v>
+        <v>44204</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>158</v>
@@ -60728,10 +62660,10 @@
         <v>160</v>
       </c>
       <c r="H39" s="8">
-        <v>6947</v>
+        <v>7604</v>
       </c>
       <c r="I39" s="8">
-        <v>14394</v>
+        <v>13152</v>
       </c>
       <c r="J39" s="8">
         <v>10000</v>
@@ -60742,10 +62674,10 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="4">
-        <v>44295</v>
+        <v>44236</v>
       </c>
       <c r="B40" s="4">
-        <v>44300</v>
+        <v>44242</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>158</v>
@@ -60763,10 +62695,10 @@
         <v>160</v>
       </c>
       <c r="H40" s="8">
-        <v>6460</v>
+        <v>7041</v>
       </c>
       <c r="I40" s="8">
-        <v>15481</v>
+        <v>14202</v>
       </c>
       <c r="J40" s="8">
         <v>10000</v>
@@ -60777,10 +62709,10 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B41" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>158</v>
@@ -60798,13 +62730,13 @@
         <v>160</v>
       </c>
       <c r="H41" s="8">
-        <v>3167</v>
+        <v>6947</v>
       </c>
       <c r="I41" s="8">
-        <v>15789</v>
+        <v>14394</v>
       </c>
       <c r="J41" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K41" s="21">
         <v>0</v>
@@ -60812,10 +62744,10 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B42" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>158</v>
@@ -60833,10 +62765,10 @@
         <v>160</v>
       </c>
       <c r="H42" s="8">
-        <v>6263</v>
+        <v>6460</v>
       </c>
       <c r="I42" s="8">
-        <v>15967</v>
+        <v>15481</v>
       </c>
       <c r="J42" s="8">
         <v>10000</v>
@@ -60847,10 +62779,10 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="4">
-        <v>44377</v>
+        <v>44327</v>
       </c>
       <c r="B43" s="4">
-        <v>44382</v>
+        <v>44330</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>158</v>
@@ -60868,13 +62800,13 @@
         <v>160</v>
       </c>
       <c r="H43" s="8">
-        <v>6081</v>
+        <v>3167</v>
       </c>
       <c r="I43" s="8">
-        <v>16444</v>
+        <v>15789</v>
       </c>
       <c r="J43" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K43" s="21">
         <v>0</v>
@@ -60882,10 +62814,10 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="4">
-        <v>44921</v>
+        <v>44350</v>
       </c>
       <c r="B44" s="4">
-        <v>44924</v>
+        <v>44355</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>158</v>
@@ -60903,13 +62835,13 @@
         <v>160</v>
       </c>
       <c r="H44" s="8">
-        <v>24940</v>
+        <v>6263</v>
       </c>
       <c r="I44" s="8">
-        <v>17961</v>
+        <v>15967</v>
       </c>
       <c r="J44" s="8">
-        <v>44794</v>
+        <v>10000</v>
       </c>
       <c r="K44" s="21">
         <v>0</v>
@@ -60917,10 +62849,10 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" s="4">
-        <v>45243</v>
+        <v>44377</v>
       </c>
       <c r="B45" s="4">
-        <v>45246</v>
+        <v>44382</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>158</v>
@@ -60938,13 +62870,13 @@
         <v>160</v>
       </c>
       <c r="H45" s="8">
-        <v>590</v>
+        <v>6081</v>
       </c>
       <c r="I45" s="8">
-        <v>23925</v>
+        <v>16444</v>
       </c>
       <c r="J45" s="8">
-        <v>1410</v>
+        <v>10000</v>
       </c>
       <c r="K45" s="21">
         <v>0</v>
@@ -60952,10 +62884,10 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="4">
-        <v>45656</v>
+        <v>44921</v>
       </c>
       <c r="B46" s="4">
-        <v>45663</v>
+        <v>44924</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>158</v>
@@ -60967,15 +62899,19 @@
         <v>295</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H46" s="8">
+        <v>24940</v>
+      </c>
+      <c r="I46" s="8">
+        <v>17961</v>
+      </c>
+      <c r="J46" s="8">
+        <v>44794</v>
       </c>
       <c r="K46" s="21">
         <v>0</v>
@@ -60983,10 +62919,10 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" s="4">
-        <v>45772</v>
+        <v>45243</v>
       </c>
       <c r="B47" s="4">
-        <v>45778</v>
+        <v>45246</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>158</v>
@@ -60998,28 +62934,30 @@
         <v>295</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="21">
-        <v>69093</v>
-      </c>
-      <c r="I47" s="19">
-        <v>28502</v>
-      </c>
-      <c r="J47" s="19">
-        <v>196929</v>
+        <v>30</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H47" s="8">
+        <v>590</v>
+      </c>
+      <c r="I47" s="8">
+        <v>23925</v>
+      </c>
+      <c r="J47" s="8">
+        <v>1410</v>
       </c>
       <c r="K47" s="21">
-        <v>86850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="4">
-        <v>44404</v>
+        <v>45656</v>
       </c>
       <c r="B48" s="4">
-        <v>44407</v>
+        <v>45663</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>158</v>
@@ -61028,22 +62966,18 @@
         <v>159</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H48" s="8">
-        <v>11832</v>
-      </c>
-      <c r="I48" s="8">
-        <v>16903</v>
-      </c>
-      <c r="J48" s="8">
-        <v>20000</v>
+        <v>289</v>
+      </c>
+      <c r="G48" s="5"/>
+      <c r="H48" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9">
+        <v>0</v>
       </c>
       <c r="K48" s="21">
         <v>0</v>
@@ -61051,10 +62985,10 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" s="4">
-        <v>44435</v>
+        <v>45772</v>
       </c>
       <c r="B49" s="4">
-        <v>44440</v>
+        <v>45778</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>158</v>
@@ -61063,31 +62997,31 @@
         <v>159</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G49" s="5"/>
-      <c r="H49" s="8">
-        <v>11832</v>
-      </c>
-      <c r="I49" s="8">
-        <v>17067</v>
-      </c>
-      <c r="J49" s="8">
-        <v>20194</v>
-      </c>
-      <c r="K49" s="19">
-        <v>194</v>
+      <c r="H49" s="21">
+        <v>69093</v>
+      </c>
+      <c r="I49" s="19">
+        <v>28502</v>
+      </c>
+      <c r="J49" s="19">
+        <v>196929</v>
+      </c>
+      <c r="K49" s="21">
+        <v>86850</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" s="4">
-        <v>45656</v>
+        <v>44404</v>
       </c>
       <c r="B50" s="4">
-        <v>45663</v>
+        <v>44407</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>158</v>
@@ -61096,18 +63030,22 @@
         <v>159</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>294</v>
+        <v>67</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H50" s="8">
+        <v>11832</v>
+      </c>
+      <c r="I50" s="8">
+        <v>16903</v>
+      </c>
+      <c r="J50" s="8">
+        <v>20000</v>
       </c>
       <c r="K50" s="21">
         <v>0</v>
@@ -61115,10 +63053,10 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" s="4">
-        <v>45824</v>
+        <v>44435</v>
       </c>
       <c r="B51" s="4">
-        <v>45827</v>
+        <v>44440</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>158</v>
@@ -61127,55 +63065,51 @@
         <v>159</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G51" s="5"/>
-      <c r="H51" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I51" s="19">
-        <v>31398</v>
-      </c>
-      <c r="J51" s="19">
-        <v>12076</v>
-      </c>
-      <c r="K51" s="21">
-        <v>-1071</v>
+      <c r="H51" s="8">
+        <v>11832</v>
+      </c>
+      <c r="I51" s="8">
+        <v>17067</v>
+      </c>
+      <c r="J51" s="8">
+        <v>20194</v>
+      </c>
+      <c r="K51" s="19">
+        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" s="4">
-        <v>44188</v>
+        <v>45656</v>
       </c>
       <c r="B52" s="4">
-        <v>44193</v>
+        <v>45663</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H52" s="8">
-        <v>4490</v>
-      </c>
-      <c r="I52" s="8">
-        <v>22273</v>
-      </c>
-      <c r="J52" s="8">
-        <v>10000</v>
+        <v>296</v>
+      </c>
+      <c r="G52" s="5"/>
+      <c r="H52" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9">
+        <v>0</v>
       </c>
       <c r="K52" s="21">
         <v>0</v>
@@ -61183,45 +63117,43 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" s="4">
-        <v>44224</v>
+        <v>45824</v>
       </c>
       <c r="B53" s="4">
-        <v>44229</v>
+        <v>45827</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>295</v>
+        <v>68</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H53" s="8">
-        <v>2108</v>
-      </c>
-      <c r="I53" s="8">
-        <v>23721</v>
-      </c>
-      <c r="J53" s="8">
-        <v>5000</v>
+        <v>298</v>
+      </c>
+      <c r="G53" s="5"/>
+      <c r="H53" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I53" s="19">
+        <v>31398</v>
+      </c>
+      <c r="J53" s="19">
+        <v>12076</v>
       </c>
       <c r="K53" s="21">
-        <v>0</v>
+        <v>-1071</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" s="4">
-        <v>44257</v>
+        <v>44188</v>
       </c>
       <c r="B54" s="4">
-        <v>44260</v>
+        <v>44193</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>162</v>
@@ -61239,13 +63171,13 @@
         <v>160</v>
       </c>
       <c r="H54" s="8">
-        <v>1938</v>
+        <v>4490</v>
       </c>
       <c r="I54" s="8">
-        <v>25804</v>
+        <v>22273</v>
       </c>
       <c r="J54" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K54" s="21">
         <v>0</v>
@@ -61253,10 +63185,10 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" s="4">
-        <v>44295</v>
+        <v>44224</v>
       </c>
       <c r="B55" s="4">
-        <v>44300</v>
+        <v>44229</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>162</v>
@@ -61274,10 +63206,10 @@
         <v>160</v>
       </c>
       <c r="H55" s="8">
-        <v>1920</v>
+        <v>2108</v>
       </c>
       <c r="I55" s="8">
-        <v>26043</v>
+        <v>23721</v>
       </c>
       <c r="J55" s="8">
         <v>5000</v>
@@ -61288,10 +63220,10 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B56" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>162</v>
@@ -61309,13 +63241,13 @@
         <v>160</v>
       </c>
       <c r="H56" s="8">
-        <v>4166</v>
+        <v>1938</v>
       </c>
       <c r="I56" s="8">
-        <v>24007</v>
+        <v>25804</v>
       </c>
       <c r="J56" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K56" s="21">
         <v>0</v>
@@ -61323,10 +63255,10 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B57" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>162</v>
@@ -61344,10 +63276,10 @@
         <v>160</v>
       </c>
       <c r="H57" s="8">
-        <v>1983</v>
+        <v>1920</v>
       </c>
       <c r="I57" s="8">
-        <v>25216</v>
+        <v>26043</v>
       </c>
       <c r="J57" s="8">
         <v>5000</v>
@@ -61358,10 +63290,10 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" s="4">
-        <v>44362</v>
+        <v>44327</v>
       </c>
       <c r="B58" s="4">
-        <v>44365</v>
+        <v>44330</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>162</v>
@@ -61373,31 +63305,33 @@
         <v>295</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G58" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H58" s="8">
-        <v>16605</v>
+        <v>4166</v>
       </c>
       <c r="I58" s="8">
-        <v>26019</v>
+        <v>24007</v>
       </c>
       <c r="J58" s="8">
-        <v>43205</v>
-      </c>
-      <c r="K58" s="19">
-        <v>3205</v>
+        <v>10000</v>
+      </c>
+      <c r="K58" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" s="4">
-        <v>44187</v>
+        <v>44350</v>
       </c>
       <c r="B59" s="4">
-        <v>44190</v>
+        <v>44355</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>159</v>
@@ -61412,27 +63346,27 @@
         <v>160</v>
       </c>
       <c r="H59" s="8">
-        <v>6447</v>
+        <v>1983</v>
       </c>
       <c r="I59" s="8">
-        <v>15511</v>
+        <v>25216</v>
       </c>
       <c r="J59" s="8">
-        <v>10000</v>
-      </c>
-      <c r="K59" s="19">
+        <v>5000</v>
+      </c>
+      <c r="K59" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60" s="4">
-        <v>44224</v>
+        <v>44362</v>
       </c>
       <c r="B60" s="4">
-        <v>44229</v>
+        <v>44365</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>159</v>
@@ -61441,30 +63375,28 @@
         <v>295</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="G60" s="5"/>
       <c r="H60" s="8">
-        <v>3093</v>
+        <v>16605</v>
       </c>
       <c r="I60" s="8">
-        <v>16167</v>
+        <v>26019</v>
       </c>
       <c r="J60" s="8">
-        <v>5000</v>
+        <v>43205</v>
       </c>
       <c r="K60" s="19">
-        <v>0</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" s="4">
-        <v>44257</v>
+        <v>44187</v>
       </c>
       <c r="B61" s="4">
-        <v>44260</v>
+        <v>44190</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>161</v>
@@ -61482,13 +63414,13 @@
         <v>160</v>
       </c>
       <c r="H61" s="8">
-        <v>2978</v>
+        <v>6447</v>
       </c>
       <c r="I61" s="8">
-        <v>16792</v>
+        <v>15511</v>
       </c>
       <c r="J61" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K61" s="19">
         <v>0</v>
@@ -61496,10 +63428,10 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62" s="4">
-        <v>44295</v>
+        <v>44224</v>
       </c>
       <c r="B62" s="4">
-        <v>44300</v>
+        <v>44229</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>161</v>
@@ -61517,10 +63449,10 @@
         <v>160</v>
       </c>
       <c r="H62" s="8">
-        <v>2810</v>
+        <v>3093</v>
       </c>
       <c r="I62" s="8">
-        <v>17792</v>
+        <v>16167</v>
       </c>
       <c r="J62" s="8">
         <v>5000</v>
@@ -61531,10 +63463,10 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B63" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>161</v>
@@ -61552,10 +63484,10 @@
         <v>160</v>
       </c>
       <c r="H63" s="8">
-        <v>2903</v>
+        <v>2978</v>
       </c>
       <c r="I63" s="8">
-        <v>17225</v>
+        <v>16792</v>
       </c>
       <c r="J63" s="8">
         <v>5000</v>
@@ -61566,10 +63498,10 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B64" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>161</v>
@@ -61587,10 +63519,10 @@
         <v>160</v>
       </c>
       <c r="H64" s="8">
-        <v>2819</v>
+        <v>2810</v>
       </c>
       <c r="I64" s="8">
-        <v>17736</v>
+        <v>17792</v>
       </c>
       <c r="J64" s="8">
         <v>5000</v>
@@ -61601,10 +63533,10 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A65" s="4">
-        <v>44362</v>
+        <v>44327</v>
       </c>
       <c r="B65" s="4">
-        <v>44365</v>
+        <v>44330</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>161</v>
@@ -61616,37 +63548,39 @@
         <v>295</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G65" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H65" s="8">
-        <v>21050</v>
+        <v>2903</v>
       </c>
       <c r="I65" s="8">
-        <v>18410</v>
+        <v>17225</v>
       </c>
       <c r="J65" s="8">
-        <v>38753</v>
+        <v>5000</v>
       </c>
       <c r="K65" s="19">
-        <v>3753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66" s="4">
-        <v>45243</v>
+        <v>44350</v>
       </c>
       <c r="B66" s="4">
-        <v>45247</v>
+        <v>44355</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>30</v>
@@ -61654,56 +63588,124 @@
       <c r="G66" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="H66" s="19">
-        <v>180143</v>
-      </c>
-      <c r="I66" s="19">
-        <v>12456</v>
+      <c r="H66" s="8">
+        <v>2819</v>
+      </c>
+      <c r="I66" s="8">
+        <v>17736</v>
       </c>
       <c r="J66" s="8">
-        <v>224386</v>
-      </c>
-      <c r="K66" s="21">
+        <v>5000</v>
+      </c>
+      <c r="K66" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67" s="4">
-        <v>45664</v>
+        <v>44362</v>
       </c>
       <c r="B67" s="4">
-        <v>45671</v>
+        <v>44365</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G67" s="5"/>
-      <c r="H67" s="21">
+      <c r="H67" s="8">
+        <v>21050</v>
+      </c>
+      <c r="I67" s="8">
+        <v>18410</v>
+      </c>
+      <c r="J67" s="8">
+        <v>38753</v>
+      </c>
+      <c r="K67" s="19">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A68" s="4">
+        <v>45243</v>
+      </c>
+      <c r="B68" s="4">
+        <v>45247</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H68" s="19">
         <v>180143</v>
       </c>
-      <c r="I67" s="21">
+      <c r="I68" s="19">
+        <v>12456</v>
+      </c>
+      <c r="J68" s="8">
+        <v>224386</v>
+      </c>
+      <c r="K68" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A69" s="4">
+        <v>45664</v>
+      </c>
+      <c r="B69" s="4">
+        <v>45671</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G69" s="5"/>
+      <c r="H69" s="21">
+        <v>180143</v>
+      </c>
+      <c r="I69" s="21">
         <v>15148</v>
       </c>
-      <c r="J67" s="21">
+      <c r="J69" s="21">
         <v>272881</v>
       </c>
-      <c r="K67" s="19">
+      <c r="K69" s="19">
         <v>48494</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K57" xr:uid="{00000000-0009-0000-0000-000007000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K67">
-      <sortCondition ref="C1:C57"/>
+  <autoFilter ref="A1:K59" xr:uid="{00000000-0009-0000-0000-000007000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K69">
+      <sortCondition ref="C1:C59"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18"/>

--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="477" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7287AF3-870A-4D9C-B4E9-B8D9DE6E7C43}"/>
+  <xr:revisionPtr revIDLastSave="492" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31AD0F31-64B9-4092-B2A8-44C16492410D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6868" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6929" uniqueCount="454">
   <si>
     <t>約定日</t>
   </si>
@@ -2978,7 +2978,7 @@
     <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>9647753</v>
+        <v>9651653</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
@@ -3419,15 +3419,15 @@
       </c>
       <c r="H4" s="20">
         <f>SUM(H5:H100)</f>
-        <v>820330</v>
+        <v>822090</v>
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>6309304</v>
+        <v>6314964</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>5027568.8923999993</v>
+        <v>5032079.0633999994</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -3463,11 +3463,11 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>8095241.1473499993</v>
+        <v>8099751.3183499994</v>
       </c>
       <c r="U4" s="56">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.3890410958904109</v>
+        <v>5.4164383561643836</v>
       </c>
       <c r="V4" s="56"/>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="F10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
-        <v>2001360</v>
+        <v>2005260</v>
       </c>
       <c r="G10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
@@ -3886,15 +3886,15 @@
       </c>
       <c r="H10" s="19">
         <f>SUMIFS(国内株式_特定_配当!$H$2:$H$999,国内株式_特定_配当!$A$2:$A$999,"&gt;=2026/1/1",国内株式_特定_配当!$A$2:$A$999,"&lt;=2026/12/31")</f>
-        <v>18175</v>
+        <v>19935</v>
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>1286055</v>
+        <v>1291715</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>1024792.92675</v>
+        <v>1029303.09775</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>1237245.64325</v>
+        <v>1241755.8142500001</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -12291,7 +12291,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O872"/>
+  <dimension ref="A1:O883"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -51483,7 +51483,7 @@
       <c r="H871" s="5">
         <v>400</v>
       </c>
-      <c r="I871" s="72">
+      <c r="I871" s="7">
         <v>3693</v>
       </c>
       <c r="J871" s="9">
@@ -51525,7 +51525,7 @@
       <c r="H872" s="5">
         <v>400</v>
       </c>
-      <c r="I872" s="72">
+      <c r="I872" s="7">
         <v>1462.2</v>
       </c>
       <c r="J872" s="9">
@@ -51541,6 +51541,501 @@
         <v>0</v>
       </c>
       <c r="N872" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A873" s="4">
+        <v>46118</v>
+      </c>
+      <c r="B873" s="4">
+        <v>46120</v>
+      </c>
+      <c r="C873" s="5">
+        <v>1540</v>
+      </c>
+      <c r="D873" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="E873" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F873" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G873" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H873" s="5">
+        <v>5</v>
+      </c>
+      <c r="I873" s="7">
+        <v>22244</v>
+      </c>
+      <c r="J873" s="9">
+        <v>0</v>
+      </c>
+      <c r="K873" s="9">
+        <v>0</v>
+      </c>
+      <c r="L873" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M873" s="15">
+        <f t="shared" ref="M873:M883" si="20">IF(G873="買付",H873*I873+SUM(J873:K873),H873*I873-SUM(J873:K873))</f>
+        <v>111220</v>
+      </c>
+      <c r="N873" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A874" s="4">
+        <v>46118</v>
+      </c>
+      <c r="B874" s="4">
+        <v>46120</v>
+      </c>
+      <c r="C874" s="5">
+        <v>2802</v>
+      </c>
+      <c r="D874" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="E874" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F874" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G874" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H874" s="5">
+        <v>100</v>
+      </c>
+      <c r="I874" s="7">
+        <v>4677</v>
+      </c>
+      <c r="J874" s="9">
+        <v>0</v>
+      </c>
+      <c r="K874" s="9">
+        <v>0</v>
+      </c>
+      <c r="L874" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M874" s="15">
+        <f t="shared" si="20"/>
+        <v>467700</v>
+      </c>
+      <c r="N874" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A875" s="4">
+        <v>46118</v>
+      </c>
+      <c r="B875" s="4">
+        <v>46120</v>
+      </c>
+      <c r="C875" s="5">
+        <v>4063</v>
+      </c>
+      <c r="D875" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E875" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F875" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G875" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H875" s="5">
+        <v>100</v>
+      </c>
+      <c r="I875" s="7">
+        <v>6585</v>
+      </c>
+      <c r="J875" s="9">
+        <v>0</v>
+      </c>
+      <c r="K875" s="9">
+        <v>0</v>
+      </c>
+      <c r="L875" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M875" s="15">
+        <f t="shared" si="20"/>
+        <v>658500</v>
+      </c>
+      <c r="N875" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A876" s="4">
+        <v>46120</v>
+      </c>
+      <c r="B876" s="4">
+        <v>46122</v>
+      </c>
+      <c r="C876" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D876" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E876" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F876" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G876" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H876" s="5">
+        <v>100</v>
+      </c>
+      <c r="I876" s="7">
+        <v>1180</v>
+      </c>
+      <c r="J876" s="9">
+        <v>0</v>
+      </c>
+      <c r="K876" s="9">
+        <v>0</v>
+      </c>
+      <c r="L876" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M876" s="15">
+        <f t="shared" si="20"/>
+        <v>118000</v>
+      </c>
+      <c r="N876" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A877" s="4">
+        <v>46120</v>
+      </c>
+      <c r="B877" s="4">
+        <v>46122</v>
+      </c>
+      <c r="C877" s="5">
+        <v>5803</v>
+      </c>
+      <c r="D877" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E877" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F877" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G877" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H877" s="5">
+        <v>100</v>
+      </c>
+      <c r="I877" s="7">
+        <v>4829.2</v>
+      </c>
+      <c r="J877" s="9">
+        <v>0</v>
+      </c>
+      <c r="K877" s="9">
+        <v>0</v>
+      </c>
+      <c r="L877" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M877" s="15">
+        <f t="shared" si="20"/>
+        <v>482920</v>
+      </c>
+      <c r="N877" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A878" s="4">
+        <v>46120</v>
+      </c>
+      <c r="B878" s="4">
+        <v>46122</v>
+      </c>
+      <c r="C878" s="5">
+        <v>7721</v>
+      </c>
+      <c r="D878" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="E878" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F878" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G878" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H878" s="5">
+        <v>100</v>
+      </c>
+      <c r="I878" s="7">
+        <v>7960</v>
+      </c>
+      <c r="J878" s="9">
+        <v>0</v>
+      </c>
+      <c r="K878" s="9">
+        <v>0</v>
+      </c>
+      <c r="L878" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M878" s="15">
+        <f t="shared" si="20"/>
+        <v>796000</v>
+      </c>
+      <c r="N878" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A879" s="4">
+        <v>46121</v>
+      </c>
+      <c r="B879" s="4">
+        <v>46125</v>
+      </c>
+      <c r="C879" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D879" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E879" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F879" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G879" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H879" s="5">
+        <v>300</v>
+      </c>
+      <c r="I879" s="7">
+        <v>1221</v>
+      </c>
+      <c r="J879" s="9">
+        <v>0</v>
+      </c>
+      <c r="K879" s="9">
+        <v>0</v>
+      </c>
+      <c r="L879" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M879" s="15">
+        <f t="shared" si="20"/>
+        <v>366300</v>
+      </c>
+      <c r="N879" s="19">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="880" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A880" s="4">
+        <v>46121</v>
+      </c>
+      <c r="B880" s="4">
+        <v>46125</v>
+      </c>
+      <c r="C880" s="5">
+        <v>2802</v>
+      </c>
+      <c r="D880" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="E880" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F880" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G880" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H880" s="5">
+        <v>100</v>
+      </c>
+      <c r="I880" s="7">
+        <v>4715</v>
+      </c>
+      <c r="J880" s="9">
+        <v>0</v>
+      </c>
+      <c r="K880" s="9">
+        <v>0</v>
+      </c>
+      <c r="L880" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M880" s="15">
+        <f t="shared" si="20"/>
+        <v>471500</v>
+      </c>
+      <c r="N880" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A881" s="4">
+        <v>46121</v>
+      </c>
+      <c r="B881" s="4">
+        <v>46125</v>
+      </c>
+      <c r="C881" s="5">
+        <v>5803</v>
+      </c>
+      <c r="D881" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E881" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F881" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G881" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H881" s="5">
+        <v>100</v>
+      </c>
+      <c r="I881" s="7">
+        <v>5021</v>
+      </c>
+      <c r="J881" s="9">
+        <v>0</v>
+      </c>
+      <c r="K881" s="9">
+        <v>0</v>
+      </c>
+      <c r="L881" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M881" s="15">
+        <f t="shared" si="20"/>
+        <v>502100</v>
+      </c>
+      <c r="N881" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A882" s="4">
+        <v>46122</v>
+      </c>
+      <c r="B882" s="4">
+        <v>46126</v>
+      </c>
+      <c r="C882" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D882" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E882" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F882" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G882" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H882" s="5">
+        <v>100</v>
+      </c>
+      <c r="I882" s="7">
+        <v>1344.4</v>
+      </c>
+      <c r="J882" s="9">
+        <v>0</v>
+      </c>
+      <c r="K882" s="9">
+        <v>0</v>
+      </c>
+      <c r="L882" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M882" s="15">
+        <f t="shared" si="20"/>
+        <v>134440</v>
+      </c>
+      <c r="N882" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A883" s="4">
+        <v>46122</v>
+      </c>
+      <c r="B883" s="4">
+        <v>46126</v>
+      </c>
+      <c r="C883" s="5">
+        <v>6590</v>
+      </c>
+      <c r="D883" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="E883" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F883" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G883" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H883" s="5">
+        <v>100</v>
+      </c>
+      <c r="I883" s="7">
+        <v>4810</v>
+      </c>
+      <c r="J883" s="9">
+        <v>0</v>
+      </c>
+      <c r="K883" s="9">
+        <v>0</v>
+      </c>
+      <c r="L883" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M883" s="15">
+        <f t="shared" si="20"/>
+        <v>481000</v>
+      </c>
+      <c r="N883" s="19">
         <v>0</v>
       </c>
     </row>
@@ -51561,7 +52056,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -54607,11 +55102,11 @@
         <v>1218</v>
       </c>
       <c r="J80" s="19">
-        <f t="shared" ref="J80:J88" si="16">H80-I80</f>
+        <f t="shared" ref="J80:J89" si="16">H80-I80</f>
         <v>4782</v>
       </c>
       <c r="K80" s="19">
-        <f t="shared" ref="K80:K88" si="17">J80</f>
+        <f t="shared" ref="K80:K89" si="17">J80</f>
         <v>4782</v>
       </c>
     </row>
@@ -54866,7 +55361,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="19">
-        <f t="shared" ref="H87:H88" si="18">F87*G87</f>
+        <f t="shared" ref="H87:H89" si="18">F87*G87</f>
         <v>8000</v>
       </c>
       <c r="I87" s="19">
@@ -54917,6 +55412,44 @@
       <c r="K88" s="19">
         <f t="shared" si="17"/>
         <v>6694</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A89" s="4">
+        <v>46122</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" s="5">
+        <v>1488</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="F89" s="72">
+        <v>32</v>
+      </c>
+      <c r="G89" s="5">
+        <v>55</v>
+      </c>
+      <c r="H89" s="19">
+        <f t="shared" si="18"/>
+        <v>1760</v>
+      </c>
+      <c r="I89" s="19">
+        <v>357</v>
+      </c>
+      <c r="J89" s="19">
+        <f t="shared" si="16"/>
+        <v>1403</v>
+      </c>
+      <c r="K89" s="19">
+        <f t="shared" si="17"/>
+        <v>1403</v>
       </c>
     </row>
   </sheetData>

--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="492" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31AD0F31-64B9-4092-B2A8-44C16492410D}"/>
+  <xr:revisionPtr revIDLastSave="524" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A433DA7-AE71-4509-ACBD-FACE29DA9E11}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">国内株式_信用!$A$1:$AA$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">国内株式_特定!$A$1:$N$852</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">国内株式_特定_配当!$A$1:$K$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">投資信託!$A$1:$K$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">投資信託!$A$1:$K$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">米国株式!$A$1:$S$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">米国株式_配当!$A$1:$K$74</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6929" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6985" uniqueCount="455">
   <si>
     <t>約定日</t>
   </si>
@@ -2041,6 +2041,9 @@
     <t>-</t>
     <phoneticPr fontId="18"/>
   </si>
+  <si>
+    <t>ハーモニック・ドライブ・シス</t>
+  </si>
 </sst>
 </file>
 
@@ -2927,16 +2930,22 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2960,12 +2969,6 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2978,7 +2981,7 @@
     <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3259,31 +3262,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="59" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>216</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55" t="s">
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59" t="s">
         <v>218</v>
       </c>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="63" t="s">
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="65" t="s">
         <v>302</v>
       </c>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="65"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="67"/>
       <c r="S1" s="37" t="s">
         <v>219</v>
       </c>
@@ -3295,50 +3298,50 @@
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57" t="s">
+      <c r="C2" s="55"/>
+      <c r="D2" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57" t="s">
+      <c r="G2" s="55"/>
+      <c r="H2" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="L2" s="57"/>
-      <c r="M2" s="58" t="s">
+      <c r="L2" s="55"/>
+      <c r="M2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="O2" s="61" t="s">
+      <c r="O2" s="63" t="s">
         <v>212</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="58" t="s">
+      <c r="P2" s="64"/>
+      <c r="Q2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="R2" s="60" t="s">
+      <c r="R2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="S2" s="59" t="s">
+      <c r="S2" s="61" t="s">
         <v>214</v>
       </c>
       <c r="U2" s="49">
@@ -3346,7 +3349,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3356,38 +3359,38 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="57"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
       <c r="K3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
       <c r="O3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="P3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="59"/>
-      <c r="U3" s="55" t="s">
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="61"/>
+      <c r="U3" s="59" t="s">
         <v>363</v>
       </c>
-      <c r="V3" s="55"/>
+      <c r="V3" s="59"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="34" t="s">
@@ -3411,7 +3414,7 @@
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>9651653</v>
+        <v>10017693</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
@@ -3423,11 +3426,11 @@
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>6314964</v>
+        <v>6681004</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>5032079.0633999994</v>
+        <v>5323758.0373999998</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -3463,13 +3466,13 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>8099751.3183499994</v>
-      </c>
-      <c r="U4" s="56">
+        <v>8391430.2923499998</v>
+      </c>
+      <c r="U4" s="60">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.4164383561643836</v>
-      </c>
-      <c r="V4" s="56"/>
+        <v>5.441095890410959</v>
+      </c>
+      <c r="V4" s="60"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="34" t="s">
@@ -3528,11 +3531,11 @@
         <v>-68778</v>
       </c>
       <c r="O5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2021/1/1",投資信託!$B$2:$B$1027,"&lt;=2021/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2021/1/1",投資信託!$B$2:$B$1029,"&lt;=2021/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
         <v>7366</v>
       </c>
       <c r="P5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2021/1/1",投資信託!$B$2:$B$1027,"&lt;=2021/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2021/1/1",投資信託!$B$2:$B$1029,"&lt;=2021/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
         <v>-1498</v>
       </c>
       <c r="Q5" s="35">
@@ -3605,11 +3608,11 @@
         <v>-106573</v>
       </c>
       <c r="O6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2022/1/1",投資信託!$B$2:$B$1027,"&lt;=2022/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2022/1/1",投資信託!$B$2:$B$1029,"&lt;=2022/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2022/1/1",投資信託!$B$2:$B$1027,"&lt;=2022/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2022/1/1",投資信託!$B$2:$B$1029,"&lt;=2022/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q6" s="35">
@@ -3682,11 +3685,11 @@
         <v>-50703</v>
       </c>
       <c r="O7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2023/1/1",投資信託!$B$2:$B$1027,"&lt;=2023/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2023/1/1",投資信託!$B$2:$B$1029,"&lt;=2023/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2023/1/1",投資信託!$B$2:$B$1027,"&lt;=2023/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2023/1/1",投資信託!$B$2:$B$1029,"&lt;=2023/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q7" s="35">
@@ -3759,11 +3762,11 @@
         <v>-247960</v>
       </c>
       <c r="O8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2024/1/1",投資信託!$B$2:$B$1027,"&lt;=2024/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2024/1/1",投資信託!$B$2:$B$1029,"&lt;=2024/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2024/1/1",投資信託!$B$2:$B$1027,"&lt;=2024/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2024/1/1",投資信託!$B$2:$B$1029,"&lt;=2024/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q8" s="35">
@@ -3836,11 +3839,11 @@
         <v>8063.3251500000006</v>
       </c>
       <c r="O9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2025/1/1",投資信託!$B$2:$B$1027,"&lt;=2025/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2025/1/1",投資信託!$B$2:$B$1029,"&lt;=2025/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
         <v>185421</v>
       </c>
       <c r="P9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2025/1/1",投資信託!$B$2:$B$1027,"&lt;=2025/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2025/1/1",投資信託!$B$2:$B$1029,"&lt;=2025/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
         <v>-1071</v>
       </c>
       <c r="Q9" s="35">
@@ -3878,7 +3881,7 @@
       </c>
       <c r="F10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
-        <v>2005260</v>
+        <v>2371300</v>
       </c>
       <c r="G10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
@@ -3890,11 +3893,11 @@
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>1291715</v>
+        <v>1657755</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>1029303.09775</v>
+        <v>1320982.0717500001</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -3913,11 +3916,11 @@
         <v>207252.71650000001</v>
       </c>
       <c r="O10" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2026/1/1",投資信託!$B$2:$B$1027,"&lt;=2026/12/31",投資信託!$K$2:$K$1027,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2026/1/1",投資信託!$B$2:$B$1029,"&lt;=2026/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P10" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1027,投資信託!$B$2:$B$1027,"&gt;=2026/1/1",投資信託!$B$2:$B$1027,"&lt;=2026/12/31",投資信託!$K$2:$K$1027,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2026/1/1",投資信託!$B$2:$B$1029,"&lt;=2026/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="35">
@@ -3930,7 +3933,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>1241755.8142500001</v>
+        <v>1533434.7882500002</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -3944,11 +3947,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F2:G2"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="H2:H3"/>
@@ -3964,6 +3962,11 @@
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6753,49 +6756,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>416</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
       <c r="K1" s="69" t="s">
         <v>219</v>
       </c>
       <c r="L1" s="69"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="57"/>
+      <c r="C2" s="55"/>
       <c r="D2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="57"/>
+      <c r="G2" s="55"/>
       <c r="H2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="59" t="s">
+      <c r="K2" s="61" t="s">
         <v>214</v>
       </c>
       <c r="L2" s="70" t="s">
@@ -6809,18 +6812,18 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="61"/>
       <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -12291,7 +12294,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O883"/>
+  <dimension ref="A1:O892"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -51582,7 +51585,7 @@
         <v>31</v>
       </c>
       <c r="M873" s="15">
-        <f t="shared" ref="M873:M883" si="20">IF(G873="買付",H873*I873+SUM(J873:K873),H873*I873-SUM(J873:K873))</f>
+        <f t="shared" ref="M873:M892" si="20">IF(G873="買付",H873*I873+SUM(J873:K873),H873*I873-SUM(J873:K873))</f>
         <v>111220</v>
       </c>
       <c r="N873" s="19">
@@ -52037,6 +52040,412 @@
       </c>
       <c r="N883" s="19">
         <v>0</v>
+      </c>
+    </row>
+    <row r="884" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A884" s="4">
+        <v>46125</v>
+      </c>
+      <c r="B884" s="4">
+        <v>46127</v>
+      </c>
+      <c r="C884" s="5">
+        <v>4063</v>
+      </c>
+      <c r="D884" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E884" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F884" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G884" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H884" s="5">
+        <v>100</v>
+      </c>
+      <c r="I884" s="7">
+        <v>6592</v>
+      </c>
+      <c r="J884" s="9">
+        <v>0</v>
+      </c>
+      <c r="K884" s="9">
+        <v>0</v>
+      </c>
+      <c r="L884" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M884" s="15">
+        <f t="shared" si="20"/>
+        <v>659200</v>
+      </c>
+      <c r="N884" s="19">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="885" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A885" s="4">
+        <v>46125</v>
+      </c>
+      <c r="B885" s="4">
+        <v>46127</v>
+      </c>
+      <c r="C885" s="5">
+        <v>5016</v>
+      </c>
+      <c r="D885" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E885" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F885" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G885" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H885" s="5">
+        <v>100</v>
+      </c>
+      <c r="I885" s="7">
+        <v>4560</v>
+      </c>
+      <c r="J885" s="9">
+        <v>0</v>
+      </c>
+      <c r="K885" s="9">
+        <v>0</v>
+      </c>
+      <c r="L885" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M885" s="15">
+        <f t="shared" si="20"/>
+        <v>456000</v>
+      </c>
+      <c r="N885" s="19">
+        <v>23400</v>
+      </c>
+    </row>
+    <row r="886" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A886" s="4">
+        <v>46125</v>
+      </c>
+      <c r="B886" s="4">
+        <v>46127</v>
+      </c>
+      <c r="C886" s="5">
+        <v>5803</v>
+      </c>
+      <c r="D886" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E886" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F886" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G886" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H886" s="5">
+        <v>200</v>
+      </c>
+      <c r="I886" s="7">
+        <v>5761.2</v>
+      </c>
+      <c r="J886" s="9">
+        <v>0</v>
+      </c>
+      <c r="K886" s="9">
+        <v>0</v>
+      </c>
+      <c r="L886" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M886" s="15">
+        <f t="shared" si="20"/>
+        <v>1152240</v>
+      </c>
+      <c r="N886" s="19">
+        <f>83520*2</f>
+        <v>167040</v>
+      </c>
+    </row>
+    <row r="887" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A887" s="4">
+        <v>46125</v>
+      </c>
+      <c r="B887" s="4">
+        <v>46127</v>
+      </c>
+      <c r="C887" s="5">
+        <v>8766</v>
+      </c>
+      <c r="D887" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E887" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F887" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G887" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H887" s="5">
+        <v>100</v>
+      </c>
+      <c r="I887" s="7">
+        <v>7044</v>
+      </c>
+      <c r="J887" s="9">
+        <v>0</v>
+      </c>
+      <c r="K887" s="9">
+        <v>0</v>
+      </c>
+      <c r="L887" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M887" s="15">
+        <f t="shared" si="20"/>
+        <v>704400</v>
+      </c>
+      <c r="N887" s="19">
+        <v>97700</v>
+      </c>
+    </row>
+    <row r="888" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A888" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B888" s="4">
+        <v>46129</v>
+      </c>
+      <c r="C888" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D888" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E888" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F888" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G888" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H888" s="5">
+        <v>100</v>
+      </c>
+      <c r="I888" s="7">
+        <v>1352</v>
+      </c>
+      <c r="J888" s="9">
+        <v>0</v>
+      </c>
+      <c r="K888" s="9">
+        <v>0</v>
+      </c>
+      <c r="L888" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M888" s="15">
+        <f t="shared" si="20"/>
+        <v>135200</v>
+      </c>
+      <c r="N888" s="19">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="889" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A889" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B889" s="4">
+        <v>46129</v>
+      </c>
+      <c r="C889" s="5">
+        <v>6324</v>
+      </c>
+      <c r="D889" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E889" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F889" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G889" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H889" s="5">
+        <v>100</v>
+      </c>
+      <c r="I889" s="7">
+        <v>4380</v>
+      </c>
+      <c r="J889" s="9">
+        <v>0</v>
+      </c>
+      <c r="K889" s="9">
+        <v>0</v>
+      </c>
+      <c r="L889" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M889" s="15">
+        <f t="shared" si="20"/>
+        <v>438000</v>
+      </c>
+      <c r="N889" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A890" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B890" s="4">
+        <v>46129</v>
+      </c>
+      <c r="C890" s="5">
+        <v>8316</v>
+      </c>
+      <c r="D890" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E890" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F890" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G890" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H890" s="5">
+        <v>100</v>
+      </c>
+      <c r="I890" s="7">
+        <v>5653</v>
+      </c>
+      <c r="J890" s="9">
+        <v>0</v>
+      </c>
+      <c r="K890" s="9">
+        <v>0</v>
+      </c>
+      <c r="L890" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M890" s="15">
+        <f t="shared" si="20"/>
+        <v>565300</v>
+      </c>
+      <c r="N890" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="891" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A891" s="4">
+        <v>46128</v>
+      </c>
+      <c r="B891" s="4">
+        <v>46132</v>
+      </c>
+      <c r="C891" s="5">
+        <v>6590</v>
+      </c>
+      <c r="D891" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="E891" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F891" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G891" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H891" s="5">
+        <v>100</v>
+      </c>
+      <c r="I891" s="7">
+        <v>5410</v>
+      </c>
+      <c r="J891" s="9">
+        <v>0</v>
+      </c>
+      <c r="K891" s="9">
+        <v>0</v>
+      </c>
+      <c r="L891" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M891" s="15">
+        <f t="shared" si="20"/>
+        <v>541000</v>
+      </c>
+      <c r="N891" s="19">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="892" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A892" s="4">
+        <v>46129</v>
+      </c>
+      <c r="B892" s="4">
+        <v>46133</v>
+      </c>
+      <c r="C892" s="5">
+        <v>6324</v>
+      </c>
+      <c r="D892" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E892" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F892" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G892" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H892" s="5">
+        <v>100</v>
+      </c>
+      <c r="I892" s="72">
+        <v>4545</v>
+      </c>
+      <c r="J892" s="9">
+        <v>0</v>
+      </c>
+      <c r="K892" s="9">
+        <v>0</v>
+      </c>
+      <c r="L892" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M892" s="15">
+        <f t="shared" si="20"/>
+        <v>454500</v>
+      </c>
+      <c r="N892" s="19">
+        <v>16500</v>
       </c>
     </row>
   </sheetData>
@@ -55430,7 +55839,7 @@
       <c r="E89" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="F89" s="72">
+      <c r="F89" s="9">
         <v>32</v>
       </c>
       <c r="G89" s="5">
@@ -61832,7 +62241,7 @@
   <sheetPr>
     <tabColor theme="2"/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -62756,13 +63165,13 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" s="4">
-        <v>45945</v>
+        <v>46126</v>
       </c>
       <c r="B27" s="4">
-        <v>45950</v>
+        <v>46132</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>377</v>
+        <v>282</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>159</v>
@@ -62777,13 +63186,13 @@
         <v>284</v>
       </c>
       <c r="H27" s="21">
-        <v>40242</v>
+        <v>8622</v>
       </c>
       <c r="I27" s="21">
-        <v>17395</v>
+        <v>34796</v>
       </c>
       <c r="J27" s="21">
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="K27" s="21">
         <v>0</v>
@@ -62791,10 +63200,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" s="4">
-        <v>45974</v>
+        <v>46128</v>
       </c>
       <c r="B28" s="4">
-        <v>45979</v>
+        <v>45950</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>377</v>
@@ -62812,10 +63221,10 @@
         <v>284</v>
       </c>
       <c r="H28" s="21">
-        <v>38038</v>
+        <v>40242</v>
       </c>
       <c r="I28" s="21">
-        <v>18403</v>
+        <v>17395</v>
       </c>
       <c r="J28" s="21">
         <v>70000</v>
@@ -62826,10 +63235,10 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" s="4">
-        <v>46006</v>
+        <v>45974</v>
       </c>
       <c r="B29" s="4">
-        <v>46009</v>
+        <v>45979</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>377</v>
@@ -62847,10 +63256,10 @@
         <v>284</v>
       </c>
       <c r="H29" s="21">
-        <v>37910</v>
+        <v>38038</v>
       </c>
       <c r="I29" s="21">
-        <v>18465</v>
+        <v>18403</v>
       </c>
       <c r="J29" s="21">
         <v>70000</v>
@@ -62861,10 +63270,10 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" s="4">
-        <v>46036</v>
+        <v>46006</v>
       </c>
       <c r="B30" s="4">
-        <v>46041</v>
+        <v>46009</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>377</v>
@@ -62882,10 +63291,10 @@
         <v>284</v>
       </c>
       <c r="H30" s="21">
-        <v>35338</v>
+        <v>37910</v>
       </c>
       <c r="I30" s="21">
-        <v>19809</v>
+        <v>18465</v>
       </c>
       <c r="J30" s="21">
         <v>70000</v>
@@ -62896,10 +63305,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" s="4">
-        <v>46066</v>
+        <v>46036</v>
       </c>
       <c r="B31" s="4">
-        <v>46071</v>
+        <v>46041</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>377</v>
@@ -62917,10 +63326,10 @@
         <v>284</v>
       </c>
       <c r="H31" s="21">
-        <v>34978</v>
+        <v>35338</v>
       </c>
       <c r="I31" s="21">
-        <v>20013</v>
+        <v>19809</v>
       </c>
       <c r="J31" s="21">
         <v>70000</v>
@@ -62931,10 +63340,10 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" s="4">
-        <v>46094</v>
+        <v>46066</v>
       </c>
       <c r="B32" s="4">
-        <v>46099</v>
+        <v>46071</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>377</v>
@@ -62952,10 +63361,10 @@
         <v>284</v>
       </c>
       <c r="H32" s="21">
-        <v>35624</v>
+        <v>34978</v>
       </c>
       <c r="I32" s="21">
-        <v>19650</v>
+        <v>20013</v>
       </c>
       <c r="J32" s="21">
         <v>70000</v>
@@ -62966,34 +63375,34 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="4">
-        <v>44368</v>
+        <v>46094</v>
       </c>
       <c r="B33" s="4">
-        <v>44371</v>
+        <v>46099</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>163</v>
+        <v>377</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H33" s="8">
-        <v>21735</v>
-      </c>
-      <c r="I33" s="8">
-        <v>13803</v>
-      </c>
-      <c r="J33" s="8">
-        <v>30000</v>
+        <v>284</v>
+      </c>
+      <c r="H33" s="21">
+        <v>35624</v>
+      </c>
+      <c r="I33" s="21">
+        <v>19650</v>
+      </c>
+      <c r="J33" s="21">
+        <v>70000</v>
       </c>
       <c r="K33" s="21">
         <v>0</v>
@@ -63001,34 +63410,34 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="4">
-        <v>44377</v>
+        <v>46126</v>
       </c>
       <c r="B34" s="4">
-        <v>44382</v>
+        <v>46129</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>163</v>
+        <v>377</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H34" s="8">
-        <v>7034</v>
-      </c>
-      <c r="I34" s="8">
-        <v>14217</v>
-      </c>
-      <c r="J34" s="8">
-        <v>10000</v>
+        <v>284</v>
+      </c>
+      <c r="H34" s="21">
+        <v>33669</v>
+      </c>
+      <c r="I34" s="21">
+        <v>20791</v>
+      </c>
+      <c r="J34" s="21">
+        <v>70000</v>
       </c>
       <c r="K34" s="21">
         <v>0</v>
@@ -63036,10 +63445,10 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="4">
-        <v>44529</v>
+        <v>44368</v>
       </c>
       <c r="B35" s="4">
-        <v>44532</v>
+        <v>44371</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>163</v>
@@ -63051,28 +63460,30 @@
         <v>295</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G35" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H35" s="8">
-        <v>28769</v>
+        <v>21735</v>
       </c>
       <c r="I35" s="8">
-        <v>13383</v>
+        <v>13803</v>
       </c>
       <c r="J35" s="8">
-        <v>38502</v>
-      </c>
-      <c r="K35" s="19">
-        <v>-1498</v>
+        <v>30000</v>
+      </c>
+      <c r="K35" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="4">
-        <v>44403</v>
+        <v>44377</v>
       </c>
       <c r="B36" s="4">
-        <v>44406</v>
+        <v>44382</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>163</v>
@@ -63081,7 +63492,7 @@
         <v>159</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>30</v>
@@ -63090,10 +63501,10 @@
         <v>160</v>
       </c>
       <c r="H36" s="8">
-        <v>7310</v>
+        <v>7034</v>
       </c>
       <c r="I36" s="8">
-        <v>13681</v>
+        <v>14217</v>
       </c>
       <c r="J36" s="8">
         <v>10000</v>
@@ -63104,10 +63515,10 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="4">
-        <v>44525</v>
+        <v>44529</v>
       </c>
       <c r="B37" s="4">
-        <v>44530</v>
+        <v>44532</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>163</v>
@@ -63116,40 +63527,40 @@
         <v>159</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="8">
-        <v>7310</v>
+        <v>28769</v>
       </c>
       <c r="I37" s="8">
-        <v>13973</v>
+        <v>13383</v>
       </c>
       <c r="J37" s="8">
-        <v>10214</v>
+        <v>38502</v>
       </c>
       <c r="K37" s="19">
-        <v>214</v>
+        <v>-1498</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="4">
-        <v>44165</v>
+        <v>44403</v>
       </c>
       <c r="B38" s="4">
-        <v>44168</v>
+        <v>44406</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>295</v>
+        <v>67</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>30</v>
@@ -63158,13 +63569,13 @@
         <v>160</v>
       </c>
       <c r="H38" s="8">
-        <v>3846</v>
+        <v>7310</v>
       </c>
       <c r="I38" s="8">
-        <v>13000</v>
+        <v>13681</v>
       </c>
       <c r="J38" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K38" s="21">
         <v>0</v>
@@ -63172,45 +63583,43 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="4">
-        <v>44201</v>
+        <v>44525</v>
       </c>
       <c r="B39" s="4">
-        <v>44204</v>
+        <v>44530</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>295</v>
+        <v>67</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="G39" s="5"/>
       <c r="H39" s="8">
-        <v>7604</v>
+        <v>7310</v>
       </c>
       <c r="I39" s="8">
-        <v>13152</v>
+        <v>13973</v>
       </c>
       <c r="J39" s="8">
-        <v>10000</v>
-      </c>
-      <c r="K39" s="21">
-        <v>0</v>
+        <v>10214</v>
+      </c>
+      <c r="K39" s="19">
+        <v>214</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="4">
-        <v>44236</v>
+        <v>44165</v>
       </c>
       <c r="B40" s="4">
-        <v>44242</v>
+        <v>44168</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>158</v>
@@ -63228,13 +63637,13 @@
         <v>160</v>
       </c>
       <c r="H40" s="8">
-        <v>7041</v>
+        <v>3846</v>
       </c>
       <c r="I40" s="8">
-        <v>14202</v>
+        <v>13000</v>
       </c>
       <c r="J40" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K40" s="21">
         <v>0</v>
@@ -63242,10 +63651,10 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="4">
-        <v>44257</v>
+        <v>44201</v>
       </c>
       <c r="B41" s="4">
-        <v>44260</v>
+        <v>44204</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>158</v>
@@ -63263,10 +63672,10 @@
         <v>160</v>
       </c>
       <c r="H41" s="8">
-        <v>6947</v>
+        <v>7604</v>
       </c>
       <c r="I41" s="8">
-        <v>14394</v>
+        <v>13152</v>
       </c>
       <c r="J41" s="8">
         <v>10000</v>
@@ -63277,10 +63686,10 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="4">
-        <v>44295</v>
+        <v>44236</v>
       </c>
       <c r="B42" s="4">
-        <v>44300</v>
+        <v>44242</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>158</v>
@@ -63298,10 +63707,10 @@
         <v>160</v>
       </c>
       <c r="H42" s="8">
-        <v>6460</v>
+        <v>7041</v>
       </c>
       <c r="I42" s="8">
-        <v>15481</v>
+        <v>14202</v>
       </c>
       <c r="J42" s="8">
         <v>10000</v>
@@ -63312,10 +63721,10 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B43" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>158</v>
@@ -63333,13 +63742,13 @@
         <v>160</v>
       </c>
       <c r="H43" s="8">
-        <v>3167</v>
+        <v>6947</v>
       </c>
       <c r="I43" s="8">
-        <v>15789</v>
+        <v>14394</v>
       </c>
       <c r="J43" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K43" s="21">
         <v>0</v>
@@ -63347,10 +63756,10 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B44" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>158</v>
@@ -63368,10 +63777,10 @@
         <v>160</v>
       </c>
       <c r="H44" s="8">
-        <v>6263</v>
+        <v>6460</v>
       </c>
       <c r="I44" s="8">
-        <v>15967</v>
+        <v>15481</v>
       </c>
       <c r="J44" s="8">
         <v>10000</v>
@@ -63382,10 +63791,10 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" s="4">
-        <v>44377</v>
+        <v>44327</v>
       </c>
       <c r="B45" s="4">
-        <v>44382</v>
+        <v>44330</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>158</v>
@@ -63403,13 +63812,13 @@
         <v>160</v>
       </c>
       <c r="H45" s="8">
-        <v>6081</v>
+        <v>3167</v>
       </c>
       <c r="I45" s="8">
-        <v>16444</v>
+        <v>15789</v>
       </c>
       <c r="J45" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K45" s="21">
         <v>0</v>
@@ -63417,10 +63826,10 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="4">
-        <v>44921</v>
+        <v>44350</v>
       </c>
       <c r="B46" s="4">
-        <v>44924</v>
+        <v>44355</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>158</v>
@@ -63438,13 +63847,13 @@
         <v>160</v>
       </c>
       <c r="H46" s="8">
-        <v>24940</v>
+        <v>6263</v>
       </c>
       <c r="I46" s="8">
-        <v>17961</v>
+        <v>15967</v>
       </c>
       <c r="J46" s="8">
-        <v>44794</v>
+        <v>10000</v>
       </c>
       <c r="K46" s="21">
         <v>0</v>
@@ -63452,10 +63861,10 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" s="4">
-        <v>45243</v>
+        <v>44377</v>
       </c>
       <c r="B47" s="4">
-        <v>45246</v>
+        <v>44382</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>158</v>
@@ -63473,13 +63882,13 @@
         <v>160</v>
       </c>
       <c r="H47" s="8">
-        <v>590</v>
+        <v>6081</v>
       </c>
       <c r="I47" s="8">
-        <v>23925</v>
+        <v>16444</v>
       </c>
       <c r="J47" s="8">
-        <v>1410</v>
+        <v>10000</v>
       </c>
       <c r="K47" s="21">
         <v>0</v>
@@ -63487,10 +63896,10 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="4">
-        <v>45656</v>
+        <v>44921</v>
       </c>
       <c r="B48" s="4">
-        <v>45663</v>
+        <v>44924</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>158</v>
@@ -63502,15 +63911,19 @@
         <v>295</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I48" s="9"/>
-      <c r="J48" s="9">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H48" s="8">
+        <v>24940</v>
+      </c>
+      <c r="I48" s="8">
+        <v>17961</v>
+      </c>
+      <c r="J48" s="8">
+        <v>44794</v>
       </c>
       <c r="K48" s="21">
         <v>0</v>
@@ -63518,10 +63931,10 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" s="4">
-        <v>45772</v>
+        <v>45243</v>
       </c>
       <c r="B49" s="4">
-        <v>45778</v>
+        <v>45246</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>158</v>
@@ -63533,28 +63946,30 @@
         <v>295</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="21">
-        <v>69093</v>
-      </c>
-      <c r="I49" s="19">
-        <v>28502</v>
-      </c>
-      <c r="J49" s="19">
-        <v>196929</v>
+        <v>30</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H49" s="8">
+        <v>590</v>
+      </c>
+      <c r="I49" s="8">
+        <v>23925</v>
+      </c>
+      <c r="J49" s="8">
+        <v>1410</v>
       </c>
       <c r="K49" s="21">
-        <v>86850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" s="4">
-        <v>44404</v>
+        <v>45656</v>
       </c>
       <c r="B50" s="4">
-        <v>44407</v>
+        <v>45663</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>158</v>
@@ -63563,22 +63978,18 @@
         <v>159</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H50" s="8">
-        <v>11832</v>
-      </c>
-      <c r="I50" s="8">
-        <v>16903</v>
-      </c>
-      <c r="J50" s="8">
-        <v>20000</v>
+        <v>289</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9">
+        <v>0</v>
       </c>
       <c r="K50" s="21">
         <v>0</v>
@@ -63586,10 +63997,10 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" s="4">
-        <v>44435</v>
+        <v>45772</v>
       </c>
       <c r="B51" s="4">
-        <v>44440</v>
+        <v>45778</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>158</v>
@@ -63598,31 +64009,31 @@
         <v>159</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G51" s="5"/>
-      <c r="H51" s="8">
-        <v>11832</v>
-      </c>
-      <c r="I51" s="8">
-        <v>17067</v>
-      </c>
-      <c r="J51" s="8">
-        <v>20194</v>
-      </c>
-      <c r="K51" s="19">
-        <v>194</v>
+      <c r="H51" s="21">
+        <v>69093</v>
+      </c>
+      <c r="I51" s="19">
+        <v>28502</v>
+      </c>
+      <c r="J51" s="19">
+        <v>196929</v>
+      </c>
+      <c r="K51" s="21">
+        <v>86850</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" s="4">
-        <v>45656</v>
+        <v>44404</v>
       </c>
       <c r="B52" s="4">
-        <v>45663</v>
+        <v>44407</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>158</v>
@@ -63631,18 +64042,22 @@
         <v>159</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>294</v>
+        <v>67</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="G52" s="5"/>
-      <c r="H52" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H52" s="8">
+        <v>11832</v>
+      </c>
+      <c r="I52" s="8">
+        <v>16903</v>
+      </c>
+      <c r="J52" s="8">
+        <v>20000</v>
       </c>
       <c r="K52" s="21">
         <v>0</v>
@@ -63650,10 +64065,10 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" s="4">
-        <v>45824</v>
+        <v>44435</v>
       </c>
       <c r="B53" s="4">
-        <v>45827</v>
+        <v>44440</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>158</v>
@@ -63662,55 +64077,51 @@
         <v>159</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G53" s="5"/>
-      <c r="H53" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I53" s="19">
-        <v>31398</v>
-      </c>
-      <c r="J53" s="19">
-        <v>12076</v>
-      </c>
-      <c r="K53" s="21">
-        <v>-1071</v>
+      <c r="H53" s="8">
+        <v>11832</v>
+      </c>
+      <c r="I53" s="8">
+        <v>17067</v>
+      </c>
+      <c r="J53" s="8">
+        <v>20194</v>
+      </c>
+      <c r="K53" s="19">
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" s="4">
-        <v>44188</v>
+        <v>45656</v>
       </c>
       <c r="B54" s="4">
-        <v>44193</v>
+        <v>45663</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H54" s="8">
-        <v>4490</v>
-      </c>
-      <c r="I54" s="8">
-        <v>22273</v>
-      </c>
-      <c r="J54" s="8">
-        <v>10000</v>
+        <v>296</v>
+      </c>
+      <c r="G54" s="5"/>
+      <c r="H54" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9">
+        <v>0</v>
       </c>
       <c r="K54" s="21">
         <v>0</v>
@@ -63718,45 +64129,43 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" s="4">
-        <v>44224</v>
+        <v>45824</v>
       </c>
       <c r="B55" s="4">
-        <v>44229</v>
+        <v>45827</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>295</v>
+        <v>68</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H55" s="8">
-        <v>2108</v>
-      </c>
-      <c r="I55" s="8">
-        <v>23721</v>
-      </c>
-      <c r="J55" s="8">
-        <v>5000</v>
+        <v>298</v>
+      </c>
+      <c r="G55" s="5"/>
+      <c r="H55" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I55" s="19">
+        <v>31398</v>
+      </c>
+      <c r="J55" s="19">
+        <v>12076</v>
       </c>
       <c r="K55" s="21">
-        <v>0</v>
+        <v>-1071</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" s="4">
-        <v>44257</v>
+        <v>44188</v>
       </c>
       <c r="B56" s="4">
-        <v>44260</v>
+        <v>44193</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>162</v>
@@ -63774,13 +64183,13 @@
         <v>160</v>
       </c>
       <c r="H56" s="8">
-        <v>1938</v>
+        <v>4490</v>
       </c>
       <c r="I56" s="8">
-        <v>25804</v>
+        <v>22273</v>
       </c>
       <c r="J56" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K56" s="21">
         <v>0</v>
@@ -63788,10 +64197,10 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" s="4">
-        <v>44295</v>
+        <v>44224</v>
       </c>
       <c r="B57" s="4">
-        <v>44300</v>
+        <v>44229</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>162</v>
@@ -63809,10 +64218,10 @@
         <v>160</v>
       </c>
       <c r="H57" s="8">
-        <v>1920</v>
+        <v>2108</v>
       </c>
       <c r="I57" s="8">
-        <v>26043</v>
+        <v>23721</v>
       </c>
       <c r="J57" s="8">
         <v>5000</v>
@@ -63823,10 +64232,10 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B58" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>162</v>
@@ -63844,13 +64253,13 @@
         <v>160</v>
       </c>
       <c r="H58" s="8">
-        <v>4166</v>
+        <v>1938</v>
       </c>
       <c r="I58" s="8">
-        <v>24007</v>
+        <v>25804</v>
       </c>
       <c r="J58" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K58" s="21">
         <v>0</v>
@@ -63858,10 +64267,10 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B59" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>162</v>
@@ -63879,10 +64288,10 @@
         <v>160</v>
       </c>
       <c r="H59" s="8">
-        <v>1983</v>
+        <v>1920</v>
       </c>
       <c r="I59" s="8">
-        <v>25216</v>
+        <v>26043</v>
       </c>
       <c r="J59" s="8">
         <v>5000</v>
@@ -63893,10 +64302,10 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60" s="4">
-        <v>44362</v>
+        <v>44327</v>
       </c>
       <c r="B60" s="4">
-        <v>44365</v>
+        <v>44330</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>162</v>
@@ -63908,31 +64317,33 @@
         <v>295</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G60" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H60" s="8">
-        <v>16605</v>
+        <v>4166</v>
       </c>
       <c r="I60" s="8">
-        <v>26019</v>
+        <v>24007</v>
       </c>
       <c r="J60" s="8">
-        <v>43205</v>
-      </c>
-      <c r="K60" s="19">
-        <v>3205</v>
+        <v>10000</v>
+      </c>
+      <c r="K60" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" s="4">
-        <v>44187</v>
+        <v>44350</v>
       </c>
       <c r="B61" s="4">
-        <v>44190</v>
+        <v>44355</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>159</v>
@@ -63947,27 +64358,27 @@
         <v>160</v>
       </c>
       <c r="H61" s="8">
-        <v>6447</v>
+        <v>1983</v>
       </c>
       <c r="I61" s="8">
-        <v>15511</v>
+        <v>25216</v>
       </c>
       <c r="J61" s="8">
-        <v>10000</v>
-      </c>
-      <c r="K61" s="19">
+        <v>5000</v>
+      </c>
+      <c r="K61" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62" s="4">
-        <v>44224</v>
+        <v>44362</v>
       </c>
       <c r="B62" s="4">
-        <v>44229</v>
+        <v>44365</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>159</v>
@@ -63976,30 +64387,28 @@
         <v>295</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="G62" s="5"/>
       <c r="H62" s="8">
-        <v>3093</v>
+        <v>16605</v>
       </c>
       <c r="I62" s="8">
-        <v>16167</v>
+        <v>26019</v>
       </c>
       <c r="J62" s="8">
-        <v>5000</v>
+        <v>43205</v>
       </c>
       <c r="K62" s="19">
-        <v>0</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63" s="4">
-        <v>44257</v>
+        <v>44187</v>
       </c>
       <c r="B63" s="4">
-        <v>44260</v>
+        <v>44190</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>161</v>
@@ -64017,13 +64426,13 @@
         <v>160</v>
       </c>
       <c r="H63" s="8">
-        <v>2978</v>
+        <v>6447</v>
       </c>
       <c r="I63" s="8">
-        <v>16792</v>
+        <v>15511</v>
       </c>
       <c r="J63" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K63" s="19">
         <v>0</v>
@@ -64031,10 +64440,10 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64" s="4">
-        <v>44295</v>
+        <v>44224</v>
       </c>
       <c r="B64" s="4">
-        <v>44300</v>
+        <v>44229</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>161</v>
@@ -64052,10 +64461,10 @@
         <v>160</v>
       </c>
       <c r="H64" s="8">
-        <v>2810</v>
+        <v>3093</v>
       </c>
       <c r="I64" s="8">
-        <v>17792</v>
+        <v>16167</v>
       </c>
       <c r="J64" s="8">
         <v>5000</v>
@@ -64066,10 +64475,10 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A65" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B65" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>161</v>
@@ -64087,10 +64496,10 @@
         <v>160</v>
       </c>
       <c r="H65" s="8">
-        <v>2903</v>
+        <v>2978</v>
       </c>
       <c r="I65" s="8">
-        <v>17225</v>
+        <v>16792</v>
       </c>
       <c r="J65" s="8">
         <v>5000</v>
@@ -64101,10 +64510,10 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B66" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>161</v>
@@ -64122,10 +64531,10 @@
         <v>160</v>
       </c>
       <c r="H66" s="8">
-        <v>2819</v>
+        <v>2810</v>
       </c>
       <c r="I66" s="8">
-        <v>17736</v>
+        <v>17792</v>
       </c>
       <c r="J66" s="8">
         <v>5000</v>
@@ -64136,10 +64545,10 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67" s="4">
-        <v>44362</v>
+        <v>44327</v>
       </c>
       <c r="B67" s="4">
-        <v>44365</v>
+        <v>44330</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>161</v>
@@ -64151,37 +64560,39 @@
         <v>295</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G67" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H67" s="8">
-        <v>21050</v>
+        <v>2903</v>
       </c>
       <c r="I67" s="8">
-        <v>18410</v>
+        <v>17225</v>
       </c>
       <c r="J67" s="8">
-        <v>38753</v>
+        <v>5000</v>
       </c>
       <c r="K67" s="19">
-        <v>3753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68" s="4">
-        <v>45243</v>
+        <v>44350</v>
       </c>
       <c r="B68" s="4">
-        <v>45247</v>
+        <v>44355</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>30</v>
@@ -64189,56 +64600,124 @@
       <c r="G68" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="H68" s="19">
-        <v>180143</v>
-      </c>
-      <c r="I68" s="19">
-        <v>12456</v>
+      <c r="H68" s="8">
+        <v>2819</v>
+      </c>
+      <c r="I68" s="8">
+        <v>17736</v>
       </c>
       <c r="J68" s="8">
-        <v>224386</v>
-      </c>
-      <c r="K68" s="21">
+        <v>5000</v>
+      </c>
+      <c r="K68" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69" s="4">
-        <v>45664</v>
+        <v>44362</v>
       </c>
       <c r="B69" s="4">
-        <v>45671</v>
+        <v>44365</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G69" s="5"/>
-      <c r="H69" s="21">
+      <c r="H69" s="8">
+        <v>21050</v>
+      </c>
+      <c r="I69" s="8">
+        <v>18410</v>
+      </c>
+      <c r="J69" s="8">
+        <v>38753</v>
+      </c>
+      <c r="K69" s="19">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A70" s="4">
+        <v>45243</v>
+      </c>
+      <c r="B70" s="4">
+        <v>45247</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H70" s="19">
         <v>180143</v>
       </c>
-      <c r="I69" s="21">
+      <c r="I70" s="19">
+        <v>12456</v>
+      </c>
+      <c r="J70" s="8">
+        <v>224386</v>
+      </c>
+      <c r="K70" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A71" s="4">
+        <v>45664</v>
+      </c>
+      <c r="B71" s="4">
+        <v>45671</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G71" s="5"/>
+      <c r="H71" s="21">
+        <v>180143</v>
+      </c>
+      <c r="I71" s="21">
         <v>15148</v>
       </c>
-      <c r="J69" s="21">
+      <c r="J71" s="21">
         <v>272881</v>
       </c>
-      <c r="K69" s="19">
+      <c r="K71" s="19">
         <v>48494</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K59" xr:uid="{00000000-0009-0000-0000-000007000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K69">
-      <sortCondition ref="C1:C59"/>
+  <autoFilter ref="A1:K61" xr:uid="{00000000-0009-0000-0000-000007000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K71">
+      <sortCondition ref="C1:C61"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18"/>

--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="524" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A433DA7-AE71-4509-ACBD-FACE29DA9E11}"/>
+  <xr:revisionPtr revIDLastSave="541" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1759DF38-932B-42FD-9CD4-2A66EC607A45}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6985" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7145" uniqueCount="463">
   <si>
     <t>約定日</t>
   </si>
@@ -2044,6 +2044,30 @@
   <si>
     <t>ハーモニック・ドライブ・シス</t>
   </si>
+  <si>
+    <t>関電工</t>
+  </si>
+  <si>
+    <t>リクルートホールディングス</t>
+  </si>
+  <si>
+    <t>ＳＷＣＣ</t>
+  </si>
+  <si>
+    <t>アドバンテスト</t>
+  </si>
+  <si>
+    <t>フェローテック</t>
+  </si>
+  <si>
+    <t>ナブテスコ</t>
+  </si>
+  <si>
+    <t>ふくおかフィナンシャルＧ</t>
+  </si>
+  <si>
+    <t>三菱電機</t>
+  </si>
 </sst>
 </file>
 
@@ -2764,7 +2788,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2980,9 +3004,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3349,7 +3370,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46131</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3414,7 +3435,7 @@
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>10017693</v>
+        <v>10276393</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
@@ -3422,15 +3443,15 @@
       </c>
       <c r="H4" s="20">
         <f>SUM(H5:H100)</f>
-        <v>822090</v>
+        <v>829290</v>
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>6681004</v>
+        <v>6946904</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>5323758.0373999998</v>
+        <v>5535640.4523999998</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -3466,11 +3487,11 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>8391430.2923499998</v>
+        <v>8603312.7073499989</v>
       </c>
       <c r="U4" s="60">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.441095890410959</v>
+        <v>5.484931506849315</v>
       </c>
       <c r="V4" s="60"/>
     </row>
@@ -3881,7 +3902,7 @@
       </c>
       <c r="F10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
-        <v>2371300</v>
+        <v>2630000</v>
       </c>
       <c r="G10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
@@ -3889,15 +3910,15 @@
       </c>
       <c r="H10" s="19">
         <f>SUMIFS(国内株式_特定_配当!$H$2:$H$999,国内株式_特定_配当!$A$2:$A$999,"&gt;=2026/1/1",国内株式_特定_配当!$A$2:$A$999,"&lt;=2026/12/31")</f>
-        <v>19935</v>
+        <v>27135</v>
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>1657755</v>
+        <v>1923655</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>1320982.0717500001</v>
+        <v>1532864.4867499999</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -3933,7 +3954,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>1533434.7882500002</v>
+        <v>1745317.20325</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -12294,7 +12315,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O892"/>
+  <dimension ref="A1:O923"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -51585,7 +51606,7 @@
         <v>31</v>
       </c>
       <c r="M873" s="15">
-        <f t="shared" ref="M873:M892" si="20">IF(G873="買付",H873*I873+SUM(J873:K873),H873*I873-SUM(J873:K873))</f>
+        <f t="shared" ref="M873:M923" si="20">IF(G873="買付",H873*I873+SUM(J873:K873),H873*I873-SUM(J873:K873))</f>
         <v>111220</v>
       </c>
       <c r="N873" s="19">
@@ -52428,7 +52449,7 @@
       <c r="H892" s="5">
         <v>100</v>
       </c>
-      <c r="I892" s="72">
+      <c r="I892" s="7">
         <v>4545</v>
       </c>
       <c r="J892" s="9">
@@ -52446,6 +52467,1402 @@
       </c>
       <c r="N892" s="19">
         <v>16500</v>
+      </c>
+    </row>
+    <row r="893" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A893" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B893" s="4">
+        <v>46135</v>
+      </c>
+      <c r="C893" s="5">
+        <v>1540</v>
+      </c>
+      <c r="D893" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="E893" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F893" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G893" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H893" s="5">
+        <v>5</v>
+      </c>
+      <c r="I893" s="7">
+        <v>22875</v>
+      </c>
+      <c r="J893" s="9">
+        <v>0</v>
+      </c>
+      <c r="K893" s="9">
+        <v>0</v>
+      </c>
+      <c r="L893" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M893" s="15">
+        <f t="shared" si="20"/>
+        <v>114375</v>
+      </c>
+      <c r="N893" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A894" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B894" s="4">
+        <v>46135</v>
+      </c>
+      <c r="C894" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D894" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E894" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F894" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G894" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H894" s="5">
+        <v>100</v>
+      </c>
+      <c r="I894" s="7">
+        <v>1483</v>
+      </c>
+      <c r="J894" s="9">
+        <v>0</v>
+      </c>
+      <c r="K894" s="9">
+        <v>0</v>
+      </c>
+      <c r="L894" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M894" s="15">
+        <f t="shared" si="20"/>
+        <v>148300</v>
+      </c>
+      <c r="N894" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A895" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B895" s="4">
+        <v>46135</v>
+      </c>
+      <c r="C895" s="5">
+        <v>1942</v>
+      </c>
+      <c r="D895" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="E895" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F895" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G895" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H895" s="5">
+        <v>100</v>
+      </c>
+      <c r="I895" s="7">
+        <v>6125</v>
+      </c>
+      <c r="J895" s="9">
+        <v>0</v>
+      </c>
+      <c r="K895" s="9">
+        <v>0</v>
+      </c>
+      <c r="L895" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M895" s="15">
+        <f t="shared" si="20"/>
+        <v>612500</v>
+      </c>
+      <c r="N895" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A896" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B896" s="4">
+        <v>46135</v>
+      </c>
+      <c r="C896" s="5">
+        <v>5803</v>
+      </c>
+      <c r="D896" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E896" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F896" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G896" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H896" s="5">
+        <v>100</v>
+      </c>
+      <c r="I896" s="7">
+        <v>5806</v>
+      </c>
+      <c r="J896" s="9">
+        <v>0</v>
+      </c>
+      <c r="K896" s="9">
+        <v>0</v>
+      </c>
+      <c r="L896" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M896" s="15">
+        <f t="shared" si="20"/>
+        <v>580600</v>
+      </c>
+      <c r="N896" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="897" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A897" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B897" s="4">
+        <v>46135</v>
+      </c>
+      <c r="C897" s="5">
+        <v>6098</v>
+      </c>
+      <c r="D897" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="E897" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F897" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G897" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H897" s="5">
+        <v>100</v>
+      </c>
+      <c r="I897" s="7">
+        <v>7821.9</v>
+      </c>
+      <c r="J897" s="9">
+        <v>0</v>
+      </c>
+      <c r="K897" s="9">
+        <v>0</v>
+      </c>
+      <c r="L897" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M897" s="15">
+        <f t="shared" si="20"/>
+        <v>782190</v>
+      </c>
+      <c r="N897" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="898" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A898" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B898" s="4">
+        <v>46135</v>
+      </c>
+      <c r="C898" s="5">
+        <v>6954</v>
+      </c>
+      <c r="D898" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="E898" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F898" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G898" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H898" s="5">
+        <v>100</v>
+      </c>
+      <c r="I898" s="7">
+        <v>6533.8</v>
+      </c>
+      <c r="J898" s="9">
+        <v>0</v>
+      </c>
+      <c r="K898" s="9">
+        <v>0</v>
+      </c>
+      <c r="L898" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M898" s="15">
+        <f t="shared" si="20"/>
+        <v>653380</v>
+      </c>
+      <c r="N898" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="899" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A899" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B899" s="4">
+        <v>46135</v>
+      </c>
+      <c r="C899" s="5">
+        <v>8766</v>
+      </c>
+      <c r="D899" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E899" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F899" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G899" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H899" s="5">
+        <v>100</v>
+      </c>
+      <c r="I899" s="7">
+        <v>7248</v>
+      </c>
+      <c r="J899" s="9">
+        <v>0</v>
+      </c>
+      <c r="K899" s="9">
+        <v>0</v>
+      </c>
+      <c r="L899" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M899" s="15">
+        <f t="shared" si="20"/>
+        <v>724800</v>
+      </c>
+      <c r="N899" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="900" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A900" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B900" s="4">
+        <v>46136</v>
+      </c>
+      <c r="C900" s="5">
+        <v>5805</v>
+      </c>
+      <c r="D900" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="E900" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F900" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G900" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H900" s="5">
+        <v>100</v>
+      </c>
+      <c r="I900" s="7">
+        <v>15600</v>
+      </c>
+      <c r="J900" s="9">
+        <v>0</v>
+      </c>
+      <c r="K900" s="9">
+        <v>0</v>
+      </c>
+      <c r="L900" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M900" s="15">
+        <f t="shared" si="20"/>
+        <v>1560000</v>
+      </c>
+      <c r="N900" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="901" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A901" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B901" s="4">
+        <v>46136</v>
+      </c>
+      <c r="C901" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D901" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E901" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F901" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G901" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H901" s="5">
+        <v>100</v>
+      </c>
+      <c r="I901" s="7">
+        <v>27875</v>
+      </c>
+      <c r="J901" s="9">
+        <v>0</v>
+      </c>
+      <c r="K901" s="9">
+        <v>0</v>
+      </c>
+      <c r="L901" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M901" s="15">
+        <f t="shared" si="20"/>
+        <v>2787500</v>
+      </c>
+      <c r="N901" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A902" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B902" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C902" s="5">
+        <v>5803</v>
+      </c>
+      <c r="D902" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E902" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F902" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G902" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H902" s="5">
+        <v>100</v>
+      </c>
+      <c r="I902" s="7">
+        <v>5866</v>
+      </c>
+      <c r="J902" s="9">
+        <v>0</v>
+      </c>
+      <c r="K902" s="9">
+        <v>0</v>
+      </c>
+      <c r="L902" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M902" s="15">
+        <f t="shared" si="20"/>
+        <v>586600</v>
+      </c>
+      <c r="N902" s="19">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="903" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A903" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B903" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C903" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D903" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E903" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F903" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G903" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H903" s="5">
+        <v>100</v>
+      </c>
+      <c r="I903" s="7">
+        <v>28445</v>
+      </c>
+      <c r="J903" s="9">
+        <v>0</v>
+      </c>
+      <c r="K903" s="9">
+        <v>0</v>
+      </c>
+      <c r="L903" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M903" s="15">
+        <f t="shared" si="20"/>
+        <v>2844500</v>
+      </c>
+      <c r="N903" s="19">
+        <v>57000</v>
+      </c>
+    </row>
+    <row r="904" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A904" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B904" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C904" s="5">
+        <v>7721</v>
+      </c>
+      <c r="D904" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="E904" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F904" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G904" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H904" s="5">
+        <v>100</v>
+      </c>
+      <c r="I904" s="7">
+        <v>8141</v>
+      </c>
+      <c r="J904" s="9">
+        <v>0</v>
+      </c>
+      <c r="K904" s="9">
+        <v>0</v>
+      </c>
+      <c r="L904" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M904" s="15">
+        <f t="shared" si="20"/>
+        <v>814100</v>
+      </c>
+      <c r="N904" s="19">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="905" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A905" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B905" s="4">
+        <v>46140</v>
+      </c>
+      <c r="C905" s="5">
+        <v>5803</v>
+      </c>
+      <c r="D905" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E905" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F905" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G905" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H905" s="5">
+        <v>100</v>
+      </c>
+      <c r="I905" s="7">
+        <v>6050</v>
+      </c>
+      <c r="J905" s="9">
+        <v>0</v>
+      </c>
+      <c r="K905" s="9">
+        <v>0</v>
+      </c>
+      <c r="L905" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M905" s="15">
+        <f t="shared" si="20"/>
+        <v>605000</v>
+      </c>
+      <c r="N905" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A906" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B906" s="4">
+        <v>46140</v>
+      </c>
+      <c r="C906" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D906" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E906" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F906" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G906" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H906" s="5">
+        <v>100</v>
+      </c>
+      <c r="I906" s="7">
+        <v>29235.3</v>
+      </c>
+      <c r="J906" s="9">
+        <v>0</v>
+      </c>
+      <c r="K906" s="9">
+        <v>0</v>
+      </c>
+      <c r="L906" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M906" s="15">
+        <f t="shared" si="20"/>
+        <v>2923530</v>
+      </c>
+      <c r="N906" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="907" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A907" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B907" s="4">
+        <v>46140</v>
+      </c>
+      <c r="C907" s="5">
+        <v>6890</v>
+      </c>
+      <c r="D907" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E907" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F907" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G907" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H907" s="5">
+        <v>100</v>
+      </c>
+      <c r="I907" s="7">
+        <v>7496</v>
+      </c>
+      <c r="J907" s="9">
+        <v>0</v>
+      </c>
+      <c r="K907" s="9">
+        <v>0</v>
+      </c>
+      <c r="L907" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M907" s="15">
+        <f t="shared" si="20"/>
+        <v>749600</v>
+      </c>
+      <c r="N907" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A908" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B908" s="4">
+        <v>46142</v>
+      </c>
+      <c r="C908" s="5">
+        <v>2802</v>
+      </c>
+      <c r="D908" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="E908" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F908" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G908" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H908" s="5">
+        <v>200</v>
+      </c>
+      <c r="I908" s="7">
+        <v>4790</v>
+      </c>
+      <c r="J908" s="9">
+        <v>0</v>
+      </c>
+      <c r="K908" s="9">
+        <v>0</v>
+      </c>
+      <c r="L908" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M908" s="15">
+        <f t="shared" si="20"/>
+        <v>958000</v>
+      </c>
+      <c r="N908" s="19">
+        <f>9400*2</f>
+        <v>18800</v>
+      </c>
+    </row>
+    <row r="909" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A909" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B909" s="4">
+        <v>46142</v>
+      </c>
+      <c r="C909" s="5">
+        <v>5803</v>
+      </c>
+      <c r="D909" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E909" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F909" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G909" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H909" s="5">
+        <v>100</v>
+      </c>
+      <c r="I909" s="7">
+        <v>6360</v>
+      </c>
+      <c r="J909" s="9">
+        <v>0</v>
+      </c>
+      <c r="K909" s="9">
+        <v>0</v>
+      </c>
+      <c r="L909" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M909" s="15">
+        <f t="shared" si="20"/>
+        <v>636000</v>
+      </c>
+      <c r="N909" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="910" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A910" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B910" s="4">
+        <v>46142</v>
+      </c>
+      <c r="C910" s="5">
+        <v>6268</v>
+      </c>
+      <c r="D910" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="E910" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F910" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G910" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H910" s="5">
+        <v>100</v>
+      </c>
+      <c r="I910" s="7">
+        <v>4978</v>
+      </c>
+      <c r="J910" s="9">
+        <v>0</v>
+      </c>
+      <c r="K910" s="9">
+        <v>0</v>
+      </c>
+      <c r="L910" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M910" s="15">
+        <f t="shared" si="20"/>
+        <v>497800</v>
+      </c>
+      <c r="N910" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A911" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B911" s="4">
+        <v>46142</v>
+      </c>
+      <c r="C911" s="5">
+        <v>6324</v>
+      </c>
+      <c r="D911" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E911" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F911" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G911" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H911" s="5">
+        <v>100</v>
+      </c>
+      <c r="I911" s="7">
+        <v>4895</v>
+      </c>
+      <c r="J911" s="9">
+        <v>0</v>
+      </c>
+      <c r="K911" s="9">
+        <v>0</v>
+      </c>
+      <c r="L911" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M911" s="15">
+        <f t="shared" si="20"/>
+        <v>489500</v>
+      </c>
+      <c r="N911" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A912" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B912" s="4">
+        <v>46143</v>
+      </c>
+      <c r="C912" s="5">
+        <v>6268</v>
+      </c>
+      <c r="D912" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="E912" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F912" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G912" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H912" s="5">
+        <v>100</v>
+      </c>
+      <c r="I912" s="7">
+        <v>5002</v>
+      </c>
+      <c r="J912" s="9">
+        <v>0</v>
+      </c>
+      <c r="K912" s="9">
+        <v>0</v>
+      </c>
+      <c r="L912" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M912" s="15">
+        <f t="shared" si="20"/>
+        <v>500200</v>
+      </c>
+      <c r="N912" s="19">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="913" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A913" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B913" s="4">
+        <v>46143</v>
+      </c>
+      <c r="C913" s="5">
+        <v>6890</v>
+      </c>
+      <c r="D913" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E913" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F913" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G913" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H913" s="5">
+        <v>100</v>
+      </c>
+      <c r="I913" s="7">
+        <v>7300</v>
+      </c>
+      <c r="J913" s="9">
+        <v>0</v>
+      </c>
+      <c r="K913" s="9">
+        <v>0</v>
+      </c>
+      <c r="L913" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M913" s="15">
+        <f t="shared" si="20"/>
+        <v>730000</v>
+      </c>
+      <c r="N913" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A914" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B914" s="4">
+        <v>46143</v>
+      </c>
+      <c r="C914" s="5">
+        <v>8031</v>
+      </c>
+      <c r="D914" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E914" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F914" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G914" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H914" s="5">
+        <v>100</v>
+      </c>
+      <c r="I914" s="7">
+        <v>5825</v>
+      </c>
+      <c r="J914" s="9">
+        <v>0</v>
+      </c>
+      <c r="K914" s="9">
+        <v>0</v>
+      </c>
+      <c r="L914" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M914" s="15">
+        <f t="shared" si="20"/>
+        <v>582500</v>
+      </c>
+      <c r="N914" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="915" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A915" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B915" s="4">
+        <v>46143</v>
+      </c>
+      <c r="C915" s="5">
+        <v>8354</v>
+      </c>
+      <c r="D915" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="E915" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F915" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G915" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H915" s="5">
+        <v>100</v>
+      </c>
+      <c r="I915" s="7">
+        <v>6409.2</v>
+      </c>
+      <c r="J915" s="9">
+        <v>0</v>
+      </c>
+      <c r="K915" s="9">
+        <v>0</v>
+      </c>
+      <c r="L915" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M915" s="15">
+        <f t="shared" si="20"/>
+        <v>640920</v>
+      </c>
+      <c r="N915" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A916" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B916" s="4">
+        <v>46149</v>
+      </c>
+      <c r="C916" s="5">
+        <v>8354</v>
+      </c>
+      <c r="D916" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="E916" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F916" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G916" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H916" s="5">
+        <v>100</v>
+      </c>
+      <c r="I916" s="7">
+        <v>6412</v>
+      </c>
+      <c r="J916" s="9">
+        <v>0</v>
+      </c>
+      <c r="K916" s="9">
+        <v>0</v>
+      </c>
+      <c r="L916" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M916" s="15">
+        <f t="shared" si="20"/>
+        <v>641200</v>
+      </c>
+      <c r="N916" s="19">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="917" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A917" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B917" s="4">
+        <v>46149</v>
+      </c>
+      <c r="C917" s="5">
+        <v>1942</v>
+      </c>
+      <c r="D917" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="E917" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F917" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G917" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H917" s="5">
+        <v>100</v>
+      </c>
+      <c r="I917" s="7">
+        <v>6627</v>
+      </c>
+      <c r="J917" s="9">
+        <v>0</v>
+      </c>
+      <c r="K917" s="9">
+        <v>0</v>
+      </c>
+      <c r="L917" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M917" s="15">
+        <f t="shared" si="20"/>
+        <v>662700</v>
+      </c>
+      <c r="N917" s="19">
+        <v>50200</v>
+      </c>
+    </row>
+    <row r="918" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A918" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B918" s="4">
+        <v>46149</v>
+      </c>
+      <c r="C918" s="5">
+        <v>6503</v>
+      </c>
+      <c r="D918" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="E918" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F918" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G918" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H918" s="5">
+        <v>100</v>
+      </c>
+      <c r="I918" s="7">
+        <v>6441</v>
+      </c>
+      <c r="J918" s="9">
+        <v>0</v>
+      </c>
+      <c r="K918" s="9">
+        <v>0</v>
+      </c>
+      <c r="L918" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M918" s="15">
+        <f t="shared" si="20"/>
+        <v>644100</v>
+      </c>
+      <c r="N918" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="919" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A919" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B919" s="4">
+        <v>46149</v>
+      </c>
+      <c r="C919" s="5">
+        <v>6890</v>
+      </c>
+      <c r="D919" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E919" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F919" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G919" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H919" s="5">
+        <v>200</v>
+      </c>
+      <c r="I919" s="7">
+        <v>7740</v>
+      </c>
+      <c r="J919" s="9">
+        <v>0</v>
+      </c>
+      <c r="K919" s="9">
+        <v>0</v>
+      </c>
+      <c r="L919" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M919" s="15">
+        <f t="shared" si="20"/>
+        <v>1548000</v>
+      </c>
+      <c r="N919" s="19">
+        <v>68400</v>
+      </c>
+    </row>
+    <row r="920" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A920" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B920" s="4">
+        <v>46149</v>
+      </c>
+      <c r="C920" s="5">
+        <v>5805</v>
+      </c>
+      <c r="D920" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="E920" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F920" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G920" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H920" s="5">
+        <v>100</v>
+      </c>
+      <c r="I920" s="7">
+        <v>15631</v>
+      </c>
+      <c r="J920" s="9">
+        <v>0</v>
+      </c>
+      <c r="K920" s="9">
+        <v>0</v>
+      </c>
+      <c r="L920" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M920" s="15">
+        <f t="shared" si="20"/>
+        <v>1563100</v>
+      </c>
+      <c r="N920" s="19">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="921" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A921" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B921" s="4">
+        <v>46150</v>
+      </c>
+      <c r="C921" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D921" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E921" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F921" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G921" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H921" s="5">
+        <v>100</v>
+      </c>
+      <c r="I921" s="7">
+        <v>1328</v>
+      </c>
+      <c r="J921" s="9">
+        <v>0</v>
+      </c>
+      <c r="K921" s="9">
+        <v>0</v>
+      </c>
+      <c r="L921" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M921" s="15">
+        <f t="shared" si="20"/>
+        <v>132800</v>
+      </c>
+      <c r="N921" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A922" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B922" s="4">
+        <v>46150</v>
+      </c>
+      <c r="C922" s="5">
+        <v>6232</v>
+      </c>
+      <c r="D922" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="E922" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F922" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G922" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H922" s="5">
+        <v>100</v>
+      </c>
+      <c r="I922" s="7">
+        <v>2585</v>
+      </c>
+      <c r="J922" s="9">
+        <v>0</v>
+      </c>
+      <c r="K922" s="9">
+        <v>0</v>
+      </c>
+      <c r="L922" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M922" s="15">
+        <f t="shared" si="20"/>
+        <v>258500</v>
+      </c>
+      <c r="N922" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A923" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B923" s="4">
+        <v>46150</v>
+      </c>
+      <c r="C923" s="5">
+        <v>6324</v>
+      </c>
+      <c r="D923" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E923" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F923" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G923" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H923" s="5">
+        <v>100</v>
+      </c>
+      <c r="I923" s="7">
+        <v>5240</v>
+      </c>
+      <c r="J923" s="9">
+        <v>0</v>
+      </c>
+      <c r="K923" s="9">
+        <v>0</v>
+      </c>
+      <c r="L923" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M923" s="15">
+        <f t="shared" si="20"/>
+        <v>524000</v>
+      </c>
+      <c r="N923" s="19">
+        <v>34500</v>
       </c>
     </row>
   </sheetData>
@@ -52465,7 +53882,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -55511,11 +56928,11 @@
         <v>1218</v>
       </c>
       <c r="J80" s="19">
-        <f t="shared" ref="J80:J89" si="16">H80-I80</f>
+        <f t="shared" ref="J80:J90" si="16">H80-I80</f>
         <v>4782</v>
       </c>
       <c r="K80" s="19">
-        <f t="shared" ref="K80:K89" si="17">J80</f>
+        <f t="shared" ref="K80:K90" si="17">J80</f>
         <v>4782</v>
       </c>
     </row>
@@ -55770,7 +57187,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="19">
-        <f t="shared" ref="H87:H89" si="18">F87*G87</f>
+        <f t="shared" ref="H87:H90" si="18">F87*G87</f>
         <v>8000</v>
       </c>
       <c r="I87" s="19">
@@ -55859,6 +57276,44 @@
       <c r="K89" s="19">
         <f t="shared" si="17"/>
         <v>1403</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A90" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" s="5">
+        <v>1928</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="F90" s="9">
+        <v>72</v>
+      </c>
+      <c r="G90" s="5">
+        <v>100</v>
+      </c>
+      <c r="H90" s="19">
+        <f t="shared" si="18"/>
+        <v>7200</v>
+      </c>
+      <c r="I90" s="19">
+        <v>1462</v>
+      </c>
+      <c r="J90" s="19">
+        <f t="shared" si="16"/>
+        <v>5738</v>
+      </c>
+      <c r="K90" s="19">
+        <f t="shared" si="17"/>
+        <v>5738</v>
       </c>
     </row>
   </sheetData>

--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="541" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1759DF38-932B-42FD-9CD4-2A66EC607A45}"/>
+  <xr:revisionPtr revIDLastSave="552" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A48A877C-DF71-401F-B68F-82B4653DABEE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ_日本" sheetId="10" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7145" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7199" uniqueCount="463">
   <si>
     <t>約定日</t>
   </si>
@@ -2788,7 +2788,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2954,22 +2954,16 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2993,6 +2987,12 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3004,6 +3004,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3283,31 +3286,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55" t="s">
         <v>216</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59" t="s">
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55" t="s">
         <v>218</v>
       </c>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="65" t="s">
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="63" t="s">
         <v>302</v>
       </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="67"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="65"/>
       <c r="S1" s="37" t="s">
         <v>219</v>
       </c>
@@ -3319,50 +3322,50 @@
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55" t="s">
+      <c r="C2" s="57"/>
+      <c r="D2" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55" t="s">
+      <c r="G2" s="57"/>
+      <c r="H2" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="55" t="s">
+      <c r="K2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="57" t="s">
+      <c r="L2" s="57"/>
+      <c r="M2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="N2" s="62" t="s">
+      <c r="N2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="O2" s="63" t="s">
+      <c r="O2" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="57" t="s">
+      <c r="P2" s="62"/>
+      <c r="Q2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="R2" s="62" t="s">
+      <c r="R2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="S2" s="61" t="s">
+      <c r="S2" s="59" t="s">
         <v>214</v>
       </c>
       <c r="U2" s="49">
@@ -3370,7 +3373,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3380,38 +3383,38 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="58"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="55"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
       <c r="K3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
       <c r="O3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="P3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="61"/>
-      <c r="U3" s="59" t="s">
+      <c r="Q3" s="58"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="59"/>
+      <c r="U3" s="55" t="s">
         <v>363</v>
       </c>
-      <c r="V3" s="59"/>
+      <c r="V3" s="55"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="34" t="s">
@@ -3427,15 +3430,15 @@
       </c>
       <c r="D4" s="20">
         <f>SUM(D5:D100)</f>
-        <v>455495</v>
+        <v>458895</v>
       </c>
       <c r="E4" s="35">
         <f>SUM(B4:D4)</f>
-        <v>3174795</v>
+        <v>3178195</v>
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>10276393</v>
+        <v>10577223</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
@@ -3447,11 +3450,11 @@
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>6946904</v>
+        <v>7247734</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>5535640.4523999998</v>
+        <v>5775356.8378999997</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -3487,13 +3490,13 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>8603312.7073499989</v>
-      </c>
-      <c r="U4" s="60">
+        <v>8846429.0928499997</v>
+      </c>
+      <c r="U4" s="56">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.484931506849315</v>
-      </c>
-      <c r="V4" s="60"/>
+        <v>5.5041095890410956</v>
+      </c>
+      <c r="V4" s="56"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="34" t="s">
@@ -3894,15 +3897,15 @@
       </c>
       <c r="D10" s="19">
         <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1003,国内株式_NISA_配当!$A$2:$A$1003,"&gt;=2026/1/1",国内株式_NISA_配当!$A$2:$A$1003,"&lt;=2026/12/31")</f>
-        <v>5200</v>
+        <v>8600</v>
       </c>
       <c r="E10" s="35">
         <f t="shared" si="7"/>
-        <v>5200</v>
+        <v>8600</v>
       </c>
       <c r="F10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
-        <v>2630000</v>
+        <v>2930830</v>
       </c>
       <c r="G10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
@@ -3914,11 +3917,11 @@
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>1923655</v>
+        <v>2224485</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>1532864.4867499999</v>
+        <v>1772580.87225</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -3954,7 +3957,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>1745317.20325</v>
+        <v>1988433.5887500001</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -3968,6 +3971,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="H2:H3"/>
@@ -3983,11 +3991,6 @@
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6777,49 +6780,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="55" t="s">
         <v>417</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55" t="s">
         <v>416</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
       <c r="K1" s="69" t="s">
         <v>219</v>
       </c>
       <c r="L1" s="69"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="55"/>
+      <c r="C2" s="57"/>
       <c r="D2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="55"/>
+      <c r="G2" s="57"/>
       <c r="H2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="61" t="s">
+      <c r="K2" s="59" t="s">
         <v>214</v>
       </c>
       <c r="L2" s="70" t="s">
@@ -6833,18 +6836,18 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="58"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="56"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="61"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
       <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -10007,7 +10010,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -12283,19 +12286,57 @@
         <v>400</v>
       </c>
       <c r="H60" s="19">
-        <f t="shared" ref="H60" si="10">F60*G60</f>
+        <f t="shared" ref="H60:H61" si="10">F60*G60</f>
         <v>5200</v>
       </c>
       <c r="I60" s="19">
         <v>0</v>
       </c>
       <c r="J60" s="19">
-        <f t="shared" ref="J60" si="11">H60-I60</f>
+        <f t="shared" ref="J60:J61" si="11">H60-I60</f>
         <v>5200</v>
       </c>
       <c r="K60" s="19">
-        <f t="shared" ref="K60" si="12">J60</f>
+        <f t="shared" ref="K60:K61" si="12">J60</f>
         <v>5200</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A61" s="4">
+        <v>46150</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D61" s="5">
+        <v>6506</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="F61" s="72">
+        <v>34</v>
+      </c>
+      <c r="G61" s="5">
+        <v>100</v>
+      </c>
+      <c r="H61" s="19">
+        <f t="shared" si="10"/>
+        <v>3400</v>
+      </c>
+      <c r="I61" s="19">
+        <v>0</v>
+      </c>
+      <c r="J61" s="19">
+        <f t="shared" si="11"/>
+        <v>3400</v>
+      </c>
+      <c r="K61" s="19">
+        <f t="shared" si="12"/>
+        <v>3400</v>
       </c>
     </row>
   </sheetData>
@@ -12315,7 +12356,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O923"/>
+  <dimension ref="A1:O933"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -51606,7 +51647,7 @@
         <v>31</v>
       </c>
       <c r="M873" s="15">
-        <f t="shared" ref="M873:M923" si="20">IF(G873="買付",H873*I873+SUM(J873:K873),H873*I873-SUM(J873:K873))</f>
+        <f t="shared" ref="M873:M933" si="20">IF(G873="買付",H873*I873+SUM(J873:K873),H873*I873-SUM(J873:K873))</f>
         <v>111220</v>
       </c>
       <c r="N873" s="19">
@@ -53863,6 +53904,456 @@
       </c>
       <c r="N923" s="19">
         <v>34500</v>
+      </c>
+    </row>
+    <row r="924" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A924" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B924" s="4">
+        <v>46153</v>
+      </c>
+      <c r="C924" s="5">
+        <v>5803</v>
+      </c>
+      <c r="D924" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E924" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F924" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G924" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H924" s="5">
+        <v>200</v>
+      </c>
+      <c r="I924" s="7">
+        <v>6325</v>
+      </c>
+      <c r="J924" s="9">
+        <v>0</v>
+      </c>
+      <c r="K924" s="9">
+        <v>0</v>
+      </c>
+      <c r="L924" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M924" s="15">
+        <f t="shared" si="20"/>
+        <v>1265000</v>
+      </c>
+      <c r="N924" s="19">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="925" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A925" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B925" s="4">
+        <v>46153</v>
+      </c>
+      <c r="C925" s="5">
+        <v>6503</v>
+      </c>
+      <c r="D925" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="E925" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F925" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G925" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H925" s="5">
+        <v>100</v>
+      </c>
+      <c r="I925" s="7">
+        <v>6480.3</v>
+      </c>
+      <c r="J925" s="9">
+        <v>0</v>
+      </c>
+      <c r="K925" s="9">
+        <v>0</v>
+      </c>
+      <c r="L925" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M925" s="15">
+        <f t="shared" si="20"/>
+        <v>648030</v>
+      </c>
+      <c r="N925" s="19">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="926" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A926" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B926" s="4">
+        <v>46153</v>
+      </c>
+      <c r="C926" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D926" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E926" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F926" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G926" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H926" s="5">
+        <v>100</v>
+      </c>
+      <c r="I926" s="7">
+        <v>30000</v>
+      </c>
+      <c r="J926" s="9">
+        <v>0</v>
+      </c>
+      <c r="K926" s="9">
+        <v>0</v>
+      </c>
+      <c r="L926" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M926" s="15">
+        <f t="shared" si="20"/>
+        <v>3000000</v>
+      </c>
+      <c r="N926" s="19">
+        <v>76400</v>
+      </c>
+    </row>
+    <row r="927" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A927" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B927" s="4">
+        <v>46153</v>
+      </c>
+      <c r="C927" s="5">
+        <v>6954</v>
+      </c>
+      <c r="D927" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="E927" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F927" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G927" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H927" s="5">
+        <v>100</v>
+      </c>
+      <c r="I927" s="7">
+        <v>7133</v>
+      </c>
+      <c r="J927" s="9">
+        <v>0</v>
+      </c>
+      <c r="K927" s="9">
+        <v>0</v>
+      </c>
+      <c r="L927" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M927" s="15">
+        <f t="shared" si="20"/>
+        <v>713300</v>
+      </c>
+      <c r="N927" s="19">
+        <v>59900</v>
+      </c>
+    </row>
+    <row r="928" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A928" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B928" s="4">
+        <v>46153</v>
+      </c>
+      <c r="C928" s="5">
+        <v>6965</v>
+      </c>
+      <c r="D928" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="E928" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F928" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G928" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H928" s="5">
+        <v>100</v>
+      </c>
+      <c r="I928" s="7">
+        <v>2113</v>
+      </c>
+      <c r="J928" s="9">
+        <v>0</v>
+      </c>
+      <c r="K928" s="9">
+        <v>0</v>
+      </c>
+      <c r="L928" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M928" s="15">
+        <f t="shared" si="20"/>
+        <v>211300</v>
+      </c>
+      <c r="N928" s="19">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="929" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A929" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B929" s="4">
+        <v>46153</v>
+      </c>
+      <c r="C929" s="5">
+        <v>8316</v>
+      </c>
+      <c r="D929" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E929" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F929" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G929" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H929" s="5">
+        <v>100</v>
+      </c>
+      <c r="I929" s="7">
+        <v>5654</v>
+      </c>
+      <c r="J929" s="9">
+        <v>0</v>
+      </c>
+      <c r="K929" s="9">
+        <v>0</v>
+      </c>
+      <c r="L929" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M929" s="15">
+        <f t="shared" si="20"/>
+        <v>565400</v>
+      </c>
+      <c r="N929" s="19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="930" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A930" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B930" s="4">
+        <v>46153</v>
+      </c>
+      <c r="C930" s="5">
+        <v>8766</v>
+      </c>
+      <c r="D930" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E930" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F930" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G930" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H930" s="5">
+        <v>100</v>
+      </c>
+      <c r="I930" s="7">
+        <v>7248</v>
+      </c>
+      <c r="J930" s="9">
+        <v>0</v>
+      </c>
+      <c r="K930" s="9">
+        <v>0</v>
+      </c>
+      <c r="L930" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M930" s="15">
+        <f t="shared" si="20"/>
+        <v>724800</v>
+      </c>
+      <c r="N930" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="931" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A931" s="4">
+        <v>46150</v>
+      </c>
+      <c r="B931" s="4">
+        <v>46154</v>
+      </c>
+      <c r="C931" s="5">
+        <v>6098</v>
+      </c>
+      <c r="D931" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="E931" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F931" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G931" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H931" s="5">
+        <v>100</v>
+      </c>
+      <c r="I931" s="7">
+        <v>7832</v>
+      </c>
+      <c r="J931" s="9">
+        <v>0</v>
+      </c>
+      <c r="K931" s="9">
+        <v>0</v>
+      </c>
+      <c r="L931" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M931" s="15">
+        <f t="shared" si="20"/>
+        <v>783200</v>
+      </c>
+      <c r="N931" s="19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="932" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A932" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B932" s="4">
+        <v>46156</v>
+      </c>
+      <c r="C932" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D932" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E932" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F932" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G932" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H932" s="5">
+        <v>200</v>
+      </c>
+      <c r="I932" s="7">
+        <v>1749</v>
+      </c>
+      <c r="J932" s="9">
+        <v>0</v>
+      </c>
+      <c r="K932" s="9">
+        <v>0</v>
+      </c>
+      <c r="L932" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M932" s="15">
+        <f t="shared" si="20"/>
+        <v>349800</v>
+      </c>
+      <c r="N932" s="19">
+        <v>68700</v>
+      </c>
+    </row>
+    <row r="933" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A933" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B933" s="4">
+        <v>46156</v>
+      </c>
+      <c r="C933" s="5">
+        <v>6232</v>
+      </c>
+      <c r="D933" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="E933" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F933" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G933" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H933" s="5">
+        <v>100</v>
+      </c>
+      <c r="I933" s="7">
+        <v>3250</v>
+      </c>
+      <c r="J933" s="9">
+        <v>0</v>
+      </c>
+      <c r="K933" s="9">
+        <v>0</v>
+      </c>
+      <c r="L933" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M933" s="15">
+        <f t="shared" si="20"/>
+        <v>325000</v>
+      </c>
+      <c r="N933" s="19">
+        <v>66500</v>
       </c>
     </row>
   </sheetData>

--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="552" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A48A877C-DF71-401F-B68F-82B4653DABEE}"/>
+  <xr:revisionPtr revIDLastSave="574" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{316413CE-8AEF-4166-BDD2-60043540D671}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">国内株式_信用!$A$1:$AA$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">国内株式_特定!$A$1:$N$852</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">国内株式_特定_配当!$A$1:$K$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">投資信託!$A$1:$K$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">投資信託!$A$1:$K$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">米国株式!$A$1:$S$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">米国株式_配当!$A$1:$K$74</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7199" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7275" uniqueCount="465">
   <si>
     <t>約定日</t>
   </si>
@@ -2068,6 +2068,13 @@
   <si>
     <t>三菱電機</t>
   </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ダイキン工業</t>
+  </si>
 </sst>
 </file>
 
@@ -2954,16 +2961,22 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2985,12 +2998,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3286,31 +3293,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="59" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>216</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55" t="s">
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59" t="s">
         <v>218</v>
       </c>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="63" t="s">
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="65" t="s">
         <v>302</v>
       </c>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="65"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="67"/>
       <c r="S1" s="37" t="s">
         <v>219</v>
       </c>
@@ -3322,50 +3329,50 @@
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57" t="s">
+      <c r="C2" s="55"/>
+      <c r="D2" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57" t="s">
+      <c r="G2" s="55"/>
+      <c r="H2" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="L2" s="57"/>
-      <c r="M2" s="58" t="s">
+      <c r="L2" s="55"/>
+      <c r="M2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="O2" s="61" t="s">
+      <c r="O2" s="63" t="s">
         <v>212</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="58" t="s">
+      <c r="P2" s="64"/>
+      <c r="Q2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="R2" s="60" t="s">
+      <c r="R2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="S2" s="59" t="s">
+      <c r="S2" s="61" t="s">
         <v>214</v>
       </c>
       <c r="U2" s="49">
@@ -3373,7 +3380,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3383,38 +3390,38 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="57"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
       <c r="K3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
       <c r="O3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="P3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="59"/>
-      <c r="U3" s="55" t="s">
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="61"/>
+      <c r="U3" s="59" t="s">
         <v>363</v>
       </c>
-      <c r="V3" s="55"/>
+      <c r="V3" s="59"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="34" t="s">
@@ -3438,7 +3445,7 @@
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>10577223</v>
+        <v>10639223</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
@@ -3446,15 +3453,15 @@
       </c>
       <c r="H4" s="20">
         <f>SUM(H5:H100)</f>
-        <v>829290</v>
+        <v>836040</v>
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>7247734</v>
+        <v>7316484</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>5775356.8378999997</v>
+        <v>5830140.2753999997</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -3490,13 +3497,13 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>8846429.0928499997</v>
-      </c>
-      <c r="U4" s="56">
+        <v>8901212.5303499997</v>
+      </c>
+      <c r="U4" s="60">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.5041095890410956</v>
-      </c>
-      <c r="V4" s="56"/>
+        <v>5.5561643835616437</v>
+      </c>
+      <c r="V4" s="60"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="34" t="s">
@@ -3555,11 +3562,11 @@
         <v>-68778</v>
       </c>
       <c r="O5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2021/1/1",投資信託!$B$2:$B$1029,"&lt;=2021/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2021/1/1",投資信託!$B$2:$B$1031,"&lt;=2021/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
         <v>7366</v>
       </c>
       <c r="P5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2021/1/1",投資信託!$B$2:$B$1029,"&lt;=2021/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2021/1/1",投資信託!$B$2:$B$1031,"&lt;=2021/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
         <v>-1498</v>
       </c>
       <c r="Q5" s="35">
@@ -3632,11 +3639,11 @@
         <v>-106573</v>
       </c>
       <c r="O6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2022/1/1",投資信託!$B$2:$B$1029,"&lt;=2022/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2022/1/1",投資信託!$B$2:$B$1031,"&lt;=2022/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2022/1/1",投資信託!$B$2:$B$1029,"&lt;=2022/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2022/1/1",投資信託!$B$2:$B$1031,"&lt;=2022/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q6" s="35">
@@ -3709,11 +3716,11 @@
         <v>-50703</v>
       </c>
       <c r="O7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2023/1/1",投資信託!$B$2:$B$1029,"&lt;=2023/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2023/1/1",投資信託!$B$2:$B$1031,"&lt;=2023/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2023/1/1",投資信託!$B$2:$B$1029,"&lt;=2023/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2023/1/1",投資信託!$B$2:$B$1031,"&lt;=2023/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q7" s="35">
@@ -3786,11 +3793,11 @@
         <v>-247960</v>
       </c>
       <c r="O8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2024/1/1",投資信託!$B$2:$B$1029,"&lt;=2024/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2024/1/1",投資信託!$B$2:$B$1031,"&lt;=2024/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2024/1/1",投資信託!$B$2:$B$1029,"&lt;=2024/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2024/1/1",投資信託!$B$2:$B$1031,"&lt;=2024/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q8" s="35">
@@ -3863,11 +3870,11 @@
         <v>8063.3251500000006</v>
       </c>
       <c r="O9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2025/1/1",投資信託!$B$2:$B$1029,"&lt;=2025/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2025/1/1",投資信託!$B$2:$B$1031,"&lt;=2025/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
         <v>185421</v>
       </c>
       <c r="P9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2025/1/1",投資信託!$B$2:$B$1029,"&lt;=2025/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2025/1/1",投資信託!$B$2:$B$1031,"&lt;=2025/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
         <v>-1071</v>
       </c>
       <c r="Q9" s="35">
@@ -3905,7 +3912,7 @@
       </c>
       <c r="F10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
-        <v>2930830</v>
+        <v>2992830</v>
       </c>
       <c r="G10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
@@ -3913,15 +3920,15 @@
       </c>
       <c r="H10" s="19">
         <f>SUMIFS(国内株式_特定_配当!$H$2:$H$999,国内株式_特定_配当!$A$2:$A$999,"&gt;=2026/1/1",国内株式_特定_配当!$A$2:$A$999,"&lt;=2026/12/31")</f>
-        <v>27135</v>
+        <v>33885</v>
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>2224485</v>
+        <v>2293235</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>1772580.87225</v>
+        <v>1827364.30975</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -3940,11 +3947,11 @@
         <v>207252.71650000001</v>
       </c>
       <c r="O10" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2026/1/1",投資信託!$B$2:$B$1029,"&lt;=2026/12/31",投資信託!$K$2:$K$1029,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2026/1/1",投資信託!$B$2:$B$1031,"&lt;=2026/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P10" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1029,投資信託!$B$2:$B$1029,"&gt;=2026/1/1",投資信託!$B$2:$B$1029,"&lt;=2026/12/31",投資信託!$K$2:$K$1029,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2026/1/1",投資信託!$B$2:$B$1031,"&lt;=2026/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="35">
@@ -3957,7 +3964,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>1988433.5887500001</v>
+        <v>2043217.0262500001</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -3971,11 +3978,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F2:G2"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="H2:H3"/>
@@ -3991,6 +3993,11 @@
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6780,49 +6787,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>416</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
       <c r="K1" s="69" t="s">
         <v>219</v>
       </c>
       <c r="L1" s="69"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="57"/>
+      <c r="C2" s="55"/>
       <c r="D2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="57"/>
+      <c r="G2" s="55"/>
       <c r="H2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="59" t="s">
+      <c r="K2" s="61" t="s">
         <v>214</v>
       </c>
       <c r="L2" s="70" t="s">
@@ -6836,18 +6843,18 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="61"/>
       <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -12317,7 +12324,7 @@
       <c r="E61" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="F61" s="72">
+      <c r="F61" s="9">
         <v>34</v>
       </c>
       <c r="G61" s="5">
@@ -12356,7 +12363,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O933"/>
+  <dimension ref="A1:O945"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -51647,7 +51654,7 @@
         <v>31</v>
       </c>
       <c r="M873" s="15">
-        <f t="shared" ref="M873:M933" si="20">IF(G873="買付",H873*I873+SUM(J873:K873),H873*I873-SUM(J873:K873))</f>
+        <f t="shared" ref="M873:M937" si="20">IF(G873="買付",H873*I873+SUM(J873:K873),H873*I873-SUM(J873:K873))</f>
         <v>111220</v>
       </c>
       <c r="N873" s="19">
@@ -54354,6 +54361,546 @@
       </c>
       <c r="N933" s="19">
         <v>66500</v>
+      </c>
+    </row>
+    <row r="934" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A934" s="4">
+        <v>46156</v>
+      </c>
+      <c r="B934" s="4">
+        <v>46160</v>
+      </c>
+      <c r="C934" s="5">
+        <v>5803</v>
+      </c>
+      <c r="D934" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E934" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F934" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G934" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H934" s="5">
+        <v>100</v>
+      </c>
+      <c r="I934" s="7">
+        <v>7855</v>
+      </c>
+      <c r="J934" s="9">
+        <v>0</v>
+      </c>
+      <c r="K934" s="9">
+        <v>0</v>
+      </c>
+      <c r="L934" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="M934" s="15">
+        <f t="shared" si="20"/>
+        <v>785500</v>
+      </c>
+      <c r="N934" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="935" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A935" s="4">
+        <v>46156</v>
+      </c>
+      <c r="B935" s="4">
+        <v>46160</v>
+      </c>
+      <c r="C935" s="5">
+        <v>6324</v>
+      </c>
+      <c r="D935" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E935" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F935" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G935" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H935" s="5">
+        <v>100</v>
+      </c>
+      <c r="I935" s="7">
+        <v>6770</v>
+      </c>
+      <c r="J935" s="9">
+        <v>0</v>
+      </c>
+      <c r="K935" s="9">
+        <v>0</v>
+      </c>
+      <c r="L935" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="M935" s="15">
+        <f t="shared" si="20"/>
+        <v>677000</v>
+      </c>
+      <c r="N935" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="936" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A936" s="4">
+        <v>46157</v>
+      </c>
+      <c r="B936" s="4">
+        <v>46161</v>
+      </c>
+      <c r="C936" s="5">
+        <v>6324</v>
+      </c>
+      <c r="D936" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E936" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F936" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G936" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H936" s="5">
+        <v>100</v>
+      </c>
+      <c r="I936" s="7">
+        <v>6950</v>
+      </c>
+      <c r="J936" s="9">
+        <v>0</v>
+      </c>
+      <c r="K936" s="9">
+        <v>0</v>
+      </c>
+      <c r="L936" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M936" s="15">
+        <f t="shared" si="20"/>
+        <v>695000</v>
+      </c>
+      <c r="N936" s="19">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="937" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A937" s="4">
+        <v>46164</v>
+      </c>
+      <c r="B937" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C937" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D937" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E937" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F937" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G937" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H937" s="5">
+        <v>100</v>
+      </c>
+      <c r="I937" s="7">
+        <v>2352</v>
+      </c>
+      <c r="J937" s="9">
+        <v>0</v>
+      </c>
+      <c r="K937" s="9">
+        <v>0</v>
+      </c>
+      <c r="L937" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M937" s="15">
+        <f t="shared" si="20"/>
+        <v>235200</v>
+      </c>
+      <c r="N937" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="938" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A938" s="4">
+        <v>46164</v>
+      </c>
+      <c r="B938" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C938" s="5">
+        <v>2802</v>
+      </c>
+      <c r="D938" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="E938" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F938" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G938" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H938" s="5">
+        <v>100</v>
+      </c>
+      <c r="I938" s="7">
+        <v>5269</v>
+      </c>
+      <c r="J938" s="9">
+        <v>0</v>
+      </c>
+      <c r="K938" s="9">
+        <v>0</v>
+      </c>
+      <c r="L938" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M938" s="15">
+        <f t="shared" ref="M938:M945" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
+        <v>526900</v>
+      </c>
+      <c r="N938" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="939" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A939" s="4">
+        <v>46164</v>
+      </c>
+      <c r="B939" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C939" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D939" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E939" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F939" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G939" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H939" s="5">
+        <v>100</v>
+      </c>
+      <c r="I939" s="7">
+        <v>57120</v>
+      </c>
+      <c r="J939" s="9">
+        <v>0</v>
+      </c>
+      <c r="K939" s="9">
+        <v>0</v>
+      </c>
+      <c r="L939" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M939" s="15">
+        <f t="shared" si="21"/>
+        <v>5712000</v>
+      </c>
+      <c r="N939" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="940" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A940" s="4">
+        <v>46164</v>
+      </c>
+      <c r="B940" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C940" s="5">
+        <v>3563</v>
+      </c>
+      <c r="D940" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="E940" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F940" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G940" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H940" s="5">
+        <v>100</v>
+      </c>
+      <c r="I940" s="7">
+        <v>10850</v>
+      </c>
+      <c r="J940" s="9">
+        <v>0</v>
+      </c>
+      <c r="K940" s="9">
+        <v>0</v>
+      </c>
+      <c r="L940" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M940" s="15">
+        <f t="shared" si="21"/>
+        <v>1085000</v>
+      </c>
+      <c r="N940" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="941" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A941" s="4">
+        <v>46164</v>
+      </c>
+      <c r="B941" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C941" s="5">
+        <v>4063</v>
+      </c>
+      <c r="D941" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E941" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F941" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G941" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H941" s="5">
+        <v>100</v>
+      </c>
+      <c r="I941" s="7">
+        <v>7010</v>
+      </c>
+      <c r="J941" s="9">
+        <v>0</v>
+      </c>
+      <c r="K941" s="9">
+        <v>0</v>
+      </c>
+      <c r="L941" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M941" s="15">
+        <f t="shared" si="21"/>
+        <v>701000</v>
+      </c>
+      <c r="N941" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="942" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A942" s="4">
+        <v>46164</v>
+      </c>
+      <c r="B942" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C942" s="5">
+        <v>6098</v>
+      </c>
+      <c r="D942" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="E942" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F942" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G942" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H942" s="5">
+        <v>100</v>
+      </c>
+      <c r="I942" s="7">
+        <v>9765</v>
+      </c>
+      <c r="J942" s="9">
+        <v>0</v>
+      </c>
+      <c r="K942" s="9">
+        <v>0</v>
+      </c>
+      <c r="L942" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M942" s="15">
+        <f t="shared" si="21"/>
+        <v>976500</v>
+      </c>
+      <c r="N942" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="943" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A943" s="4">
+        <v>46164</v>
+      </c>
+      <c r="B943" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C943" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D943" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E943" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F943" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G943" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H943" s="5">
+        <v>100</v>
+      </c>
+      <c r="I943" s="7">
+        <v>26985</v>
+      </c>
+      <c r="J943" s="9">
+        <v>0</v>
+      </c>
+      <c r="K943" s="9">
+        <v>0</v>
+      </c>
+      <c r="L943" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M943" s="15">
+        <f t="shared" si="21"/>
+        <v>2698500</v>
+      </c>
+      <c r="N943" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="944" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A944" s="4">
+        <v>46167</v>
+      </c>
+      <c r="B944" s="4">
+        <v>46169</v>
+      </c>
+      <c r="C944" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D944" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E944" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F944" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G944" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H944" s="5">
+        <v>100</v>
+      </c>
+      <c r="I944" s="7">
+        <v>2792</v>
+      </c>
+      <c r="J944" s="9">
+        <v>0</v>
+      </c>
+      <c r="K944" s="9">
+        <v>0</v>
+      </c>
+      <c r="L944" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M944" s="15">
+        <f t="shared" si="21"/>
+        <v>279200</v>
+      </c>
+      <c r="N944" s="19">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="945" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A945" s="4">
+        <v>46167</v>
+      </c>
+      <c r="B945" s="4">
+        <v>46169</v>
+      </c>
+      <c r="C945" s="5">
+        <v>6367</v>
+      </c>
+      <c r="D945" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E945" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F945" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G945" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H945" s="5">
+        <v>100</v>
+      </c>
+      <c r="I945" s="7">
+        <v>24400</v>
+      </c>
+      <c r="J945" s="9">
+        <v>0</v>
+      </c>
+      <c r="K945" s="9">
+        <v>0</v>
+      </c>
+      <c r="L945" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M945" s="15">
+        <f t="shared" si="21"/>
+        <v>2440000</v>
+      </c>
+      <c r="N945" s="19">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -54373,7 +54920,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -57419,11 +57966,11 @@
         <v>1218</v>
       </c>
       <c r="J80" s="19">
-        <f t="shared" ref="J80:J90" si="16">H80-I80</f>
+        <f t="shared" ref="J80:J91" si="16">H80-I80</f>
         <v>4782</v>
       </c>
       <c r="K80" s="19">
-        <f t="shared" ref="K80:K90" si="17">J80</f>
+        <f t="shared" ref="K80:K91" si="17">J80</f>
         <v>4782</v>
       </c>
     </row>
@@ -57678,7 +58225,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="19">
-        <f t="shared" ref="H87:H90" si="18">F87*G87</f>
+        <f t="shared" ref="H87:H91" si="18">F87*G87</f>
         <v>8000</v>
       </c>
       <c r="I87" s="19">
@@ -57805,6 +58352,44 @@
       <c r="K90" s="19">
         <f t="shared" si="17"/>
         <v>5738</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A91" s="4">
+        <v>46171</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" s="5">
+        <v>9602</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="F91" s="72">
+        <v>67.5</v>
+      </c>
+      <c r="G91" s="5">
+        <v>100</v>
+      </c>
+      <c r="H91" s="19">
+        <f t="shared" si="18"/>
+        <v>6750</v>
+      </c>
+      <c r="I91" s="19">
+        <v>1370</v>
+      </c>
+      <c r="J91" s="19">
+        <f t="shared" si="16"/>
+        <v>5380</v>
+      </c>
+      <c r="K91" s="19">
+        <f t="shared" si="17"/>
+        <v>5380</v>
       </c>
     </row>
   </sheetData>
@@ -64187,7 +64772,7 @@
   <sheetPr>
     <tabColor theme="2"/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -65146,13 +65731,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" s="4">
-        <v>46128</v>
+        <v>46155</v>
       </c>
       <c r="B28" s="4">
-        <v>45950</v>
+        <v>46161</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>377</v>
+        <v>282</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>159</v>
@@ -65167,13 +65752,13 @@
         <v>284</v>
       </c>
       <c r="H28" s="21">
-        <v>40242</v>
+        <v>8199</v>
       </c>
       <c r="I28" s="21">
-        <v>17395</v>
+        <v>36592</v>
       </c>
       <c r="J28" s="21">
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="K28" s="21">
         <v>0</v>
@@ -65181,10 +65766,10 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" s="4">
-        <v>45974</v>
+        <v>46128</v>
       </c>
       <c r="B29" s="4">
-        <v>45979</v>
+        <v>45950</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>377</v>
@@ -65202,10 +65787,10 @@
         <v>284</v>
       </c>
       <c r="H29" s="21">
-        <v>38038</v>
+        <v>40242</v>
       </c>
       <c r="I29" s="21">
-        <v>18403</v>
+        <v>17395</v>
       </c>
       <c r="J29" s="21">
         <v>70000</v>
@@ -65216,10 +65801,10 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" s="4">
-        <v>46006</v>
+        <v>45974</v>
       </c>
       <c r="B30" s="4">
-        <v>46009</v>
+        <v>45979</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>377</v>
@@ -65237,10 +65822,10 @@
         <v>284</v>
       </c>
       <c r="H30" s="21">
-        <v>37910</v>
+        <v>38038</v>
       </c>
       <c r="I30" s="21">
-        <v>18465</v>
+        <v>18403</v>
       </c>
       <c r="J30" s="21">
         <v>70000</v>
@@ -65251,10 +65836,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" s="4">
-        <v>46036</v>
+        <v>46006</v>
       </c>
       <c r="B31" s="4">
-        <v>46041</v>
+        <v>46009</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>377</v>
@@ -65272,10 +65857,10 @@
         <v>284</v>
       </c>
       <c r="H31" s="21">
-        <v>35338</v>
+        <v>37910</v>
       </c>
       <c r="I31" s="21">
-        <v>19809</v>
+        <v>18465</v>
       </c>
       <c r="J31" s="21">
         <v>70000</v>
@@ -65286,10 +65871,10 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" s="4">
-        <v>46066</v>
+        <v>46036</v>
       </c>
       <c r="B32" s="4">
-        <v>46071</v>
+        <v>46041</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>377</v>
@@ -65307,10 +65892,10 @@
         <v>284</v>
       </c>
       <c r="H32" s="21">
-        <v>34978</v>
+        <v>35338</v>
       </c>
       <c r="I32" s="21">
-        <v>20013</v>
+        <v>19809</v>
       </c>
       <c r="J32" s="21">
         <v>70000</v>
@@ -65321,10 +65906,10 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="4">
-        <v>46094</v>
+        <v>46066</v>
       </c>
       <c r="B33" s="4">
-        <v>46099</v>
+        <v>46071</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>377</v>
@@ -65342,10 +65927,10 @@
         <v>284</v>
       </c>
       <c r="H33" s="21">
-        <v>35624</v>
+        <v>34978</v>
       </c>
       <c r="I33" s="21">
-        <v>19650</v>
+        <v>20013</v>
       </c>
       <c r="J33" s="21">
         <v>70000</v>
@@ -65356,10 +65941,10 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="4">
-        <v>46126</v>
+        <v>46094</v>
       </c>
       <c r="B34" s="4">
-        <v>46129</v>
+        <v>46099</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>377</v>
@@ -65377,10 +65962,10 @@
         <v>284</v>
       </c>
       <c r="H34" s="21">
-        <v>33669</v>
+        <v>35624</v>
       </c>
       <c r="I34" s="21">
-        <v>20791</v>
+        <v>19650</v>
       </c>
       <c r="J34" s="21">
         <v>70000</v>
@@ -65391,34 +65976,34 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="4">
-        <v>44368</v>
+        <v>46126</v>
       </c>
       <c r="B35" s="4">
-        <v>44371</v>
+        <v>46129</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>163</v>
+        <v>377</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H35" s="8">
-        <v>21735</v>
-      </c>
-      <c r="I35" s="8">
-        <v>13803</v>
-      </c>
-      <c r="J35" s="8">
-        <v>30000</v>
+        <v>284</v>
+      </c>
+      <c r="H35" s="21">
+        <v>33669</v>
+      </c>
+      <c r="I35" s="21">
+        <v>20791</v>
+      </c>
+      <c r="J35" s="21">
+        <v>70000</v>
       </c>
       <c r="K35" s="21">
         <v>0</v>
@@ -65426,34 +66011,34 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="4">
-        <v>44377</v>
+        <v>46155</v>
       </c>
       <c r="B36" s="4">
-        <v>44382</v>
+        <v>46160</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>163</v>
+        <v>377</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H36" s="8">
-        <v>7034</v>
-      </c>
-      <c r="I36" s="8">
-        <v>14217</v>
-      </c>
-      <c r="J36" s="8">
-        <v>10000</v>
+        <v>284</v>
+      </c>
+      <c r="H36" s="21">
+        <v>32999</v>
+      </c>
+      <c r="I36" s="21">
+        <v>21213</v>
+      </c>
+      <c r="J36" s="21">
+        <v>70000</v>
       </c>
       <c r="K36" s="21">
         <v>0</v>
@@ -65461,10 +66046,10 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="4">
-        <v>44529</v>
+        <v>44368</v>
       </c>
       <c r="B37" s="4">
-        <v>44532</v>
+        <v>44371</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>163</v>
@@ -65476,28 +66061,30 @@
         <v>295</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G37" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H37" s="8">
-        <v>28769</v>
+        <v>21735</v>
       </c>
       <c r="I37" s="8">
-        <v>13383</v>
+        <v>13803</v>
       </c>
       <c r="J37" s="8">
-        <v>38502</v>
-      </c>
-      <c r="K37" s="19">
-        <v>-1498</v>
+        <v>30000</v>
+      </c>
+      <c r="K37" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="4">
-        <v>44403</v>
+        <v>44377</v>
       </c>
       <c r="B38" s="4">
-        <v>44406</v>
+        <v>44382</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>163</v>
@@ -65506,7 +66093,7 @@
         <v>159</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>30</v>
@@ -65515,10 +66102,10 @@
         <v>160</v>
       </c>
       <c r="H38" s="8">
-        <v>7310</v>
+        <v>7034</v>
       </c>
       <c r="I38" s="8">
-        <v>13681</v>
+        <v>14217</v>
       </c>
       <c r="J38" s="8">
         <v>10000</v>
@@ -65529,10 +66116,10 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="4">
-        <v>44525</v>
+        <v>44529</v>
       </c>
       <c r="B39" s="4">
-        <v>44530</v>
+        <v>44532</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>163</v>
@@ -65541,40 +66128,40 @@
         <v>159</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="8">
-        <v>7310</v>
+        <v>28769</v>
       </c>
       <c r="I39" s="8">
-        <v>13973</v>
+        <v>13383</v>
       </c>
       <c r="J39" s="8">
-        <v>10214</v>
+        <v>38502</v>
       </c>
       <c r="K39" s="19">
-        <v>214</v>
+        <v>-1498</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="4">
-        <v>44165</v>
+        <v>44403</v>
       </c>
       <c r="B40" s="4">
-        <v>44168</v>
+        <v>44406</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>295</v>
+        <v>67</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>30</v>
@@ -65583,13 +66170,13 @@
         <v>160</v>
       </c>
       <c r="H40" s="8">
-        <v>3846</v>
+        <v>7310</v>
       </c>
       <c r="I40" s="8">
-        <v>13000</v>
+        <v>13681</v>
       </c>
       <c r="J40" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K40" s="21">
         <v>0</v>
@@ -65597,45 +66184,43 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="4">
-        <v>44201</v>
+        <v>44525</v>
       </c>
       <c r="B41" s="4">
-        <v>44204</v>
+        <v>44530</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>295</v>
+        <v>67</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="G41" s="5"/>
       <c r="H41" s="8">
-        <v>7604</v>
+        <v>7310</v>
       </c>
       <c r="I41" s="8">
-        <v>13152</v>
+        <v>13973</v>
       </c>
       <c r="J41" s="8">
-        <v>10000</v>
-      </c>
-      <c r="K41" s="21">
-        <v>0</v>
+        <v>10214</v>
+      </c>
+      <c r="K41" s="19">
+        <v>214</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="4">
-        <v>44236</v>
+        <v>44165</v>
       </c>
       <c r="B42" s="4">
-        <v>44242</v>
+        <v>44168</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>158</v>
@@ -65653,13 +66238,13 @@
         <v>160</v>
       </c>
       <c r="H42" s="8">
-        <v>7041</v>
+        <v>3846</v>
       </c>
       <c r="I42" s="8">
-        <v>14202</v>
+        <v>13000</v>
       </c>
       <c r="J42" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K42" s="21">
         <v>0</v>
@@ -65667,10 +66252,10 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="4">
-        <v>44257</v>
+        <v>44201</v>
       </c>
       <c r="B43" s="4">
-        <v>44260</v>
+        <v>44204</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>158</v>
@@ -65688,10 +66273,10 @@
         <v>160</v>
       </c>
       <c r="H43" s="8">
-        <v>6947</v>
+        <v>7604</v>
       </c>
       <c r="I43" s="8">
-        <v>14394</v>
+        <v>13152</v>
       </c>
       <c r="J43" s="8">
         <v>10000</v>
@@ -65702,10 +66287,10 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="4">
-        <v>44295</v>
+        <v>44236</v>
       </c>
       <c r="B44" s="4">
-        <v>44300</v>
+        <v>44242</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>158</v>
@@ -65723,10 +66308,10 @@
         <v>160</v>
       </c>
       <c r="H44" s="8">
-        <v>6460</v>
+        <v>7041</v>
       </c>
       <c r="I44" s="8">
-        <v>15481</v>
+        <v>14202</v>
       </c>
       <c r="J44" s="8">
         <v>10000</v>
@@ -65737,10 +66322,10 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B45" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>158</v>
@@ -65758,13 +66343,13 @@
         <v>160</v>
       </c>
       <c r="H45" s="8">
-        <v>3167</v>
+        <v>6947</v>
       </c>
       <c r="I45" s="8">
-        <v>15789</v>
+        <v>14394</v>
       </c>
       <c r="J45" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K45" s="21">
         <v>0</v>
@@ -65772,10 +66357,10 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B46" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>158</v>
@@ -65793,10 +66378,10 @@
         <v>160</v>
       </c>
       <c r="H46" s="8">
-        <v>6263</v>
+        <v>6460</v>
       </c>
       <c r="I46" s="8">
-        <v>15967</v>
+        <v>15481</v>
       </c>
       <c r="J46" s="8">
         <v>10000</v>
@@ -65807,10 +66392,10 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" s="4">
-        <v>44377</v>
+        <v>44327</v>
       </c>
       <c r="B47" s="4">
-        <v>44382</v>
+        <v>44330</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>158</v>
@@ -65828,13 +66413,13 @@
         <v>160</v>
       </c>
       <c r="H47" s="8">
-        <v>6081</v>
+        <v>3167</v>
       </c>
       <c r="I47" s="8">
-        <v>16444</v>
+        <v>15789</v>
       </c>
       <c r="J47" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K47" s="21">
         <v>0</v>
@@ -65842,10 +66427,10 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="4">
-        <v>44921</v>
+        <v>44350</v>
       </c>
       <c r="B48" s="4">
-        <v>44924</v>
+        <v>44355</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>158</v>
@@ -65863,13 +66448,13 @@
         <v>160</v>
       </c>
       <c r="H48" s="8">
-        <v>24940</v>
+        <v>6263</v>
       </c>
       <c r="I48" s="8">
-        <v>17961</v>
+        <v>15967</v>
       </c>
       <c r="J48" s="8">
-        <v>44794</v>
+        <v>10000</v>
       </c>
       <c r="K48" s="21">
         <v>0</v>
@@ -65877,10 +66462,10 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" s="4">
-        <v>45243</v>
+        <v>44377</v>
       </c>
       <c r="B49" s="4">
-        <v>45246</v>
+        <v>44382</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>158</v>
@@ -65898,13 +66483,13 @@
         <v>160</v>
       </c>
       <c r="H49" s="8">
-        <v>590</v>
+        <v>6081</v>
       </c>
       <c r="I49" s="8">
-        <v>23925</v>
+        <v>16444</v>
       </c>
       <c r="J49" s="8">
-        <v>1410</v>
+        <v>10000</v>
       </c>
       <c r="K49" s="21">
         <v>0</v>
@@ -65912,10 +66497,10 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" s="4">
-        <v>45656</v>
+        <v>44921</v>
       </c>
       <c r="B50" s="4">
-        <v>45663</v>
+        <v>44924</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>158</v>
@@ -65927,15 +66512,19 @@
         <v>295</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H50" s="8">
+        <v>24940</v>
+      </c>
+      <c r="I50" s="8">
+        <v>17961</v>
+      </c>
+      <c r="J50" s="8">
+        <v>44794</v>
       </c>
       <c r="K50" s="21">
         <v>0</v>
@@ -65943,10 +66532,10 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" s="4">
-        <v>45772</v>
+        <v>45243</v>
       </c>
       <c r="B51" s="4">
-        <v>45778</v>
+        <v>45246</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>158</v>
@@ -65958,28 +66547,30 @@
         <v>295</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G51" s="5"/>
-      <c r="H51" s="21">
-        <v>69093</v>
-      </c>
-      <c r="I51" s="19">
-        <v>28502</v>
-      </c>
-      <c r="J51" s="19">
-        <v>196929</v>
+        <v>30</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H51" s="8">
+        <v>590</v>
+      </c>
+      <c r="I51" s="8">
+        <v>23925</v>
+      </c>
+      <c r="J51" s="8">
+        <v>1410</v>
       </c>
       <c r="K51" s="21">
-        <v>86850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" s="4">
-        <v>44404</v>
+        <v>45656</v>
       </c>
       <c r="B52" s="4">
-        <v>44407</v>
+        <v>45663</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>158</v>
@@ -65988,22 +66579,18 @@
         <v>159</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H52" s="8">
-        <v>11832</v>
-      </c>
-      <c r="I52" s="8">
-        <v>16903</v>
-      </c>
-      <c r="J52" s="8">
-        <v>20000</v>
+        <v>289</v>
+      </c>
+      <c r="G52" s="5"/>
+      <c r="H52" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9">
+        <v>0</v>
       </c>
       <c r="K52" s="21">
         <v>0</v>
@@ -66011,10 +66598,10 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" s="4">
-        <v>44435</v>
+        <v>45772</v>
       </c>
       <c r="B53" s="4">
-        <v>44440</v>
+        <v>45778</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>158</v>
@@ -66023,31 +66610,31 @@
         <v>159</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G53" s="5"/>
-      <c r="H53" s="8">
-        <v>11832</v>
-      </c>
-      <c r="I53" s="8">
-        <v>17067</v>
-      </c>
-      <c r="J53" s="8">
-        <v>20194</v>
-      </c>
-      <c r="K53" s="19">
-        <v>194</v>
+      <c r="H53" s="21">
+        <v>69093</v>
+      </c>
+      <c r="I53" s="19">
+        <v>28502</v>
+      </c>
+      <c r="J53" s="19">
+        <v>196929</v>
+      </c>
+      <c r="K53" s="21">
+        <v>86850</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" s="4">
-        <v>45656</v>
+        <v>44404</v>
       </c>
       <c r="B54" s="4">
-        <v>45663</v>
+        <v>44407</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>158</v>
@@ -66056,18 +66643,22 @@
         <v>159</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>294</v>
+        <v>67</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="G54" s="5"/>
-      <c r="H54" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H54" s="8">
+        <v>11832</v>
+      </c>
+      <c r="I54" s="8">
+        <v>16903</v>
+      </c>
+      <c r="J54" s="8">
+        <v>20000</v>
       </c>
       <c r="K54" s="21">
         <v>0</v>
@@ -66075,10 +66666,10 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" s="4">
-        <v>45824</v>
+        <v>44435</v>
       </c>
       <c r="B55" s="4">
-        <v>45827</v>
+        <v>44440</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>158</v>
@@ -66087,55 +66678,51 @@
         <v>159</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G55" s="5"/>
-      <c r="H55" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I55" s="19">
-        <v>31398</v>
-      </c>
-      <c r="J55" s="19">
-        <v>12076</v>
-      </c>
-      <c r="K55" s="21">
-        <v>-1071</v>
+      <c r="H55" s="8">
+        <v>11832</v>
+      </c>
+      <c r="I55" s="8">
+        <v>17067</v>
+      </c>
+      <c r="J55" s="8">
+        <v>20194</v>
+      </c>
+      <c r="K55" s="19">
+        <v>194</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" s="4">
-        <v>44188</v>
+        <v>45656</v>
       </c>
       <c r="B56" s="4">
-        <v>44193</v>
+        <v>45663</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H56" s="8">
-        <v>4490</v>
-      </c>
-      <c r="I56" s="8">
-        <v>22273</v>
-      </c>
-      <c r="J56" s="8">
-        <v>10000</v>
+        <v>296</v>
+      </c>
+      <c r="G56" s="5"/>
+      <c r="H56" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9">
+        <v>0</v>
       </c>
       <c r="K56" s="21">
         <v>0</v>
@@ -66143,45 +66730,43 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" s="4">
-        <v>44224</v>
+        <v>45824</v>
       </c>
       <c r="B57" s="4">
-        <v>44229</v>
+        <v>45827</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>295</v>
+        <v>68</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H57" s="8">
-        <v>2108</v>
-      </c>
-      <c r="I57" s="8">
-        <v>23721</v>
-      </c>
-      <c r="J57" s="8">
-        <v>5000</v>
+        <v>298</v>
+      </c>
+      <c r="G57" s="5"/>
+      <c r="H57" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I57" s="19">
+        <v>31398</v>
+      </c>
+      <c r="J57" s="19">
+        <v>12076</v>
       </c>
       <c r="K57" s="21">
-        <v>0</v>
+        <v>-1071</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" s="4">
-        <v>44257</v>
+        <v>44188</v>
       </c>
       <c r="B58" s="4">
-        <v>44260</v>
+        <v>44193</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>162</v>
@@ -66199,13 +66784,13 @@
         <v>160</v>
       </c>
       <c r="H58" s="8">
-        <v>1938</v>
+        <v>4490</v>
       </c>
       <c r="I58" s="8">
-        <v>25804</v>
+        <v>22273</v>
       </c>
       <c r="J58" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K58" s="21">
         <v>0</v>
@@ -66213,10 +66798,10 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" s="4">
-        <v>44295</v>
+        <v>44224</v>
       </c>
       <c r="B59" s="4">
-        <v>44300</v>
+        <v>44229</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>162</v>
@@ -66234,10 +66819,10 @@
         <v>160</v>
       </c>
       <c r="H59" s="8">
-        <v>1920</v>
+        <v>2108</v>
       </c>
       <c r="I59" s="8">
-        <v>26043</v>
+        <v>23721</v>
       </c>
       <c r="J59" s="8">
         <v>5000</v>
@@ -66248,10 +66833,10 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B60" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>162</v>
@@ -66269,13 +66854,13 @@
         <v>160</v>
       </c>
       <c r="H60" s="8">
-        <v>4166</v>
+        <v>1938</v>
       </c>
       <c r="I60" s="8">
-        <v>24007</v>
+        <v>25804</v>
       </c>
       <c r="J60" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K60" s="21">
         <v>0</v>
@@ -66283,10 +66868,10 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B61" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>162</v>
@@ -66304,10 +66889,10 @@
         <v>160</v>
       </c>
       <c r="H61" s="8">
-        <v>1983</v>
+        <v>1920</v>
       </c>
       <c r="I61" s="8">
-        <v>25216</v>
+        <v>26043</v>
       </c>
       <c r="J61" s="8">
         <v>5000</v>
@@ -66318,10 +66903,10 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62" s="4">
-        <v>44362</v>
+        <v>44327</v>
       </c>
       <c r="B62" s="4">
-        <v>44365</v>
+        <v>44330</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>162</v>
@@ -66333,31 +66918,33 @@
         <v>295</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G62" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H62" s="8">
-        <v>16605</v>
+        <v>4166</v>
       </c>
       <c r="I62" s="8">
-        <v>26019</v>
+        <v>24007</v>
       </c>
       <c r="J62" s="8">
-        <v>43205</v>
-      </c>
-      <c r="K62" s="19">
-        <v>3205</v>
+        <v>10000</v>
+      </c>
+      <c r="K62" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63" s="4">
-        <v>44187</v>
+        <v>44350</v>
       </c>
       <c r="B63" s="4">
-        <v>44190</v>
+        <v>44355</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>159</v>
@@ -66372,27 +66959,27 @@
         <v>160</v>
       </c>
       <c r="H63" s="8">
-        <v>6447</v>
+        <v>1983</v>
       </c>
       <c r="I63" s="8">
-        <v>15511</v>
+        <v>25216</v>
       </c>
       <c r="J63" s="8">
-        <v>10000</v>
-      </c>
-      <c r="K63" s="19">
+        <v>5000</v>
+      </c>
+      <c r="K63" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64" s="4">
-        <v>44224</v>
+        <v>44362</v>
       </c>
       <c r="B64" s="4">
-        <v>44229</v>
+        <v>44365</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>159</v>
@@ -66401,30 +66988,28 @@
         <v>295</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="G64" s="5"/>
       <c r="H64" s="8">
-        <v>3093</v>
+        <v>16605</v>
       </c>
       <c r="I64" s="8">
-        <v>16167</v>
+        <v>26019</v>
       </c>
       <c r="J64" s="8">
-        <v>5000</v>
+        <v>43205</v>
       </c>
       <c r="K64" s="19">
-        <v>0</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A65" s="4">
-        <v>44257</v>
+        <v>44187</v>
       </c>
       <c r="B65" s="4">
-        <v>44260</v>
+        <v>44190</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>161</v>
@@ -66442,13 +67027,13 @@
         <v>160</v>
       </c>
       <c r="H65" s="8">
-        <v>2978</v>
+        <v>6447</v>
       </c>
       <c r="I65" s="8">
-        <v>16792</v>
+        <v>15511</v>
       </c>
       <c r="J65" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K65" s="19">
         <v>0</v>
@@ -66456,10 +67041,10 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66" s="4">
-        <v>44295</v>
+        <v>44224</v>
       </c>
       <c r="B66" s="4">
-        <v>44300</v>
+        <v>44229</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>161</v>
@@ -66477,10 +67062,10 @@
         <v>160</v>
       </c>
       <c r="H66" s="8">
-        <v>2810</v>
+        <v>3093</v>
       </c>
       <c r="I66" s="8">
-        <v>17792</v>
+        <v>16167</v>
       </c>
       <c r="J66" s="8">
         <v>5000</v>
@@ -66491,10 +67076,10 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B67" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>161</v>
@@ -66512,10 +67097,10 @@
         <v>160</v>
       </c>
       <c r="H67" s="8">
-        <v>2903</v>
+        <v>2978</v>
       </c>
       <c r="I67" s="8">
-        <v>17225</v>
+        <v>16792</v>
       </c>
       <c r="J67" s="8">
         <v>5000</v>
@@ -66526,10 +67111,10 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B68" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>161</v>
@@ -66547,10 +67132,10 @@
         <v>160</v>
       </c>
       <c r="H68" s="8">
-        <v>2819</v>
+        <v>2810</v>
       </c>
       <c r="I68" s="8">
-        <v>17736</v>
+        <v>17792</v>
       </c>
       <c r="J68" s="8">
         <v>5000</v>
@@ -66561,10 +67146,10 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69" s="4">
-        <v>44362</v>
+        <v>44327</v>
       </c>
       <c r="B69" s="4">
-        <v>44365</v>
+        <v>44330</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>161</v>
@@ -66576,37 +67161,39 @@
         <v>295</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G69" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H69" s="8">
-        <v>21050</v>
+        <v>2903</v>
       </c>
       <c r="I69" s="8">
-        <v>18410</v>
+        <v>17225</v>
       </c>
       <c r="J69" s="8">
-        <v>38753</v>
+        <v>5000</v>
       </c>
       <c r="K69" s="19">
-        <v>3753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A70" s="4">
-        <v>45243</v>
+        <v>44350</v>
       </c>
       <c r="B70" s="4">
-        <v>45247</v>
+        <v>44355</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>30</v>
@@ -66614,56 +67201,124 @@
       <c r="G70" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="H70" s="19">
-        <v>180143</v>
-      </c>
-      <c r="I70" s="19">
-        <v>12456</v>
+      <c r="H70" s="8">
+        <v>2819</v>
+      </c>
+      <c r="I70" s="8">
+        <v>17736</v>
       </c>
       <c r="J70" s="8">
-        <v>224386</v>
-      </c>
-      <c r="K70" s="21">
+        <v>5000</v>
+      </c>
+      <c r="K70" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A71" s="4">
-        <v>45664</v>
+        <v>44362</v>
       </c>
       <c r="B71" s="4">
-        <v>45671</v>
+        <v>44365</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G71" s="5"/>
-      <c r="H71" s="21">
+      <c r="H71" s="8">
+        <v>21050</v>
+      </c>
+      <c r="I71" s="8">
+        <v>18410</v>
+      </c>
+      <c r="J71" s="8">
+        <v>38753</v>
+      </c>
+      <c r="K71" s="19">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A72" s="4">
+        <v>45243</v>
+      </c>
+      <c r="B72" s="4">
+        <v>45247</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H72" s="19">
         <v>180143</v>
       </c>
-      <c r="I71" s="21">
+      <c r="I72" s="19">
+        <v>12456</v>
+      </c>
+      <c r="J72" s="8">
+        <v>224386</v>
+      </c>
+      <c r="K72" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A73" s="4">
+        <v>45664</v>
+      </c>
+      <c r="B73" s="4">
+        <v>45671</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G73" s="5"/>
+      <c r="H73" s="21">
+        <v>180143</v>
+      </c>
+      <c r="I73" s="21">
         <v>15148</v>
       </c>
-      <c r="J71" s="21">
+      <c r="J73" s="21">
         <v>272881</v>
       </c>
-      <c r="K71" s="19">
+      <c r="K73" s="19">
         <v>48494</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K61" xr:uid="{00000000-0009-0000-0000-000007000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K71">
-      <sortCondition ref="C1:C61"/>
+  <autoFilter ref="A1:K63" xr:uid="{00000000-0009-0000-0000-000007000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K73">
+      <sortCondition ref="C1:C63"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18"/>

--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="574" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{316413CE-8AEF-4166-BDD2-60043540D671}"/>
+  <xr:revisionPtr revIDLastSave="594" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B1D374D-DC42-40A3-8E0C-69F9EFAB9787}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ_日本" sheetId="10" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7275" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7386" uniqueCount="472">
   <si>
     <t>約定日</t>
   </si>
@@ -2075,6 +2075,34 @@
   <si>
     <t>ダイキン工業</t>
   </si>
+  <si>
+    <t>双日</t>
+    <rPh sb="0" eb="2">
+      <t>ソウジツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ＮＦＪ－ＲＥＩＴ</t>
+  </si>
+  <si>
+    <t>サイバーセキュリティクラウド</t>
+  </si>
+  <si>
+    <t>ミネベアミツミ</t>
+  </si>
+  <si>
+    <t>SPCX</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>SPACEX</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="18"/>
+  </si>
 </sst>
 </file>
 
@@ -3380,7 +3408,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46186</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3437,31 +3465,31 @@
       </c>
       <c r="D4" s="20">
         <f>SUM(D5:D100)</f>
-        <v>458895</v>
+        <v>477495</v>
       </c>
       <c r="E4" s="35">
         <f>SUM(B4:D4)</f>
-        <v>3178195</v>
+        <v>3196795</v>
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>10639223</v>
+        <v>12277423</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
-        <v>-4158779</v>
+        <v>-4570437</v>
       </c>
       <c r="H4" s="20">
         <f>SUM(H5:H100)</f>
-        <v>836040</v>
+        <v>850810</v>
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>7316484</v>
+        <v>8557796</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>5830140.2753999997</v>
+        <v>6819279.7425999995</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -3497,11 +3525,11 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>8901212.5303499997</v>
+        <v>9908951.9975499995</v>
       </c>
       <c r="U4" s="60">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.5561643835616437</v>
+        <v>5.5917808219178085</v>
       </c>
       <c r="V4" s="60"/>
     </row>
@@ -3518,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="19">
-        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1003,国内株式_NISA_配当!$A$2:$A$1003,"&gt;=2021/1/1",国内株式_NISA_配当!$A$2:$A$1003,"&lt;=2021/12/31")</f>
+        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1004,国内株式_NISA_配当!$A$2:$A$1004,"&gt;=2021/1/1",国内株式_NISA_配当!$A$2:$A$1004,"&lt;=2021/12/31")</f>
         <v>27700</v>
       </c>
       <c r="E5" s="35">
@@ -3595,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="19">
-        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1003,国内株式_NISA_配当!$A$2:$A$1003,"&gt;=2022/1/1",国内株式_NISA_配当!$A$2:$A$1003,"&lt;=2022/12/31")</f>
+        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1004,国内株式_NISA_配当!$A$2:$A$1004,"&gt;=2022/1/1",国内株式_NISA_配当!$A$2:$A$1004,"&lt;=2022/12/31")</f>
         <v>35720</v>
       </c>
       <c r="E6" s="35">
@@ -3672,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="19">
-        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1003,国内株式_NISA_配当!$A$2:$A$1003,"&gt;=2023/1/1",国内株式_NISA_配当!$A$2:$A$1003,"&lt;=2023/12/31")</f>
+        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1004,国内株式_NISA_配当!$A$2:$A$1004,"&gt;=2023/1/1",国内株式_NISA_配当!$A$2:$A$1004,"&lt;=2023/12/31")</f>
         <v>88900</v>
       </c>
       <c r="E7" s="35">
@@ -3749,7 +3777,7 @@
         <v>-49300</v>
       </c>
       <c r="D8" s="19">
-        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1003,国内株式_NISA_配当!$A$2:$A$1003,"&gt;=2024/1/1",国内株式_NISA_配当!$A$2:$A$1003,"&lt;=2024/12/31")</f>
+        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1004,国内株式_NISA_配当!$A$2:$A$1004,"&gt;=2024/1/1",国内株式_NISA_配当!$A$2:$A$1004,"&lt;=2024/12/31")</f>
         <v>136475</v>
       </c>
       <c r="E8" s="35">
@@ -3826,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="19">
-        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1003,国内株式_NISA_配当!$A$2:$A$1003,"&gt;=2025/1/1",国内株式_NISA_配当!$A$2:$A$1003,"&lt;=2025/12/31")</f>
+        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1004,国内株式_NISA_配当!$A$2:$A$1004,"&gt;=2025/1/1",国内株式_NISA_配当!$A$2:$A$1004,"&lt;=2025/12/31")</f>
         <v>161500</v>
       </c>
       <c r="E9" s="35">
@@ -3903,32 +3931,32 @@
         <v>0</v>
       </c>
       <c r="D10" s="19">
-        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1003,国内株式_NISA_配当!$A$2:$A$1003,"&gt;=2026/1/1",国内株式_NISA_配当!$A$2:$A$1003,"&lt;=2026/12/31")</f>
-        <v>8600</v>
+        <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1004,国内株式_NISA_配当!$A$2:$A$1004,"&gt;=2026/1/1",国内株式_NISA_配当!$A$2:$A$1004,"&lt;=2026/12/31")</f>
+        <v>27200</v>
       </c>
       <c r="E10" s="35">
         <f t="shared" si="7"/>
-        <v>8600</v>
+        <v>27200</v>
       </c>
       <c r="F10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
-        <v>2992830</v>
+        <v>4631030</v>
       </c>
       <c r="G10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
-        <v>-733480</v>
+        <v>-1145138</v>
       </c>
       <c r="H10" s="19">
         <f>SUMIFS(国内株式_特定_配当!$H$2:$H$999,国内株式_特定_配当!$A$2:$A$999,"&gt;=2026/1/1",国内株式_特定_配当!$A$2:$A$999,"&lt;=2026/12/31")</f>
-        <v>33885</v>
+        <v>48655</v>
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>2293235</v>
+        <v>3534547</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>1827364.30975</v>
+        <v>2816503.7769499999</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -3964,7 +3992,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>2043217.0262500001</v>
+        <v>3050956.49345</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -10017,7 +10045,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -10089,18 +10117,18 @@
         <v>100</v>
       </c>
       <c r="H2" s="19">
-        <f t="shared" ref="H2:H34" si="0">F2*G2</f>
+        <f t="shared" ref="H2:H33" si="0">F2*G2</f>
         <v>1600</v>
       </c>
       <c r="I2" s="19">
         <v>0</v>
       </c>
       <c r="J2" s="19">
-        <f t="shared" ref="J2:J34" si="1">H2-I2</f>
+        <f t="shared" ref="J2:J33" si="1">H2-I2</f>
         <v>1600</v>
       </c>
       <c r="K2" s="19">
-        <f t="shared" ref="K2:K34" si="2">J2</f>
+        <f t="shared" ref="K2:K33" si="2">J2</f>
         <v>1600</v>
       </c>
     </row>
@@ -10182,45 +10210,45 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="4">
-        <v>45001</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D5" s="5">
-        <v>4324</v>
+        <v>4204</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>182</v>
+        <v>300</v>
       </c>
       <c r="F5" s="9">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="G5" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="0"/>
-        <v>8500</v>
+        <v>20000</v>
       </c>
       <c r="I5" s="19">
         <v>0</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="1"/>
-        <v>8500</v>
+        <v>20000</v>
       </c>
       <c r="K5" s="19">
         <f t="shared" si="2"/>
-        <v>8500</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="4">
-        <v>45365</v>
+        <v>45001</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>50</v>
@@ -10235,30 +10263,30 @@
         <v>182</v>
       </c>
       <c r="F6" s="9">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="G6" s="5">
         <v>100</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="0"/>
-        <v>6100</v>
+        <v>8500</v>
       </c>
       <c r="I6" s="19">
         <v>0</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="1"/>
-        <v>6100</v>
+        <v>8500</v>
       </c>
       <c r="K6" s="19">
         <f t="shared" si="2"/>
-        <v>6100</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="4">
-        <v>45547</v>
+        <v>45365</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>50</v>
@@ -10273,30 +10301,30 @@
         <v>182</v>
       </c>
       <c r="F7" s="9">
-        <v>69.75</v>
+        <v>61</v>
       </c>
       <c r="G7" s="5">
         <v>100</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="0"/>
-        <v>6975</v>
+        <v>6100</v>
       </c>
       <c r="I7" s="19">
         <v>0</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="1"/>
-        <v>6975</v>
+        <v>6100</v>
       </c>
       <c r="K7" s="19">
         <f t="shared" si="2"/>
-        <v>6975</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="4">
-        <v>44742</v>
+        <v>45547</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>50</v>
@@ -10305,36 +10333,36 @@
         <v>258</v>
       </c>
       <c r="D8" s="5">
-        <v>4502</v>
+        <v>4324</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>42</v>
+        <v>182</v>
       </c>
       <c r="F8" s="9">
-        <v>90</v>
+        <v>69.75</v>
       </c>
       <c r="G8" s="5">
         <v>100</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="0"/>
-        <v>9000</v>
+        <v>6975</v>
       </c>
       <c r="I8" s="19">
-        <v>1828</v>
+        <v>0</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="1"/>
-        <v>7172</v>
+        <v>6975</v>
       </c>
       <c r="K8" s="19">
         <f t="shared" si="2"/>
-        <v>7172</v>
+        <v>6975</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="4">
-        <v>44896</v>
+        <v>44742</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>50</v>
@@ -10359,20 +10387,20 @@
         <v>9000</v>
       </c>
       <c r="I9" s="19">
-        <v>0</v>
+        <v>1828</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="1"/>
-        <v>9000</v>
+        <v>7172</v>
       </c>
       <c r="K9" s="19">
         <f t="shared" si="2"/>
-        <v>9000</v>
+        <v>7172</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="4">
-        <v>45106</v>
+        <v>44896</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>50</v>
@@ -10410,7 +10438,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="4">
-        <v>45261</v>
+        <v>45106</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>50</v>
@@ -10425,36 +10453,36 @@
         <v>42</v>
       </c>
       <c r="F11" s="9">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G11" s="5">
         <v>100</v>
       </c>
       <c r="H11" s="19">
         <f t="shared" si="0"/>
-        <v>9400</v>
+        <v>9000</v>
       </c>
       <c r="I11" s="19">
         <v>0</v>
       </c>
       <c r="J11" s="19">
         <f t="shared" si="1"/>
-        <v>9400</v>
+        <v>9000</v>
       </c>
       <c r="K11" s="19">
         <f t="shared" si="2"/>
-        <v>9400</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" s="4">
-        <v>45470</v>
+        <v>45261</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D12" s="5">
         <v>4502</v>
@@ -10492,7 +10520,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D13" s="5">
         <v>4502</v>
@@ -10524,13 +10552,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
-        <v>45628</v>
+        <v>45470</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D14" s="5">
         <v>4502</v>
@@ -10539,25 +10567,25 @@
         <v>42</v>
       </c>
       <c r="F14" s="9">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G14" s="5">
         <v>100</v>
       </c>
       <c r="H14" s="19">
         <f t="shared" si="0"/>
-        <v>9800</v>
+        <v>9400</v>
       </c>
       <c r="I14" s="19">
         <v>0</v>
       </c>
       <c r="J14" s="19">
         <f t="shared" si="1"/>
-        <v>9800</v>
+        <v>9400</v>
       </c>
       <c r="K14" s="19">
         <f t="shared" si="2"/>
-        <v>9800</v>
+        <v>9400</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
@@ -10568,7 +10596,7 @@
         <v>50</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D15" s="5">
         <v>4502</v>
@@ -10600,13 +10628,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
-        <v>45834</v>
+        <v>45628</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D16" s="5">
         <v>4502</v>
@@ -10644,7 +10672,7 @@
         <v>50</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D17" s="5">
         <v>4502</v>
@@ -10676,7 +10704,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
-        <v>44372</v>
+        <v>45834</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>50</v>
@@ -10685,36 +10713,36 @@
         <v>258</v>
       </c>
       <c r="D18" s="5">
-        <v>4917</v>
+        <v>4502</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F18" s="9">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="G18" s="5">
         <v>100</v>
       </c>
       <c r="H18" s="19">
         <f t="shared" si="0"/>
-        <v>1600</v>
+        <v>9800</v>
       </c>
       <c r="I18" s="19">
         <v>0</v>
       </c>
       <c r="J18" s="19">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>9800</v>
       </c>
       <c r="K18" s="31">
         <f t="shared" si="2"/>
-        <v>1600</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
-        <v>44531</v>
+        <v>45992</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>50</v>
@@ -10723,112 +10751,112 @@
         <v>258</v>
       </c>
       <c r="D19" s="5">
-        <v>4917</v>
+        <v>4502</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F19" s="9">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="G19" s="5">
         <v>100</v>
       </c>
       <c r="H19" s="19">
         <f t="shared" si="0"/>
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="I19" s="19">
         <v>0</v>
       </c>
       <c r="J19" s="19">
         <f t="shared" si="1"/>
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="K19" s="31">
         <f t="shared" si="2"/>
-        <v>1800</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
-        <v>45267</v>
+        <v>45992</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D20" s="5">
-        <v>5019</v>
+        <v>4502</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>188</v>
+        <v>42</v>
       </c>
       <c r="F20" s="9">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G20" s="5">
         <v>100</v>
       </c>
       <c r="H20" s="19">
         <f t="shared" si="0"/>
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="I20" s="19">
         <v>0</v>
       </c>
       <c r="J20" s="19">
         <f t="shared" si="1"/>
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="K20" s="31">
         <f t="shared" si="2"/>
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
-        <v>45447</v>
+        <v>46003</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D21" s="5">
-        <v>5019</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>188</v>
+        <v>4732</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>331</v>
       </c>
       <c r="F21" s="9">
-        <v>16</v>
+        <v>252</v>
       </c>
       <c r="G21" s="5">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H21" s="19">
         <f t="shared" si="0"/>
-        <v>8000</v>
+        <v>25200</v>
       </c>
       <c r="I21" s="19">
         <v>0</v>
       </c>
       <c r="J21" s="19">
         <f t="shared" si="1"/>
-        <v>8000</v>
+        <v>25200</v>
       </c>
       <c r="K21" s="19">
         <f t="shared" si="2"/>
-        <v>8000</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
-        <v>45632</v>
+        <v>44372</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>50</v>
@@ -10837,36 +10865,36 @@
         <v>258</v>
       </c>
       <c r="D22" s="5">
-        <v>5019</v>
+        <v>4917</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="F22" s="9">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G22" s="5">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H22" s="19">
         <f t="shared" si="0"/>
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="I22" s="19">
         <v>0</v>
       </c>
       <c r="J22" s="19">
         <f t="shared" si="1"/>
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="K22" s="19">
         <f t="shared" si="2"/>
-        <v>9000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" s="4">
-        <v>45812</v>
+        <v>44531</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>50</v>
@@ -10875,36 +10903,36 @@
         <v>258</v>
       </c>
       <c r="D23" s="5">
-        <v>5019</v>
+        <v>4917</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="F23" s="9">
         <v>18</v>
       </c>
       <c r="G23" s="5">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H23" s="19">
         <f t="shared" si="0"/>
-        <v>9000</v>
+        <v>1800</v>
       </c>
       <c r="I23" s="19">
         <v>0</v>
       </c>
       <c r="J23" s="19">
         <f t="shared" si="1"/>
-        <v>9000</v>
+        <v>1800</v>
       </c>
       <c r="K23" s="19">
         <f t="shared" si="2"/>
-        <v>9000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" s="4">
-        <v>45996</v>
+        <v>45267</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>50</v>
@@ -10919,30 +10947,30 @@
         <v>188</v>
       </c>
       <c r="F24" s="9">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="G24" s="5">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H24" s="19">
         <f t="shared" si="0"/>
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="I24" s="19">
         <v>0</v>
       </c>
       <c r="J24" s="19">
         <f t="shared" si="1"/>
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="K24" s="19">
         <f t="shared" si="2"/>
-        <v>9000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" s="4">
-        <v>45016</v>
+        <v>45447</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>50</v>
@@ -10951,36 +10979,36 @@
         <v>258</v>
       </c>
       <c r="D25" s="5">
-        <v>5201</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>43</v>
+        <v>5019</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>188</v>
       </c>
       <c r="F25" s="9">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="G25" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H25" s="19">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>8000</v>
       </c>
       <c r="I25" s="19">
         <v>0</v>
       </c>
       <c r="J25" s="19">
         <f t="shared" si="1"/>
-        <v>10500</v>
+        <v>8000</v>
       </c>
       <c r="K25" s="19">
         <f t="shared" si="2"/>
-        <v>10500</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" s="4">
-        <v>45177</v>
+        <v>45632</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>50</v>
@@ -10989,36 +11017,36 @@
         <v>258</v>
       </c>
       <c r="D26" s="5">
-        <v>5201</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>43</v>
+        <v>5019</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>188</v>
       </c>
       <c r="F26" s="9">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G26" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H26" s="19">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="I26" s="19">
         <v>0</v>
       </c>
       <c r="J26" s="19">
         <f t="shared" si="1"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="K26" s="19">
         <f t="shared" si="2"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" s="4">
-        <v>45380</v>
+        <v>45812</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>50</v>
@@ -11027,36 +11055,36 @@
         <v>258</v>
       </c>
       <c r="D27" s="5">
-        <v>5201</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>43</v>
+        <v>5019</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>188</v>
       </c>
       <c r="F27" s="9">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G27" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H27" s="19">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="I27" s="19">
         <v>0</v>
       </c>
       <c r="J27" s="19">
         <f t="shared" si="1"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="K27" s="19">
         <f t="shared" si="2"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" s="4">
-        <v>45541</v>
+        <v>45996</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>50</v>
@@ -11065,36 +11093,36 @@
         <v>258</v>
       </c>
       <c r="D28" s="5">
-        <v>5201</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>43</v>
+        <v>5019</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>188</v>
       </c>
       <c r="F28" s="9">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G28" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H28" s="19">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="I28" s="19">
         <v>0</v>
       </c>
       <c r="J28" s="19">
         <f t="shared" si="1"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="K28" s="19">
         <f t="shared" si="2"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" s="4">
-        <v>45747</v>
+        <v>46176</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>50</v>
@@ -11103,74 +11131,74 @@
         <v>258</v>
       </c>
       <c r="D29" s="5">
-        <v>5201</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="23">
-        <v>105</v>
+        <v>5019</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="F29" s="9">
+        <v>18</v>
       </c>
       <c r="G29" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H29" s="19">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="I29" s="19">
         <v>0</v>
       </c>
       <c r="J29" s="19">
         <f t="shared" si="1"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="K29" s="19">
         <f t="shared" si="2"/>
-        <v>10500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" s="4">
-        <v>45448</v>
+        <v>45016</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D30" s="5">
-        <v>6526</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>239</v>
+        <v>5201</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F30" s="9">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="G30" s="5">
         <v>100</v>
       </c>
       <c r="H30" s="19">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>10500</v>
       </c>
       <c r="I30" s="19">
         <v>0</v>
       </c>
       <c r="J30" s="19">
         <f t="shared" si="1"/>
-        <v>2500</v>
+        <v>10500</v>
       </c>
       <c r="K30" s="19">
         <f t="shared" si="2"/>
-        <v>2500</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" s="4">
-        <v>44377</v>
+        <v>45177</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>50</v>
@@ -11179,36 +11207,36 @@
         <v>258</v>
       </c>
       <c r="D31" s="5">
-        <v>7011</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>34</v>
+        <v>5201</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F31" s="9">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G31" s="5">
         <v>100</v>
       </c>
       <c r="H31" s="19">
         <f t="shared" si="0"/>
-        <v>7500</v>
+        <v>10500</v>
       </c>
       <c r="I31" s="19">
         <v>0</v>
       </c>
       <c r="J31" s="19">
         <f t="shared" si="1"/>
-        <v>7500</v>
+        <v>10500</v>
       </c>
       <c r="K31" s="19">
         <f t="shared" si="2"/>
-        <v>7500</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" s="4">
-        <v>44533</v>
+        <v>45380</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>50</v>
@@ -11217,36 +11245,36 @@
         <v>258</v>
       </c>
       <c r="D32" s="5">
-        <v>7011</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>34</v>
+        <v>5201</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F32" s="9">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="G32" s="5">
         <v>100</v>
       </c>
       <c r="H32" s="19">
         <f t="shared" si="0"/>
-        <v>4500</v>
+        <v>10500</v>
       </c>
       <c r="I32" s="19">
         <v>0</v>
       </c>
       <c r="J32" s="19">
         <f t="shared" si="1"/>
-        <v>4500</v>
+        <v>10500</v>
       </c>
       <c r="K32" s="19">
         <f t="shared" si="2"/>
-        <v>4500</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="4">
-        <v>44742</v>
+        <v>45541</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>50</v>
@@ -11255,36 +11283,36 @@
         <v>258</v>
       </c>
       <c r="D33" s="5">
-        <v>7011</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>34</v>
+        <v>5201</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F33" s="9">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="G33" s="5">
         <v>100</v>
       </c>
       <c r="H33" s="19">
         <f t="shared" si="0"/>
-        <v>5500</v>
+        <v>10500</v>
       </c>
       <c r="I33" s="19">
-        <v>1117</v>
+        <v>0</v>
       </c>
       <c r="J33" s="19">
         <f t="shared" si="1"/>
-        <v>4383</v>
+        <v>10500</v>
       </c>
       <c r="K33" s="19">
         <f t="shared" si="2"/>
-        <v>4383</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="4">
-        <v>44900</v>
+        <v>45747</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>50</v>
@@ -11293,36 +11321,36 @@
         <v>258</v>
       </c>
       <c r="D34" s="5">
-        <v>7011</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="9">
-        <v>60</v>
+        <v>5201</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="23">
+        <v>105</v>
       </c>
       <c r="G34" s="5">
         <v>100</v>
       </c>
       <c r="H34" s="19">
-        <f t="shared" si="0"/>
-        <v>6000</v>
+        <f t="shared" ref="H34:H66" si="3">F34*G34</f>
+        <v>10500</v>
       </c>
       <c r="I34" s="19">
         <v>0</v>
       </c>
       <c r="J34" s="19">
-        <f t="shared" si="1"/>
-        <v>6000</v>
+        <f t="shared" ref="J34:J66" si="4">H34-I34</f>
+        <v>10500</v>
       </c>
       <c r="K34" s="19">
-        <f t="shared" si="2"/>
-        <v>6000</v>
+        <f t="shared" ref="K34:K66" si="5">J34</f>
+        <v>10500</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="4">
-        <v>45107</v>
+        <v>45908</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>50</v>
@@ -11331,112 +11359,112 @@
         <v>258</v>
       </c>
       <c r="D35" s="5">
-        <v>7011</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>34</v>
+        <v>5201</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F35" s="9">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="G35" s="5">
         <v>100</v>
       </c>
       <c r="H35" s="19">
-        <f t="shared" ref="H35:H59" si="3">F35*G35</f>
-        <v>7000</v>
+        <f t="shared" si="3"/>
+        <v>10500</v>
       </c>
       <c r="I35" s="19">
         <v>0</v>
       </c>
       <c r="J35" s="19">
-        <f t="shared" ref="J35:J54" si="4">H35-I35</f>
-        <v>7000</v>
+        <f t="shared" si="4"/>
+        <v>10500</v>
       </c>
       <c r="K35" s="19">
-        <f t="shared" ref="K35:K54" si="5">J35</f>
-        <v>7000</v>
+        <f t="shared" si="5"/>
+        <v>10500</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="4">
-        <v>45265</v>
+        <v>46150</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D36" s="5">
-        <v>7011</v>
+        <v>6506</v>
       </c>
       <c r="E36" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="F36" s="9">
         <v>34</v>
-      </c>
-      <c r="F36" s="9">
-        <v>80</v>
       </c>
       <c r="G36" s="5">
         <v>100</v>
       </c>
       <c r="H36" s="19">
         <f t="shared" si="3"/>
-        <v>8000</v>
+        <v>3400</v>
       </c>
       <c r="I36" s="19">
         <v>0</v>
       </c>
       <c r="J36" s="19">
         <f t="shared" si="4"/>
-        <v>8000</v>
+        <v>3400</v>
       </c>
       <c r="K36" s="19">
         <f t="shared" si="5"/>
-        <v>8000</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="4">
-        <v>45471</v>
+        <v>45448</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D37" s="5">
-        <v>7011</v>
+        <v>6526</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>34</v>
+        <v>239</v>
       </c>
       <c r="F37" s="9">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="G37" s="5">
         <v>100</v>
       </c>
       <c r="H37" s="19">
         <f t="shared" si="3"/>
-        <v>12000</v>
+        <v>2500</v>
       </c>
       <c r="I37" s="19">
         <v>0</v>
       </c>
       <c r="J37" s="19">
         <f t="shared" si="4"/>
-        <v>12000</v>
+        <v>2500</v>
       </c>
       <c r="K37" s="19">
         <f t="shared" si="5"/>
-        <v>12000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="4">
-        <v>45631</v>
+        <v>44377</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>50</v>
@@ -11451,30 +11479,30 @@
         <v>34</v>
       </c>
       <c r="F38" s="9">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="G38" s="5">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H38" s="19">
         <f t="shared" si="3"/>
-        <v>11000</v>
+        <v>7500</v>
       </c>
       <c r="I38" s="19">
         <v>0</v>
       </c>
       <c r="J38" s="19">
         <f t="shared" si="4"/>
-        <v>11000</v>
+        <v>7500</v>
       </c>
       <c r="K38" s="19">
         <f t="shared" si="5"/>
-        <v>11000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="4">
-        <v>44286</v>
+        <v>44533</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>50</v>
@@ -11483,36 +11511,36 @@
         <v>258</v>
       </c>
       <c r="D39" s="5">
-        <v>7751</v>
+        <v>7011</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F39" s="9">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G39" s="5">
         <v>100</v>
       </c>
       <c r="H39" s="19">
         <f t="shared" si="3"/>
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="I39" s="19">
         <v>0</v>
       </c>
       <c r="J39" s="19">
         <f t="shared" si="4"/>
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="K39" s="19">
         <f t="shared" si="5"/>
-        <v>4000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="4">
-        <v>44435</v>
+        <v>44742</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>50</v>
@@ -11521,36 +11549,36 @@
         <v>258</v>
       </c>
       <c r="D40" s="5">
-        <v>7751</v>
+        <v>7011</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F40" s="9">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G40" s="5">
         <v>100</v>
       </c>
       <c r="H40" s="19">
         <f t="shared" si="3"/>
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="I40" s="19">
-        <v>0</v>
+        <v>1117</v>
       </c>
       <c r="J40" s="19">
         <f t="shared" si="4"/>
-        <v>4500</v>
+        <v>4383</v>
       </c>
       <c r="K40" s="19">
         <f t="shared" si="5"/>
-        <v>4500</v>
+        <v>4383</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="4">
-        <v>44651</v>
+        <v>44900</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>50</v>
@@ -11559,36 +11587,36 @@
         <v>258</v>
       </c>
       <c r="D41" s="5">
-        <v>7751</v>
+        <v>7011</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F41" s="9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G41" s="5">
         <v>100</v>
       </c>
       <c r="H41" s="19">
         <f t="shared" si="3"/>
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="I41" s="19">
-        <v>1117</v>
+        <v>0</v>
       </c>
       <c r="J41" s="19">
         <f t="shared" si="4"/>
-        <v>4383</v>
+        <v>6000</v>
       </c>
       <c r="K41" s="19">
         <f t="shared" si="5"/>
-        <v>4383</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="4">
-        <v>44799</v>
+        <v>45107</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>50</v>
@@ -11597,36 +11625,36 @@
         <v>258</v>
       </c>
       <c r="D42" s="5">
-        <v>7751</v>
+        <v>7011</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F42" s="9">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G42" s="5">
         <v>100</v>
       </c>
       <c r="H42" s="19">
         <f t="shared" si="3"/>
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="I42" s="19">
-        <v>1218</v>
+        <v>0</v>
       </c>
       <c r="J42" s="19">
         <f t="shared" si="4"/>
-        <v>4782</v>
+        <v>7000</v>
       </c>
       <c r="K42" s="19">
         <f t="shared" si="5"/>
-        <v>4782</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="4">
-        <v>45016</v>
+        <v>45265</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>50</v>
@@ -11635,36 +11663,36 @@
         <v>258</v>
       </c>
       <c r="D43" s="5">
-        <v>7751</v>
+        <v>7011</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F43" s="9">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G43" s="5">
         <v>100</v>
       </c>
       <c r="H43" s="19">
         <f t="shared" si="3"/>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="I43" s="19">
         <v>0</v>
       </c>
       <c r="J43" s="19">
         <f t="shared" si="4"/>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="K43" s="19">
         <f t="shared" si="5"/>
-        <v>6000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="4">
-        <v>45163</v>
+        <v>45471</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>50</v>
@@ -11673,36 +11701,36 @@
         <v>258</v>
       </c>
       <c r="D44" s="5">
-        <v>7751</v>
+        <v>7011</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F44" s="9">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="G44" s="5">
         <v>100</v>
       </c>
       <c r="H44" s="19">
         <f t="shared" si="3"/>
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="I44" s="19">
         <v>0</v>
       </c>
       <c r="J44" s="19">
         <f t="shared" si="4"/>
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="K44" s="19">
         <f t="shared" si="5"/>
-        <v>7000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" s="4">
-        <v>45380</v>
+        <v>45631</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>50</v>
@@ -11711,36 +11739,36 @@
         <v>258</v>
       </c>
       <c r="D45" s="5">
-        <v>7751</v>
+        <v>7011</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F45" s="9">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="G45" s="5">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H45" s="19">
         <f t="shared" si="3"/>
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="I45" s="19">
         <v>0</v>
       </c>
       <c r="J45" s="19">
         <f t="shared" si="4"/>
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="K45" s="19">
         <f t="shared" si="5"/>
-        <v>7000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="4">
-        <v>45530</v>
+        <v>44286</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>50</v>
@@ -11755,30 +11783,30 @@
         <v>35</v>
       </c>
       <c r="F46" s="9">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="G46" s="5">
         <v>100</v>
       </c>
       <c r="H46" s="19">
         <f t="shared" si="3"/>
-        <v>7500</v>
+        <v>4000</v>
       </c>
       <c r="I46" s="19">
         <v>0</v>
       </c>
       <c r="J46" s="19">
         <f t="shared" si="4"/>
-        <v>7500</v>
+        <v>4000</v>
       </c>
       <c r="K46" s="19">
         <f t="shared" si="5"/>
-        <v>7500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" s="4">
-        <v>44371</v>
+        <v>44435</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>50</v>
@@ -11787,150 +11815,150 @@
         <v>258</v>
       </c>
       <c r="D47" s="5">
-        <v>7867</v>
+        <v>7751</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F47" s="9">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G47" s="5">
         <v>100</v>
       </c>
       <c r="H47" s="19">
         <f t="shared" si="3"/>
-        <v>1000</v>
+        <v>4500</v>
       </c>
       <c r="I47" s="19">
         <v>0</v>
       </c>
       <c r="J47" s="19">
         <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>4500</v>
       </c>
       <c r="K47" s="19">
         <f t="shared" si="5"/>
-        <v>1000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="4">
-        <v>45747</v>
+        <v>44651</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D48" s="5">
-        <v>7984</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>259</v>
+        <v>7751</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="F48" s="9">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G48" s="5">
         <v>100</v>
       </c>
       <c r="H48" s="19">
         <f t="shared" si="3"/>
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="I48" s="19">
-        <v>0</v>
+        <v>1117</v>
       </c>
       <c r="J48" s="19">
         <f t="shared" si="4"/>
-        <v>3900</v>
+        <v>4383</v>
       </c>
       <c r="K48" s="19">
         <f t="shared" si="5"/>
-        <v>3900</v>
+        <v>4383</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" s="4">
-        <v>45817</v>
+        <v>44799</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D49" s="5">
-        <v>8593</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>189</v>
+        <v>7751</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="F49" s="9">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G49" s="5">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H49" s="19">
         <f t="shared" si="3"/>
         <v>6000</v>
       </c>
       <c r="I49" s="19">
-        <v>0</v>
+        <v>1218</v>
       </c>
       <c r="J49" s="19">
         <f t="shared" si="4"/>
-        <v>6000</v>
+        <v>4782</v>
       </c>
       <c r="K49" s="19">
         <f t="shared" si="5"/>
-        <v>6000</v>
+        <v>4782</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" s="4">
-        <v>45996</v>
+        <v>45016</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D50" s="5">
-        <v>8593</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>189</v>
+        <v>7751</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="F50" s="9">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="G50" s="5">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H50" s="19">
         <f t="shared" si="3"/>
-        <v>6600</v>
+        <v>6000</v>
       </c>
       <c r="I50" s="19">
         <v>0</v>
       </c>
       <c r="J50" s="19">
         <f t="shared" si="4"/>
-        <v>6600</v>
+        <v>6000</v>
       </c>
       <c r="K50" s="19">
         <f t="shared" si="5"/>
-        <v>6600</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" s="4">
-        <v>45104</v>
+        <v>45163</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>50</v>
@@ -11939,48 +11967,48 @@
         <v>258</v>
       </c>
       <c r="D51" s="5">
-        <v>8766</v>
+        <v>7751</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F51" s="9">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G51" s="5">
         <v>100</v>
       </c>
       <c r="H51" s="19">
         <f t="shared" si="3"/>
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="I51" s="19">
         <v>0</v>
       </c>
       <c r="J51" s="19">
         <f t="shared" si="4"/>
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="K51" s="19">
         <f t="shared" si="5"/>
-        <v>5000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" s="4">
-        <v>45463</v>
+        <v>45380</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D52" s="5">
-        <v>9433</v>
+        <v>7751</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="F52" s="9">
         <v>70</v>
@@ -12006,159 +12034,159 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" s="4">
-        <v>45999</v>
+        <v>45530</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D53" s="5">
-        <v>9433</v>
+        <v>7751</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="F53" s="9">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="G53" s="5">
         <v>100</v>
       </c>
       <c r="H53" s="19">
         <f t="shared" si="3"/>
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="I53" s="19">
         <v>0</v>
       </c>
       <c r="J53" s="19">
         <f t="shared" si="4"/>
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="K53" s="19">
         <f t="shared" si="5"/>
-        <v>4000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" s="4">
-        <v>45904</v>
+        <v>44371</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D54" s="5">
-        <v>7984</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>259</v>
+        <v>7867</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="F54" s="9">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="G54" s="5">
         <v>100</v>
       </c>
       <c r="H54" s="19">
         <f t="shared" si="3"/>
-        <v>4600</v>
+        <v>1000</v>
       </c>
       <c r="I54" s="19">
         <v>0</v>
       </c>
       <c r="J54" s="19">
         <f t="shared" si="4"/>
-        <v>4600</v>
+        <v>1000</v>
       </c>
       <c r="K54" s="19">
         <f t="shared" si="5"/>
-        <v>4600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" s="4">
-        <v>45908</v>
+        <v>45747</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D55" s="5">
-        <v>5201</v>
+        <v>7984</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>43</v>
+        <v>259</v>
       </c>
       <c r="F55" s="9">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="G55" s="5">
         <v>100</v>
       </c>
       <c r="H55" s="19">
         <f t="shared" si="3"/>
-        <v>10500</v>
+        <v>3900</v>
       </c>
       <c r="I55" s="19">
         <v>0</v>
       </c>
       <c r="J55" s="19">
-        <f t="shared" ref="J55" si="6">H55-I55</f>
-        <v>10500</v>
+        <f t="shared" si="4"/>
+        <v>3900</v>
       </c>
       <c r="K55" s="19">
-        <f t="shared" ref="K55" si="7">J55</f>
-        <v>10500</v>
+        <f t="shared" si="5"/>
+        <v>3900</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" s="4">
-        <v>45992</v>
+        <v>45904</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D56" s="5">
-        <v>4502</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>42</v>
+        <v>7984</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="F56" s="9">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="G56" s="5">
         <v>100</v>
       </c>
       <c r="H56" s="19">
         <f t="shared" si="3"/>
-        <v>10000</v>
+        <v>4600</v>
       </c>
       <c r="I56" s="19">
         <v>0</v>
       </c>
       <c r="J56" s="19">
-        <f t="shared" ref="J56:J59" si="8">H56-I56</f>
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>4600</v>
       </c>
       <c r="K56" s="19">
-        <f t="shared" ref="K56:K59" si="9">J56</f>
-        <v>10000</v>
+        <f t="shared" si="5"/>
+        <v>4600</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" s="4">
-        <v>45992</v>
+        <v>46111</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>50</v>
@@ -12167,36 +12195,36 @@
         <v>257</v>
       </c>
       <c r="D57" s="5">
-        <v>4502</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>42</v>
+        <v>7984</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="F57" s="9">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="G57" s="5">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H57" s="19">
         <f t="shared" si="3"/>
-        <v>10000</v>
+        <v>5200</v>
       </c>
       <c r="I57" s="19">
         <v>0</v>
       </c>
       <c r="J57" s="19">
-        <f t="shared" si="8"/>
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>5200</v>
       </c>
       <c r="K57" s="19">
-        <f t="shared" si="9"/>
-        <v>10000</v>
+        <f t="shared" si="5"/>
+        <v>5200</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" s="4">
-        <v>45992</v>
+        <v>45817</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>50</v>
@@ -12205,36 +12233,36 @@
         <v>257</v>
       </c>
       <c r="D58" s="5">
-        <v>4204</v>
-      </c>
-      <c r="E58" s="9" t="s">
+        <v>8593</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F58" s="9">
+        <v>20</v>
+      </c>
+      <c r="G58" s="5">
         <v>300</v>
-      </c>
-      <c r="F58" s="9">
-        <v>40</v>
-      </c>
-      <c r="G58" s="5">
-        <v>500</v>
       </c>
       <c r="H58" s="19">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="I58" s="19">
         <v>0</v>
       </c>
       <c r="J58" s="19">
-        <f t="shared" si="8"/>
-        <v>20000</v>
+        <f t="shared" si="4"/>
+        <v>6000</v>
       </c>
       <c r="K58" s="19">
-        <f t="shared" si="9"/>
-        <v>20000</v>
+        <f t="shared" si="5"/>
+        <v>6000</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" s="4">
-        <v>46003</v>
+        <v>45996</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>50</v>
@@ -12243,36 +12271,36 @@
         <v>257</v>
       </c>
       <c r="D59" s="5">
-        <v>4732</v>
+        <v>8593</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>331</v>
+        <v>189</v>
       </c>
       <c r="F59" s="9">
-        <v>252</v>
+        <v>22</v>
       </c>
       <c r="G59" s="5">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H59" s="19">
         <f t="shared" si="3"/>
-        <v>25200</v>
+        <v>6600</v>
       </c>
       <c r="I59" s="19">
         <v>0</v>
       </c>
       <c r="J59" s="19">
-        <f t="shared" si="8"/>
-        <v>25200</v>
+        <f t="shared" si="4"/>
+        <v>6600</v>
       </c>
       <c r="K59" s="19">
-        <f t="shared" si="9"/>
-        <v>25200</v>
+        <f t="shared" si="5"/>
+        <v>6600</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60" s="4">
-        <v>46111</v>
+        <v>46181</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>50</v>
@@ -12281,74 +12309,150 @@
         <v>257</v>
       </c>
       <c r="D60" s="5">
-        <v>7984</v>
+        <v>8593</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>259</v>
+        <v>189</v>
       </c>
       <c r="F60" s="9">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G60" s="5">
         <v>400</v>
       </c>
       <c r="H60" s="19">
-        <f t="shared" ref="H60:H61" si="10">F60*G60</f>
-        <v>5200</v>
+        <f t="shared" si="3"/>
+        <v>9600</v>
       </c>
       <c r="I60" s="19">
         <v>0</v>
       </c>
       <c r="J60" s="19">
-        <f t="shared" ref="J60:J61" si="11">H60-I60</f>
-        <v>5200</v>
+        <f t="shared" si="4"/>
+        <v>9600</v>
       </c>
       <c r="K60" s="19">
-        <f t="shared" ref="K60:K61" si="12">J60</f>
-        <v>5200</v>
+        <f t="shared" si="5"/>
+        <v>9600</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" s="4">
-        <v>46150</v>
+        <v>45104</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C61" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D61" s="5">
+        <v>8766</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61" s="9">
+        <v>50</v>
+      </c>
+      <c r="G61" s="5">
+        <v>100</v>
+      </c>
+      <c r="H61" s="19">
+        <f t="shared" si="3"/>
+        <v>5000</v>
+      </c>
+      <c r="I61" s="19">
+        <v>0</v>
+      </c>
+      <c r="J61" s="19">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+      <c r="K61" s="19">
+        <f t="shared" si="5"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A62" s="4">
+        <v>45463</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="D61" s="5">
-        <v>6506</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="F61" s="9">
-        <v>34</v>
-      </c>
-      <c r="G61" s="5">
-        <v>100</v>
-      </c>
-      <c r="H61" s="19">
-        <f t="shared" si="10"/>
-        <v>3400</v>
-      </c>
-      <c r="I61" s="19">
-        <v>0</v>
-      </c>
-      <c r="J61" s="19">
-        <f t="shared" si="11"/>
-        <v>3400</v>
-      </c>
-      <c r="K61" s="19">
-        <f t="shared" si="12"/>
-        <v>3400</v>
+      <c r="D62" s="5">
+        <v>9433</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" s="9">
+        <v>70</v>
+      </c>
+      <c r="G62" s="5">
+        <v>100</v>
+      </c>
+      <c r="H62" s="19">
+        <f t="shared" si="3"/>
+        <v>7000</v>
+      </c>
+      <c r="I62" s="19">
+        <v>0</v>
+      </c>
+      <c r="J62" s="19">
+        <f t="shared" si="4"/>
+        <v>7000</v>
+      </c>
+      <c r="K62" s="19">
+        <f t="shared" si="5"/>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A63" s="4">
+        <v>45999</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D63" s="5">
+        <v>9433</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F63" s="9">
+        <v>40</v>
+      </c>
+      <c r="G63" s="5">
+        <v>100</v>
+      </c>
+      <c r="H63" s="19">
+        <f t="shared" si="3"/>
+        <v>4000</v>
+      </c>
+      <c r="I63" s="19">
+        <v>0</v>
+      </c>
+      <c r="J63" s="19">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+      <c r="K63" s="19">
+        <f t="shared" si="5"/>
+        <v>4000</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K16" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K50">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K62">
       <sortCondition ref="D1:D16"/>
     </sortState>
   </autoFilter>
@@ -12363,7 +12467,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O945"/>
+  <dimension ref="A1:O962"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -54581,7 +54685,7 @@
         <v>31</v>
       </c>
       <c r="M938" s="15">
-        <f t="shared" ref="M938:M945" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
+        <f t="shared" ref="M938:M962" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
         <v>526900</v>
       </c>
       <c r="N938" s="19">
@@ -54901,6 +55005,771 @@
       </c>
       <c r="N945" s="19">
         <v>0</v>
+      </c>
+    </row>
+    <row r="946" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A946" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B946" s="4">
+        <v>46176</v>
+      </c>
+      <c r="C946" s="5">
+        <v>2802</v>
+      </c>
+      <c r="D946" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="E946" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F946" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G946" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H946" s="5">
+        <v>100</v>
+      </c>
+      <c r="I946" s="7">
+        <v>5377</v>
+      </c>
+      <c r="J946" s="9">
+        <v>0</v>
+      </c>
+      <c r="K946" s="9">
+        <v>0</v>
+      </c>
+      <c r="L946" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M946" s="15">
+        <f t="shared" si="21"/>
+        <v>537700</v>
+      </c>
+      <c r="N946" s="19">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="947" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A947" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B947" s="4">
+        <v>46176</v>
+      </c>
+      <c r="C947" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D947" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E947" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F947" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G947" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H947" s="5">
+        <v>100</v>
+      </c>
+      <c r="I947" s="7">
+        <v>70910</v>
+      </c>
+      <c r="J947" s="9">
+        <v>0</v>
+      </c>
+      <c r="K947" s="9">
+        <v>0</v>
+      </c>
+      <c r="L947" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M947" s="15">
+        <f t="shared" si="21"/>
+        <v>7091000</v>
+      </c>
+      <c r="N947" s="19">
+        <v>1379000</v>
+      </c>
+    </row>
+    <row r="948" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A948" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B948" s="4">
+        <v>46176</v>
+      </c>
+      <c r="C948" s="5">
+        <v>4063</v>
+      </c>
+      <c r="D948" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E948" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F948" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G948" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H948" s="5">
+        <v>100</v>
+      </c>
+      <c r="I948" s="7">
+        <v>7694</v>
+      </c>
+      <c r="J948" s="9">
+        <v>0</v>
+      </c>
+      <c r="K948" s="9">
+        <v>0</v>
+      </c>
+      <c r="L948" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M948" s="15">
+        <f t="shared" si="21"/>
+        <v>769400</v>
+      </c>
+      <c r="N948" s="19">
+        <v>68400</v>
+      </c>
+    </row>
+    <row r="949" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A949" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B949" s="4">
+        <v>46176</v>
+      </c>
+      <c r="C949" s="5">
+        <v>6098</v>
+      </c>
+      <c r="D949" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="E949" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F949" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G949" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H949" s="5">
+        <v>100</v>
+      </c>
+      <c r="I949" s="7">
+        <v>11205</v>
+      </c>
+      <c r="J949" s="9">
+        <v>0</v>
+      </c>
+      <c r="K949" s="9">
+        <v>0</v>
+      </c>
+      <c r="L949" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M949" s="15">
+        <f t="shared" si="21"/>
+        <v>1120500</v>
+      </c>
+      <c r="N949" s="19">
+        <v>144000</v>
+      </c>
+    </row>
+    <row r="950" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A950" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B950" s="4">
+        <v>46176</v>
+      </c>
+      <c r="C950" s="5">
+        <v>8031</v>
+      </c>
+      <c r="D950" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E950" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F950" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G950" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H950" s="5">
+        <v>100</v>
+      </c>
+      <c r="I950" s="7">
+        <v>4997</v>
+      </c>
+      <c r="J950" s="9">
+        <v>0</v>
+      </c>
+      <c r="K950" s="9">
+        <v>0</v>
+      </c>
+      <c r="L950" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M950" s="15">
+        <f t="shared" si="21"/>
+        <v>499700</v>
+      </c>
+      <c r="N950" s="19">
+        <v>-82800</v>
+      </c>
+    </row>
+    <row r="951" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A951" s="4">
+        <v>46176</v>
+      </c>
+      <c r="B951" s="4">
+        <v>46178</v>
+      </c>
+      <c r="C951" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D951" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E951" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F951" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G951" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H951" s="5">
+        <v>100</v>
+      </c>
+      <c r="I951" s="7">
+        <v>27285</v>
+      </c>
+      <c r="J951" s="9">
+        <v>0</v>
+      </c>
+      <c r="K951" s="9">
+        <v>0</v>
+      </c>
+      <c r="L951" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M951" s="15">
+        <f t="shared" si="21"/>
+        <v>2728500</v>
+      </c>
+      <c r="N951" s="19">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="952" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A952" s="4">
+        <v>46176</v>
+      </c>
+      <c r="B952" s="4">
+        <v>46178</v>
+      </c>
+      <c r="C952" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D952" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E952" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F952" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G952" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H952" s="5">
+        <v>100</v>
+      </c>
+      <c r="I952" s="7">
+        <v>79292</v>
+      </c>
+      <c r="J952" s="9">
+        <v>0</v>
+      </c>
+      <c r="K952" s="9">
+        <v>0</v>
+      </c>
+      <c r="L952" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M952" s="15">
+        <f t="shared" si="21"/>
+        <v>7929200</v>
+      </c>
+      <c r="N952" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="953" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A953" s="4">
+        <v>46176</v>
+      </c>
+      <c r="B953" s="4">
+        <v>46178</v>
+      </c>
+      <c r="C953" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D953" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E953" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F953" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G953" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H953" s="5">
+        <v>100</v>
+      </c>
+      <c r="I953" s="7">
+        <v>79300</v>
+      </c>
+      <c r="J953" s="9">
+        <v>0</v>
+      </c>
+      <c r="K953" s="9">
+        <v>0</v>
+      </c>
+      <c r="L953" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M953" s="15">
+        <f t="shared" si="21"/>
+        <v>7930000</v>
+      </c>
+      <c r="N953" s="19">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="954" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A954" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B954" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C954" s="5">
+        <v>1343</v>
+      </c>
+      <c r="D954" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="E954" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F954" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G954" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H954" s="5">
+        <v>50</v>
+      </c>
+      <c r="I954" s="7">
+        <v>1886</v>
+      </c>
+      <c r="J954" s="9">
+        <v>0</v>
+      </c>
+      <c r="K954" s="9">
+        <v>0</v>
+      </c>
+      <c r="L954" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M954" s="15">
+        <f t="shared" si="21"/>
+        <v>94300</v>
+      </c>
+      <c r="N954" s="19">
+        <v>-12750</v>
+      </c>
+    </row>
+    <row r="955" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A955" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B955" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C955" s="5">
+        <v>1488</v>
+      </c>
+      <c r="D955" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="E955" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F955" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G955" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H955" s="5">
+        <v>22</v>
+      </c>
+      <c r="I955" s="7">
+        <v>1805</v>
+      </c>
+      <c r="J955" s="9">
+        <v>0</v>
+      </c>
+      <c r="K955" s="9">
+        <v>0</v>
+      </c>
+      <c r="L955" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M955" s="15">
+        <f t="shared" si="21"/>
+        <v>39710</v>
+      </c>
+      <c r="N955" s="19">
+        <v>-6358</v>
+      </c>
+    </row>
+    <row r="956" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A956" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B956" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C956" s="5">
+        <v>1488</v>
+      </c>
+      <c r="D956" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="E956" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F956" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G956" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H956" s="5">
+        <v>5</v>
+      </c>
+      <c r="I956" s="7">
+        <v>1804</v>
+      </c>
+      <c r="J956" s="9">
+        <v>0</v>
+      </c>
+      <c r="K956" s="9">
+        <v>0</v>
+      </c>
+      <c r="L956" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M956" s="15">
+        <f t="shared" si="21"/>
+        <v>9020</v>
+      </c>
+      <c r="N956" s="19">
+        <v>-1450</v>
+      </c>
+    </row>
+    <row r="957" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A957" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B957" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C957" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D957" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E957" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F957" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G957" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H957" s="5">
+        <v>100</v>
+      </c>
+      <c r="I957" s="7">
+        <v>78610</v>
+      </c>
+      <c r="J957" s="9">
+        <v>0</v>
+      </c>
+      <c r="K957" s="9">
+        <v>0</v>
+      </c>
+      <c r="L957" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M957" s="15">
+        <f t="shared" si="21"/>
+        <v>7861000</v>
+      </c>
+      <c r="N957" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="958" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A958" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B958" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C958" s="5">
+        <v>4493</v>
+      </c>
+      <c r="D958" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="E958" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F958" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G958" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H958" s="5">
+        <v>100</v>
+      </c>
+      <c r="I958" s="7">
+        <v>1774</v>
+      </c>
+      <c r="J958" s="9">
+        <v>0</v>
+      </c>
+      <c r="K958" s="9">
+        <v>0</v>
+      </c>
+      <c r="L958" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M958" s="15">
+        <f t="shared" si="21"/>
+        <v>177400</v>
+      </c>
+      <c r="N958" s="19">
+        <v>-31100</v>
+      </c>
+    </row>
+    <row r="959" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A959" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B959" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C959" s="5">
+        <v>6479</v>
+      </c>
+      <c r="D959" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="E959" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F959" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G959" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H959" s="5">
+        <v>100</v>
+      </c>
+      <c r="I959" s="7">
+        <v>5069.8</v>
+      </c>
+      <c r="J959" s="9">
+        <v>0</v>
+      </c>
+      <c r="K959" s="9">
+        <v>0</v>
+      </c>
+      <c r="L959" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M959" s="15">
+        <f t="shared" si="21"/>
+        <v>506980</v>
+      </c>
+      <c r="N959" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="960" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A960" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B960" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C960" s="5">
+        <v>6890</v>
+      </c>
+      <c r="D960" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E960" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F960" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G960" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H960" s="5">
+        <v>100</v>
+      </c>
+      <c r="I960" s="7">
+        <v>9098</v>
+      </c>
+      <c r="J960" s="9">
+        <v>0</v>
+      </c>
+      <c r="K960" s="9">
+        <v>0</v>
+      </c>
+      <c r="L960" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M960" s="15">
+        <f t="shared" si="21"/>
+        <v>909800</v>
+      </c>
+      <c r="N960" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="961" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A961" s="4">
+        <v>46183</v>
+      </c>
+      <c r="B961" s="4">
+        <v>46185</v>
+      </c>
+      <c r="C961" s="5">
+        <v>7003</v>
+      </c>
+      <c r="D961" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E961" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F961" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G961" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H961" s="5">
+        <v>100</v>
+      </c>
+      <c r="I961" s="7">
+        <v>3942</v>
+      </c>
+      <c r="J961" s="9">
+        <v>0</v>
+      </c>
+      <c r="K961" s="9">
+        <v>0</v>
+      </c>
+      <c r="L961" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M961" s="15">
+        <f t="shared" si="21"/>
+        <v>394200</v>
+      </c>
+      <c r="N961" s="19">
+        <v>-277200</v>
+      </c>
+    </row>
+    <row r="962" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A962" s="4">
+        <v>46185</v>
+      </c>
+      <c r="B962" s="4">
+        <v>46189</v>
+      </c>
+      <c r="C962" s="5">
+        <v>6890</v>
+      </c>
+      <c r="D962" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E962" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F962" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G962" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H962" s="5">
+        <v>100</v>
+      </c>
+      <c r="I962" s="7">
+        <v>9150</v>
+      </c>
+      <c r="J962" s="9">
+        <v>0</v>
+      </c>
+      <c r="K962" s="9">
+        <v>0</v>
+      </c>
+      <c r="L962" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M962" s="15">
+        <f t="shared" si="21"/>
+        <v>915000</v>
+      </c>
+      <c r="N962" s="19">
+        <v>5200</v>
       </c>
     </row>
   </sheetData>
@@ -54920,7 +55789,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -57966,11 +58835,11 @@
         <v>1218</v>
       </c>
       <c r="J80" s="19">
-        <f t="shared" ref="J80:J91" si="16">H80-I80</f>
+        <f t="shared" ref="J80:J94" si="16">H80-I80</f>
         <v>4782</v>
       </c>
       <c r="K80" s="19">
-        <f t="shared" ref="K80:K91" si="17">J80</f>
+        <f t="shared" ref="K80:K94" si="17">J80</f>
         <v>4782</v>
       </c>
     </row>
@@ -58225,7 +59094,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="19">
-        <f t="shared" ref="H87:H91" si="18">F87*G87</f>
+        <f t="shared" ref="H87:H94" si="18">F87*G87</f>
         <v>8000</v>
       </c>
       <c r="I87" s="19">
@@ -58370,7 +59239,7 @@
       <c r="E91" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F91" s="72">
+      <c r="F91" s="9">
         <v>67.5</v>
       </c>
       <c r="G91" s="5">
@@ -58390,6 +59259,120 @@
       <c r="K91" s="19">
         <f t="shared" si="17"/>
         <v>5380</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A92" s="4">
+        <v>46175</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" s="5">
+        <v>6965</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="F92" s="9">
+        <v>19</v>
+      </c>
+      <c r="G92" s="5">
+        <v>100</v>
+      </c>
+      <c r="H92" s="19">
+        <f t="shared" si="18"/>
+        <v>1900</v>
+      </c>
+      <c r="I92" s="19">
+        <v>385</v>
+      </c>
+      <c r="J92" s="19">
+        <f t="shared" si="16"/>
+        <v>1515</v>
+      </c>
+      <c r="K92" s="19">
+        <f t="shared" si="17"/>
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A93" s="4">
+        <v>46181</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" s="5">
+        <v>8698</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F93" s="72">
+        <v>15.4</v>
+      </c>
+      <c r="G93" s="5">
+        <v>300</v>
+      </c>
+      <c r="H93" s="19">
+        <f t="shared" si="18"/>
+        <v>4620</v>
+      </c>
+      <c r="I93" s="19">
+        <v>938</v>
+      </c>
+      <c r="J93" s="19">
+        <f t="shared" si="16"/>
+        <v>3682</v>
+      </c>
+      <c r="K93" s="19">
+        <f t="shared" si="17"/>
+        <v>3682</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A94" s="4">
+        <v>46183</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" s="5">
+        <v>2768</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="F94" s="9">
+        <v>82.5</v>
+      </c>
+      <c r="G94" s="5">
+        <v>100</v>
+      </c>
+      <c r="H94" s="19">
+        <f t="shared" si="18"/>
+        <v>8250</v>
+      </c>
+      <c r="I94" s="19">
+        <v>1675</v>
+      </c>
+      <c r="J94" s="19">
+        <f t="shared" si="16"/>
+        <v>6575</v>
+      </c>
+      <c r="K94" s="19">
+        <f t="shared" si="17"/>
+        <v>6575</v>
       </c>
     </row>
   </sheetData>
@@ -67332,7 +68315,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:T58"/>
+  <dimension ref="A1:T59"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.5" style="1" bestFit="1" customWidth="1"/>
@@ -67531,7 +68514,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="19">
-        <f t="shared" ref="S3:S58" si="0">IF(H3="USD",Q3*L3,R3)</f>
+        <f t="shared" ref="S3:S59" si="0">IF(H3="USD",Q3*L3,R3)</f>
         <v>150.21300000000002</v>
       </c>
     </row>
@@ -70835,6 +71818,64 @@
       <c r="S58" s="19">
         <f t="shared" si="0"/>
         <v>9119.2803999999996</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A59" s="4">
+        <v>46185</v>
+      </c>
+      <c r="B59" s="4">
+        <v>46188</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="D59" s="72" t="s">
+        <v>470</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I59" s="72">
+        <v>3</v>
+      </c>
+      <c r="J59" s="72">
+        <v>135</v>
+      </c>
+      <c r="K59" s="12">
+        <f>I59*J59</f>
+        <v>405</v>
+      </c>
+      <c r="L59" s="72">
+        <v>160.28</v>
+      </c>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9"/>
+      <c r="O59" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="P59" s="19">
+        <f>21637*3</f>
+        <v>64911</v>
+      </c>
+      <c r="Q59" s="9">
+        <v>0</v>
+      </c>
+      <c r="R59" s="9">
+        <v>0</v>
+      </c>
+      <c r="S59" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="594" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B1D374D-DC42-40A3-8E0C-69F9EFAB9787}"/>
+  <xr:revisionPtr revIDLastSave="621" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{134C0A1D-3121-4EB9-8E1C-374528201858}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ_日本" sheetId="10" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">国内株式_信用!$A$1:$AA$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">国内株式_特定!$A$1:$N$852</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">国内株式_特定_配当!$A$1:$K$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">投資信託!$A$1:$K$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">投資信託!$A$1:$K$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">米国株式!$A$1:$S$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">米国株式_配当!$A$1:$K$74</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7386" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7402" uniqueCount="472">
   <si>
     <t>約定日</t>
   </si>
@@ -2823,7 +2823,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3039,9 +3039,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3408,7 +3405,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46186</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3473,7 +3470,7 @@
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>12277423</v>
+        <v>13397423</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
@@ -3485,11 +3482,11 @@
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>8557796</v>
+        <v>9677796</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>6819279.7425999995</v>
+        <v>7711751.7425999995</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -3525,11 +3522,11 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>9908951.9975499995</v>
+        <v>10801423.99755</v>
       </c>
       <c r="U4" s="60">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.5917808219178085</v>
+        <v>5.6</v>
       </c>
       <c r="V4" s="60"/>
     </row>
@@ -3590,11 +3587,11 @@
         <v>-68778</v>
       </c>
       <c r="O5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2021/1/1",投資信託!$B$2:$B$1031,"&lt;=2021/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2021/1/1",投資信託!$B$2:$B$1033,"&lt;=2021/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
         <v>7366</v>
       </c>
       <c r="P5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2021/1/1",投資信託!$B$2:$B$1031,"&lt;=2021/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2021/1/1",投資信託!$B$2:$B$1033,"&lt;=2021/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
         <v>-1498</v>
       </c>
       <c r="Q5" s="35">
@@ -3667,11 +3664,11 @@
         <v>-106573</v>
       </c>
       <c r="O6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2022/1/1",投資信託!$B$2:$B$1031,"&lt;=2022/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2022/1/1",投資信託!$B$2:$B$1033,"&lt;=2022/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2022/1/1",投資信託!$B$2:$B$1031,"&lt;=2022/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2022/1/1",投資信託!$B$2:$B$1033,"&lt;=2022/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q6" s="35">
@@ -3744,11 +3741,11 @@
         <v>-50703</v>
       </c>
       <c r="O7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2023/1/1",投資信託!$B$2:$B$1031,"&lt;=2023/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2023/1/1",投資信託!$B$2:$B$1033,"&lt;=2023/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2023/1/1",投資信託!$B$2:$B$1031,"&lt;=2023/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2023/1/1",投資信託!$B$2:$B$1033,"&lt;=2023/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q7" s="35">
@@ -3821,11 +3818,11 @@
         <v>-247960</v>
       </c>
       <c r="O8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2024/1/1",投資信託!$B$2:$B$1031,"&lt;=2024/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2024/1/1",投資信託!$B$2:$B$1033,"&lt;=2024/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2024/1/1",投資信託!$B$2:$B$1031,"&lt;=2024/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2024/1/1",投資信託!$B$2:$B$1033,"&lt;=2024/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q8" s="35">
@@ -3898,11 +3895,11 @@
         <v>8063.3251500000006</v>
       </c>
       <c r="O9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2025/1/1",投資信託!$B$2:$B$1031,"&lt;=2025/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2025/1/1",投資信託!$B$2:$B$1033,"&lt;=2025/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
         <v>185421</v>
       </c>
       <c r="P9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2025/1/1",投資信託!$B$2:$B$1031,"&lt;=2025/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2025/1/1",投資信託!$B$2:$B$1033,"&lt;=2025/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
         <v>-1071</v>
       </c>
       <c r="Q9" s="35">
@@ -3940,7 +3937,7 @@
       </c>
       <c r="F10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
-        <v>4631030</v>
+        <v>5751030</v>
       </c>
       <c r="G10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
@@ -3952,11 +3949,11 @@
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>3534547</v>
+        <v>4654547</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>2816503.7769499999</v>
+        <v>3708975.7769499999</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -3975,11 +3972,11 @@
         <v>207252.71650000001</v>
       </c>
       <c r="O10" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2026/1/1",投資信託!$B$2:$B$1031,"&lt;=2026/12/31",投資信託!$K$2:$K$1031,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2026/1/1",投資信託!$B$2:$B$1033,"&lt;=2026/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P10" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1031,投資信託!$B$2:$B$1031,"&gt;=2026/1/1",投資信託!$B$2:$B$1031,"&lt;=2026/12/31",投資信託!$K$2:$K$1031,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2026/1/1",投資信託!$B$2:$B$1033,"&lt;=2026/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="35">
@@ -3992,7 +3989,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>3050956.49345</v>
+        <v>3943428.49345</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -11333,18 +11330,18 @@
         <v>100</v>
       </c>
       <c r="H34" s="19">
-        <f t="shared" ref="H34:H66" si="3">F34*G34</f>
+        <f t="shared" ref="H34:H63" si="3">F34*G34</f>
         <v>10500</v>
       </c>
       <c r="I34" s="19">
         <v>0</v>
       </c>
       <c r="J34" s="19">
-        <f t="shared" ref="J34:J66" si="4">H34-I34</f>
+        <f t="shared" ref="J34:J63" si="4">H34-I34</f>
         <v>10500</v>
       </c>
       <c r="K34" s="19">
-        <f t="shared" ref="K34:K66" si="5">J34</f>
+        <f t="shared" ref="K34:K63" si="5">J34</f>
         <v>10500</v>
       </c>
     </row>
@@ -12467,7 +12464,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O962"/>
+  <dimension ref="A1:O963"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -54685,7 +54682,7 @@
         <v>31</v>
       </c>
       <c r="M938" s="15">
-        <f t="shared" ref="M938:M962" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
+        <f t="shared" ref="M938:M963" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
         <v>526900</v>
       </c>
       <c r="N938" s="19">
@@ -55770,6 +55767,51 @@
       </c>
       <c r="N962" s="19">
         <v>5200</v>
+      </c>
+    </row>
+    <row r="963" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A963" s="4">
+        <v>46188</v>
+      </c>
+      <c r="B963" s="4">
+        <v>46190</v>
+      </c>
+      <c r="C963" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D963" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E963" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F963" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G963" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H963" s="5">
+        <v>100</v>
+      </c>
+      <c r="I963" s="7">
+        <v>89810</v>
+      </c>
+      <c r="J963" s="9">
+        <v>0</v>
+      </c>
+      <c r="K963" s="9">
+        <v>0</v>
+      </c>
+      <c r="L963" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M963" s="15">
+        <f t="shared" si="21"/>
+        <v>8981000</v>
+      </c>
+      <c r="N963" s="19">
+        <v>1120000</v>
       </c>
     </row>
   </sheetData>
@@ -59315,7 +59357,7 @@
       <c r="E93" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="F93" s="72">
+      <c r="F93" s="9">
         <v>15.4</v>
       </c>
       <c r="G93" s="5">
@@ -65755,7 +65797,7 @@
   <sheetPr>
     <tabColor theme="2"/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -66749,13 +66791,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" s="4">
-        <v>46128</v>
+        <v>46188</v>
       </c>
       <c r="B29" s="4">
-        <v>45950</v>
+        <v>46192</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>377</v>
+        <v>282</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>159</v>
@@ -66770,13 +66812,13 @@
         <v>284</v>
       </c>
       <c r="H29" s="21">
-        <v>40242</v>
+        <v>7982</v>
       </c>
       <c r="I29" s="21">
-        <v>17395</v>
+        <v>37587</v>
       </c>
       <c r="J29" s="21">
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="K29" s="21">
         <v>0</v>
@@ -66784,10 +66826,10 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" s="4">
-        <v>45974</v>
+        <v>46128</v>
       </c>
       <c r="B30" s="4">
-        <v>45979</v>
+        <v>45950</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>377</v>
@@ -66805,10 +66847,10 @@
         <v>284</v>
       </c>
       <c r="H30" s="21">
-        <v>38038</v>
+        <v>40242</v>
       </c>
       <c r="I30" s="21">
-        <v>18403</v>
+        <v>17395</v>
       </c>
       <c r="J30" s="21">
         <v>70000</v>
@@ -66819,10 +66861,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" s="4">
-        <v>46006</v>
+        <v>45974</v>
       </c>
       <c r="B31" s="4">
-        <v>46009</v>
+        <v>45979</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>377</v>
@@ -66840,10 +66882,10 @@
         <v>284</v>
       </c>
       <c r="H31" s="21">
-        <v>37910</v>
+        <v>38038</v>
       </c>
       <c r="I31" s="21">
-        <v>18465</v>
+        <v>18403</v>
       </c>
       <c r="J31" s="21">
         <v>70000</v>
@@ -66854,10 +66896,10 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" s="4">
-        <v>46036</v>
+        <v>46006</v>
       </c>
       <c r="B32" s="4">
-        <v>46041</v>
+        <v>46009</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>377</v>
@@ -66875,10 +66917,10 @@
         <v>284</v>
       </c>
       <c r="H32" s="21">
-        <v>35338</v>
+        <v>37910</v>
       </c>
       <c r="I32" s="21">
-        <v>19809</v>
+        <v>18465</v>
       </c>
       <c r="J32" s="21">
         <v>70000</v>
@@ -66889,10 +66931,10 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="4">
-        <v>46066</v>
+        <v>46036</v>
       </c>
       <c r="B33" s="4">
-        <v>46071</v>
+        <v>46041</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>377</v>
@@ -66910,10 +66952,10 @@
         <v>284</v>
       </c>
       <c r="H33" s="21">
-        <v>34978</v>
+        <v>35338</v>
       </c>
       <c r="I33" s="21">
-        <v>20013</v>
+        <v>19809</v>
       </c>
       <c r="J33" s="21">
         <v>70000</v>
@@ -66924,10 +66966,10 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="4">
-        <v>46094</v>
+        <v>46066</v>
       </c>
       <c r="B34" s="4">
-        <v>46099</v>
+        <v>46071</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>377</v>
@@ -66945,10 +66987,10 @@
         <v>284</v>
       </c>
       <c r="H34" s="21">
-        <v>35624</v>
+        <v>34978</v>
       </c>
       <c r="I34" s="21">
-        <v>19650</v>
+        <v>20013</v>
       </c>
       <c r="J34" s="21">
         <v>70000</v>
@@ -66959,10 +67001,10 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="4">
-        <v>46126</v>
+        <v>46094</v>
       </c>
       <c r="B35" s="4">
-        <v>46129</v>
+        <v>46099</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>377</v>
@@ -66980,10 +67022,10 @@
         <v>284</v>
       </c>
       <c r="H35" s="21">
-        <v>33669</v>
+        <v>35624</v>
       </c>
       <c r="I35" s="21">
-        <v>20791</v>
+        <v>19650</v>
       </c>
       <c r="J35" s="21">
         <v>70000</v>
@@ -66994,10 +67036,10 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="4">
-        <v>46155</v>
+        <v>46126</v>
       </c>
       <c r="B36" s="4">
-        <v>46160</v>
+        <v>46129</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>377</v>
@@ -67015,10 +67057,10 @@
         <v>284</v>
       </c>
       <c r="H36" s="21">
-        <v>32999</v>
+        <v>33669</v>
       </c>
       <c r="I36" s="21">
-        <v>21213</v>
+        <v>20791</v>
       </c>
       <c r="J36" s="21">
         <v>70000</v>
@@ -67029,34 +67071,34 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="4">
-        <v>44368</v>
+        <v>46155</v>
       </c>
       <c r="B37" s="4">
-        <v>44371</v>
+        <v>46160</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>163</v>
+        <v>377</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H37" s="8">
-        <v>21735</v>
-      </c>
-      <c r="I37" s="8">
-        <v>13803</v>
-      </c>
-      <c r="J37" s="8">
-        <v>30000</v>
+        <v>284</v>
+      </c>
+      <c r="H37" s="21">
+        <v>32999</v>
+      </c>
+      <c r="I37" s="21">
+        <v>21213</v>
+      </c>
+      <c r="J37" s="21">
+        <v>70000</v>
       </c>
       <c r="K37" s="21">
         <v>0</v>
@@ -67064,34 +67106,34 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="4">
-        <v>44377</v>
+        <v>46188</v>
       </c>
       <c r="B38" s="4">
-        <v>44382</v>
+        <v>46191</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>163</v>
+        <v>377</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H38" s="8">
-        <v>7034</v>
-      </c>
-      <c r="I38" s="8">
-        <v>14217</v>
-      </c>
-      <c r="J38" s="8">
-        <v>10000</v>
+        <v>284</v>
+      </c>
+      <c r="H38" s="21">
+        <v>31937</v>
+      </c>
+      <c r="I38" s="21">
+        <v>21918</v>
+      </c>
+      <c r="J38" s="21">
+        <v>70000</v>
       </c>
       <c r="K38" s="21">
         <v>0</v>
@@ -67099,10 +67141,10 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="4">
-        <v>44529</v>
+        <v>44368</v>
       </c>
       <c r="B39" s="4">
-        <v>44532</v>
+        <v>44371</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>163</v>
@@ -67114,28 +67156,30 @@
         <v>295</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G39" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H39" s="8">
-        <v>28769</v>
+        <v>21735</v>
       </c>
       <c r="I39" s="8">
-        <v>13383</v>
+        <v>13803</v>
       </c>
       <c r="J39" s="8">
-        <v>38502</v>
-      </c>
-      <c r="K39" s="19">
-        <v>-1498</v>
+        <v>30000</v>
+      </c>
+      <c r="K39" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="4">
-        <v>44403</v>
+        <v>44377</v>
       </c>
       <c r="B40" s="4">
-        <v>44406</v>
+        <v>44382</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>163</v>
@@ -67144,7 +67188,7 @@
         <v>159</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>30</v>
@@ -67153,10 +67197,10 @@
         <v>160</v>
       </c>
       <c r="H40" s="8">
-        <v>7310</v>
+        <v>7034</v>
       </c>
       <c r="I40" s="8">
-        <v>13681</v>
+        <v>14217</v>
       </c>
       <c r="J40" s="8">
         <v>10000</v>
@@ -67167,10 +67211,10 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="4">
-        <v>44525</v>
+        <v>44529</v>
       </c>
       <c r="B41" s="4">
-        <v>44530</v>
+        <v>44532</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>163</v>
@@ -67179,40 +67223,40 @@
         <v>159</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="8">
-        <v>7310</v>
+        <v>28769</v>
       </c>
       <c r="I41" s="8">
-        <v>13973</v>
+        <v>13383</v>
       </c>
       <c r="J41" s="8">
-        <v>10214</v>
+        <v>38502</v>
       </c>
       <c r="K41" s="19">
-        <v>214</v>
+        <v>-1498</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="4">
-        <v>44165</v>
+        <v>44403</v>
       </c>
       <c r="B42" s="4">
-        <v>44168</v>
+        <v>44406</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>295</v>
+        <v>67</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>30</v>
@@ -67221,13 +67265,13 @@
         <v>160</v>
       </c>
       <c r="H42" s="8">
-        <v>3846</v>
+        <v>7310</v>
       </c>
       <c r="I42" s="8">
-        <v>13000</v>
+        <v>13681</v>
       </c>
       <c r="J42" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K42" s="21">
         <v>0</v>
@@ -67235,45 +67279,43 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="4">
-        <v>44201</v>
+        <v>44525</v>
       </c>
       <c r="B43" s="4">
-        <v>44204</v>
+        <v>44530</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>295</v>
+        <v>67</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="G43" s="5"/>
       <c r="H43" s="8">
-        <v>7604</v>
+        <v>7310</v>
       </c>
       <c r="I43" s="8">
-        <v>13152</v>
+        <v>13973</v>
       </c>
       <c r="J43" s="8">
-        <v>10000</v>
-      </c>
-      <c r="K43" s="21">
-        <v>0</v>
+        <v>10214</v>
+      </c>
+      <c r="K43" s="19">
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="4">
-        <v>44236</v>
+        <v>44165</v>
       </c>
       <c r="B44" s="4">
-        <v>44242</v>
+        <v>44168</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>158</v>
@@ -67291,13 +67333,13 @@
         <v>160</v>
       </c>
       <c r="H44" s="8">
-        <v>7041</v>
+        <v>3846</v>
       </c>
       <c r="I44" s="8">
-        <v>14202</v>
+        <v>13000</v>
       </c>
       <c r="J44" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K44" s="21">
         <v>0</v>
@@ -67305,10 +67347,10 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" s="4">
-        <v>44257</v>
+        <v>44201</v>
       </c>
       <c r="B45" s="4">
-        <v>44260</v>
+        <v>44204</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>158</v>
@@ -67326,10 +67368,10 @@
         <v>160</v>
       </c>
       <c r="H45" s="8">
-        <v>6947</v>
+        <v>7604</v>
       </c>
       <c r="I45" s="8">
-        <v>14394</v>
+        <v>13152</v>
       </c>
       <c r="J45" s="8">
         <v>10000</v>
@@ -67340,10 +67382,10 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="4">
-        <v>44295</v>
+        <v>44236</v>
       </c>
       <c r="B46" s="4">
-        <v>44300</v>
+        <v>44242</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>158</v>
@@ -67361,10 +67403,10 @@
         <v>160</v>
       </c>
       <c r="H46" s="8">
-        <v>6460</v>
+        <v>7041</v>
       </c>
       <c r="I46" s="8">
-        <v>15481</v>
+        <v>14202</v>
       </c>
       <c r="J46" s="8">
         <v>10000</v>
@@ -67375,10 +67417,10 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B47" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>158</v>
@@ -67396,13 +67438,13 @@
         <v>160</v>
       </c>
       <c r="H47" s="8">
-        <v>3167</v>
+        <v>6947</v>
       </c>
       <c r="I47" s="8">
-        <v>15789</v>
+        <v>14394</v>
       </c>
       <c r="J47" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K47" s="21">
         <v>0</v>
@@ -67410,10 +67452,10 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B48" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>158</v>
@@ -67431,10 +67473,10 @@
         <v>160</v>
       </c>
       <c r="H48" s="8">
-        <v>6263</v>
+        <v>6460</v>
       </c>
       <c r="I48" s="8">
-        <v>15967</v>
+        <v>15481</v>
       </c>
       <c r="J48" s="8">
         <v>10000</v>
@@ -67445,10 +67487,10 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" s="4">
-        <v>44377</v>
+        <v>44327</v>
       </c>
       <c r="B49" s="4">
-        <v>44382</v>
+        <v>44330</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>158</v>
@@ -67466,13 +67508,13 @@
         <v>160</v>
       </c>
       <c r="H49" s="8">
-        <v>6081</v>
+        <v>3167</v>
       </c>
       <c r="I49" s="8">
-        <v>16444</v>
+        <v>15789</v>
       </c>
       <c r="J49" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K49" s="21">
         <v>0</v>
@@ -67480,10 +67522,10 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" s="4">
-        <v>44921</v>
+        <v>44350</v>
       </c>
       <c r="B50" s="4">
-        <v>44924</v>
+        <v>44355</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>158</v>
@@ -67501,13 +67543,13 @@
         <v>160</v>
       </c>
       <c r="H50" s="8">
-        <v>24940</v>
+        <v>6263</v>
       </c>
       <c r="I50" s="8">
-        <v>17961</v>
+        <v>15967</v>
       </c>
       <c r="J50" s="8">
-        <v>44794</v>
+        <v>10000</v>
       </c>
       <c r="K50" s="21">
         <v>0</v>
@@ -67515,10 +67557,10 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" s="4">
-        <v>45243</v>
+        <v>44377</v>
       </c>
       <c r="B51" s="4">
-        <v>45246</v>
+        <v>44382</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>158</v>
@@ -67536,13 +67578,13 @@
         <v>160</v>
       </c>
       <c r="H51" s="8">
-        <v>590</v>
+        <v>6081</v>
       </c>
       <c r="I51" s="8">
-        <v>23925</v>
+        <v>16444</v>
       </c>
       <c r="J51" s="8">
-        <v>1410</v>
+        <v>10000</v>
       </c>
       <c r="K51" s="21">
         <v>0</v>
@@ -67550,10 +67592,10 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" s="4">
-        <v>45656</v>
+        <v>44921</v>
       </c>
       <c r="B52" s="4">
-        <v>45663</v>
+        <v>44924</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>158</v>
@@ -67565,15 +67607,19 @@
         <v>295</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G52" s="5"/>
-      <c r="H52" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H52" s="8">
+        <v>24940</v>
+      </c>
+      <c r="I52" s="8">
+        <v>17961</v>
+      </c>
+      <c r="J52" s="8">
+        <v>44794</v>
       </c>
       <c r="K52" s="21">
         <v>0</v>
@@ -67581,10 +67627,10 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" s="4">
-        <v>45772</v>
+        <v>45243</v>
       </c>
       <c r="B53" s="4">
-        <v>45778</v>
+        <v>45246</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>158</v>
@@ -67596,28 +67642,30 @@
         <v>295</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G53" s="5"/>
-      <c r="H53" s="21">
-        <v>69093</v>
-      </c>
-      <c r="I53" s="19">
-        <v>28502</v>
-      </c>
-      <c r="J53" s="19">
-        <v>196929</v>
+        <v>30</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H53" s="8">
+        <v>590</v>
+      </c>
+      <c r="I53" s="8">
+        <v>23925</v>
+      </c>
+      <c r="J53" s="8">
+        <v>1410</v>
       </c>
       <c r="K53" s="21">
-        <v>86850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" s="4">
-        <v>44404</v>
+        <v>45656</v>
       </c>
       <c r="B54" s="4">
-        <v>44407</v>
+        <v>45663</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>158</v>
@@ -67626,22 +67674,18 @@
         <v>159</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H54" s="8">
-        <v>11832</v>
-      </c>
-      <c r="I54" s="8">
-        <v>16903</v>
-      </c>
-      <c r="J54" s="8">
-        <v>20000</v>
+        <v>289</v>
+      </c>
+      <c r="G54" s="5"/>
+      <c r="H54" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9">
+        <v>0</v>
       </c>
       <c r="K54" s="21">
         <v>0</v>
@@ -67649,10 +67693,10 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" s="4">
-        <v>44435</v>
+        <v>45772</v>
       </c>
       <c r="B55" s="4">
-        <v>44440</v>
+        <v>45778</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>158</v>
@@ -67661,31 +67705,31 @@
         <v>159</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G55" s="5"/>
-      <c r="H55" s="8">
-        <v>11832</v>
-      </c>
-      <c r="I55" s="8">
-        <v>17067</v>
-      </c>
-      <c r="J55" s="8">
-        <v>20194</v>
-      </c>
-      <c r="K55" s="19">
-        <v>194</v>
+      <c r="H55" s="21">
+        <v>69093</v>
+      </c>
+      <c r="I55" s="19">
+        <v>28502</v>
+      </c>
+      <c r="J55" s="19">
+        <v>196929</v>
+      </c>
+      <c r="K55" s="21">
+        <v>86850</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" s="4">
-        <v>45656</v>
+        <v>44404</v>
       </c>
       <c r="B56" s="4">
-        <v>45663</v>
+        <v>44407</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>158</v>
@@ -67694,18 +67738,22 @@
         <v>159</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>294</v>
+        <v>67</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="G56" s="5"/>
-      <c r="H56" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H56" s="8">
+        <v>11832</v>
+      </c>
+      <c r="I56" s="8">
+        <v>16903</v>
+      </c>
+      <c r="J56" s="8">
+        <v>20000</v>
       </c>
       <c r="K56" s="21">
         <v>0</v>
@@ -67713,10 +67761,10 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" s="4">
-        <v>45824</v>
+        <v>44435</v>
       </c>
       <c r="B57" s="4">
-        <v>45827</v>
+        <v>44440</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>158</v>
@@ -67725,55 +67773,51 @@
         <v>159</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G57" s="5"/>
-      <c r="H57" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I57" s="19">
-        <v>31398</v>
-      </c>
-      <c r="J57" s="19">
-        <v>12076</v>
-      </c>
-      <c r="K57" s="21">
-        <v>-1071</v>
+      <c r="H57" s="8">
+        <v>11832</v>
+      </c>
+      <c r="I57" s="8">
+        <v>17067</v>
+      </c>
+      <c r="J57" s="8">
+        <v>20194</v>
+      </c>
+      <c r="K57" s="19">
+        <v>194</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" s="4">
-        <v>44188</v>
+        <v>45656</v>
       </c>
       <c r="B58" s="4">
-        <v>44193</v>
+        <v>45663</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H58" s="8">
-        <v>4490</v>
-      </c>
-      <c r="I58" s="8">
-        <v>22273</v>
-      </c>
-      <c r="J58" s="8">
-        <v>10000</v>
+        <v>296</v>
+      </c>
+      <c r="G58" s="5"/>
+      <c r="H58" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9">
+        <v>0</v>
       </c>
       <c r="K58" s="21">
         <v>0</v>
@@ -67781,45 +67825,43 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" s="4">
-        <v>44224</v>
+        <v>45824</v>
       </c>
       <c r="B59" s="4">
-        <v>44229</v>
+        <v>45827</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>295</v>
+        <v>68</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H59" s="8">
-        <v>2108</v>
-      </c>
-      <c r="I59" s="8">
-        <v>23721</v>
-      </c>
-      <c r="J59" s="8">
-        <v>5000</v>
+        <v>298</v>
+      </c>
+      <c r="G59" s="5"/>
+      <c r="H59" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I59" s="19">
+        <v>31398</v>
+      </c>
+      <c r="J59" s="19">
+        <v>12076</v>
       </c>
       <c r="K59" s="21">
-        <v>0</v>
+        <v>-1071</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60" s="4">
-        <v>44257</v>
+        <v>44188</v>
       </c>
       <c r="B60" s="4">
-        <v>44260</v>
+        <v>44193</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>162</v>
@@ -67837,13 +67879,13 @@
         <v>160</v>
       </c>
       <c r="H60" s="8">
-        <v>1938</v>
+        <v>4490</v>
       </c>
       <c r="I60" s="8">
-        <v>25804</v>
+        <v>22273</v>
       </c>
       <c r="J60" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K60" s="21">
         <v>0</v>
@@ -67851,10 +67893,10 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" s="4">
-        <v>44295</v>
+        <v>44224</v>
       </c>
       <c r="B61" s="4">
-        <v>44300</v>
+        <v>44229</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>162</v>
@@ -67872,10 +67914,10 @@
         <v>160</v>
       </c>
       <c r="H61" s="8">
-        <v>1920</v>
+        <v>2108</v>
       </c>
       <c r="I61" s="8">
-        <v>26043</v>
+        <v>23721</v>
       </c>
       <c r="J61" s="8">
         <v>5000</v>
@@ -67886,10 +67928,10 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B62" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>162</v>
@@ -67907,13 +67949,13 @@
         <v>160</v>
       </c>
       <c r="H62" s="8">
-        <v>4166</v>
+        <v>1938</v>
       </c>
       <c r="I62" s="8">
-        <v>24007</v>
+        <v>25804</v>
       </c>
       <c r="J62" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K62" s="21">
         <v>0</v>
@@ -67921,10 +67963,10 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B63" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>162</v>
@@ -67942,10 +67984,10 @@
         <v>160</v>
       </c>
       <c r="H63" s="8">
-        <v>1983</v>
+        <v>1920</v>
       </c>
       <c r="I63" s="8">
-        <v>25216</v>
+        <v>26043</v>
       </c>
       <c r="J63" s="8">
         <v>5000</v>
@@ -67956,10 +67998,10 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64" s="4">
-        <v>44362</v>
+        <v>44327</v>
       </c>
       <c r="B64" s="4">
-        <v>44365</v>
+        <v>44330</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>162</v>
@@ -67971,31 +68013,33 @@
         <v>295</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G64" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H64" s="8">
-        <v>16605</v>
+        <v>4166</v>
       </c>
       <c r="I64" s="8">
-        <v>26019</v>
+        <v>24007</v>
       </c>
       <c r="J64" s="8">
-        <v>43205</v>
-      </c>
-      <c r="K64" s="19">
-        <v>3205</v>
+        <v>10000</v>
+      </c>
+      <c r="K64" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A65" s="4">
-        <v>44187</v>
+        <v>44350</v>
       </c>
       <c r="B65" s="4">
-        <v>44190</v>
+        <v>44355</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>159</v>
@@ -68010,27 +68054,27 @@
         <v>160</v>
       </c>
       <c r="H65" s="8">
-        <v>6447</v>
+        <v>1983</v>
       </c>
       <c r="I65" s="8">
-        <v>15511</v>
+        <v>25216</v>
       </c>
       <c r="J65" s="8">
-        <v>10000</v>
-      </c>
-      <c r="K65" s="19">
+        <v>5000</v>
+      </c>
+      <c r="K65" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66" s="4">
-        <v>44224</v>
+        <v>44362</v>
       </c>
       <c r="B66" s="4">
-        <v>44229</v>
+        <v>44365</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>159</v>
@@ -68039,30 +68083,28 @@
         <v>295</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="G66" s="5"/>
       <c r="H66" s="8">
-        <v>3093</v>
+        <v>16605</v>
       </c>
       <c r="I66" s="8">
-        <v>16167</v>
+        <v>26019</v>
       </c>
       <c r="J66" s="8">
-        <v>5000</v>
+        <v>43205</v>
       </c>
       <c r="K66" s="19">
-        <v>0</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67" s="4">
-        <v>44257</v>
+        <v>44187</v>
       </c>
       <c r="B67" s="4">
-        <v>44260</v>
+        <v>44190</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>161</v>
@@ -68080,13 +68122,13 @@
         <v>160</v>
       </c>
       <c r="H67" s="8">
-        <v>2978</v>
+        <v>6447</v>
       </c>
       <c r="I67" s="8">
-        <v>16792</v>
+        <v>15511</v>
       </c>
       <c r="J67" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K67" s="19">
         <v>0</v>
@@ -68094,10 +68136,10 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68" s="4">
-        <v>44295</v>
+        <v>44224</v>
       </c>
       <c r="B68" s="4">
-        <v>44300</v>
+        <v>44229</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>161</v>
@@ -68115,10 +68157,10 @@
         <v>160</v>
       </c>
       <c r="H68" s="8">
-        <v>2810</v>
+        <v>3093</v>
       </c>
       <c r="I68" s="8">
-        <v>17792</v>
+        <v>16167</v>
       </c>
       <c r="J68" s="8">
         <v>5000</v>
@@ -68129,10 +68171,10 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B69" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>161</v>
@@ -68150,10 +68192,10 @@
         <v>160</v>
       </c>
       <c r="H69" s="8">
-        <v>2903</v>
+        <v>2978</v>
       </c>
       <c r="I69" s="8">
-        <v>17225</v>
+        <v>16792</v>
       </c>
       <c r="J69" s="8">
         <v>5000</v>
@@ -68164,10 +68206,10 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A70" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B70" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>161</v>
@@ -68185,10 +68227,10 @@
         <v>160</v>
       </c>
       <c r="H70" s="8">
-        <v>2819</v>
+        <v>2810</v>
       </c>
       <c r="I70" s="8">
-        <v>17736</v>
+        <v>17792</v>
       </c>
       <c r="J70" s="8">
         <v>5000</v>
@@ -68199,10 +68241,10 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A71" s="4">
-        <v>44362</v>
+        <v>44327</v>
       </c>
       <c r="B71" s="4">
-        <v>44365</v>
+        <v>44330</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>161</v>
@@ -68214,37 +68256,39 @@
         <v>295</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G71" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H71" s="8">
-        <v>21050</v>
+        <v>2903</v>
       </c>
       <c r="I71" s="8">
-        <v>18410</v>
+        <v>17225</v>
       </c>
       <c r="J71" s="8">
-        <v>38753</v>
+        <v>5000</v>
       </c>
       <c r="K71" s="19">
-        <v>3753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A72" s="4">
-        <v>45243</v>
+        <v>44350</v>
       </c>
       <c r="B72" s="4">
-        <v>45247</v>
+        <v>44355</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>30</v>
@@ -68252,56 +68296,124 @@
       <c r="G72" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="H72" s="19">
-        <v>180143</v>
-      </c>
-      <c r="I72" s="19">
-        <v>12456</v>
+      <c r="H72" s="8">
+        <v>2819</v>
+      </c>
+      <c r="I72" s="8">
+        <v>17736</v>
       </c>
       <c r="J72" s="8">
-        <v>224386</v>
-      </c>
-      <c r="K72" s="21">
+        <v>5000</v>
+      </c>
+      <c r="K72" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A73" s="4">
-        <v>45664</v>
+        <v>44362</v>
       </c>
       <c r="B73" s="4">
-        <v>45671</v>
+        <v>44365</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G73" s="5"/>
-      <c r="H73" s="21">
+      <c r="H73" s="8">
+        <v>21050</v>
+      </c>
+      <c r="I73" s="8">
+        <v>18410</v>
+      </c>
+      <c r="J73" s="8">
+        <v>38753</v>
+      </c>
+      <c r="K73" s="19">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A74" s="4">
+        <v>45243</v>
+      </c>
+      <c r="B74" s="4">
+        <v>45247</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H74" s="19">
         <v>180143</v>
       </c>
-      <c r="I73" s="21">
+      <c r="I74" s="19">
+        <v>12456</v>
+      </c>
+      <c r="J74" s="8">
+        <v>224386</v>
+      </c>
+      <c r="K74" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A75" s="4">
+        <v>45664</v>
+      </c>
+      <c r="B75" s="4">
+        <v>45671</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G75" s="5"/>
+      <c r="H75" s="21">
+        <v>180143</v>
+      </c>
+      <c r="I75" s="21">
         <v>15148</v>
       </c>
-      <c r="J73" s="21">
+      <c r="J75" s="21">
         <v>272881</v>
       </c>
-      <c r="K73" s="19">
+      <c r="K75" s="19">
         <v>48494</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K63" xr:uid="{00000000-0009-0000-0000-000007000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K73">
-      <sortCondition ref="C1:C63"/>
+  <autoFilter ref="A1:K65" xr:uid="{00000000-0009-0000-0000-000007000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K75">
+      <sortCondition ref="C1:C65"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18"/>
@@ -71830,7 +71942,7 @@
       <c r="C59" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="D59" s="72" t="s">
+      <c r="D59" s="9" t="s">
         <v>470</v>
       </c>
       <c r="E59" s="5" t="s">
@@ -71845,17 +71957,17 @@
       <c r="H59" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I59" s="72">
+      <c r="I59" s="9">
         <v>3</v>
       </c>
-      <c r="J59" s="72">
+      <c r="J59" s="9">
         <v>135</v>
       </c>
       <c r="K59" s="12">
         <f>I59*J59</f>
         <v>405</v>
       </c>
-      <c r="L59" s="72">
+      <c r="L59" s="9">
         <v>160.28</v>
       </c>
       <c r="M59" s="9"/>

--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="621" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{134C0A1D-3121-4EB9-8E1C-374528201858}"/>
+  <xr:revisionPtr revIDLastSave="636" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFBB58E5-5547-4B40-86D3-903162AF50F6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ_日本" sheetId="10" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">国内株式_NISA!$A$1:$N$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">国内株式_NISA_配当!$A$1:$K$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">国内株式_信用!$A$1:$AA$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">国内株式_特定!$A$1:$N$852</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">国内株式_特定!$A$1:$N$963</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">国内株式_特定_配当!$A$1:$K$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">投資信託!$A$1:$K$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">米国株式!$A$1:$S$1</definedName>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7402" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7432" uniqueCount="476">
   <si>
     <t>約定日</t>
   </si>
@@ -2103,6 +2103,21 @@
     <t>-</t>
     <phoneticPr fontId="18"/>
   </si>
+  <si>
+    <t>フェローテック</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>429A</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>テクセンドフォトマスク</t>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="18"/>
+  </si>
 </sst>
 </file>
 
@@ -2823,7 +2838,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3039,6 +3054,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3405,7 +3423,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46194</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3462,11 +3480,11 @@
       </c>
       <c r="D4" s="20">
         <f>SUM(D5:D100)</f>
-        <v>477495</v>
+        <v>501495</v>
       </c>
       <c r="E4" s="35">
         <f>SUM(B4:D4)</f>
-        <v>3196795</v>
+        <v>3220795</v>
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
@@ -3474,19 +3492,19 @@
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
-        <v>-4570437</v>
+        <v>-4721887</v>
       </c>
       <c r="H4" s="20">
         <f>SUM(H5:H100)</f>
-        <v>850810</v>
+        <v>851995</v>
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>9677796</v>
+        <v>9527531</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>7711751.7425999995</v>
+        <v>7592013.0773499999</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -3522,11 +3540,11 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>10801423.99755</v>
+        <v>10705685.3323</v>
       </c>
       <c r="U4" s="60">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.6</v>
+        <v>5.6136986301369864</v>
       </c>
       <c r="V4" s="60"/>
     </row>
@@ -3929,11 +3947,11 @@
       </c>
       <c r="D10" s="19">
         <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1004,国内株式_NISA_配当!$A$2:$A$1004,"&gt;=2026/1/1",国内株式_NISA_配当!$A$2:$A$1004,"&lt;=2026/12/31")</f>
-        <v>27200</v>
+        <v>51200</v>
       </c>
       <c r="E10" s="35">
         <f t="shared" si="7"/>
-        <v>27200</v>
+        <v>51200</v>
       </c>
       <c r="F10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
@@ -3941,19 +3959,19 @@
       </c>
       <c r="G10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
-        <v>-1145138</v>
+        <v>-1296588</v>
       </c>
       <c r="H10" s="19">
         <f>SUMIFS(国内株式_特定_配当!$H$2:$H$999,国内株式_特定_配当!$A$2:$A$999,"&gt;=2026/1/1",国内株式_特定_配当!$A$2:$A$999,"&lt;=2026/12/31")</f>
-        <v>48655</v>
+        <v>49840</v>
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>4654547</v>
+        <v>4504282</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>3708975.7769499999</v>
+        <v>3589237.1117000002</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -3989,7 +4007,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>3943428.49345</v>
+        <v>3847689.8282000003</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -10042,7 +10060,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -12445,6 +12463,82 @@
       <c r="K63" s="19">
         <f t="shared" si="5"/>
         <v>4000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A64" s="4">
+        <v>46191</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D64" s="5">
+        <v>9433</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F64" s="9">
+        <v>40</v>
+      </c>
+      <c r="G64" s="5">
+        <v>100</v>
+      </c>
+      <c r="H64" s="19">
+        <f t="shared" ref="H64:H65" si="6">F64*G64</f>
+        <v>4000</v>
+      </c>
+      <c r="I64" s="19">
+        <v>0</v>
+      </c>
+      <c r="J64" s="19">
+        <f t="shared" ref="J64:J65" si="7">H64-I64</f>
+        <v>4000</v>
+      </c>
+      <c r="K64" s="19">
+        <f t="shared" ref="K64:K65" si="8">J64</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A65" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D65" s="5">
+        <v>4204</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F65" s="9">
+        <v>40</v>
+      </c>
+      <c r="G65" s="5">
+        <v>500</v>
+      </c>
+      <c r="H65" s="19">
+        <f t="shared" si="6"/>
+        <v>20000</v>
+      </c>
+      <c r="I65" s="19">
+        <v>0</v>
+      </c>
+      <c r="J65" s="19">
+        <f t="shared" si="7"/>
+        <v>20000</v>
+      </c>
+      <c r="K65" s="19">
+        <f t="shared" si="8"/>
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
@@ -12464,7 +12558,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O963"/>
+  <dimension ref="A1:O967"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -23243,7 +23337,7 @@
         <v>6890</v>
       </c>
       <c r="D240" s="9" t="s">
-        <v>187</v>
+        <v>472</v>
       </c>
       <c r="E240" s="5" t="s">
         <v>68</v>
@@ -23378,7 +23472,7 @@
         <v>6890</v>
       </c>
       <c r="D243" s="9" t="s">
-        <v>187</v>
+        <v>472</v>
       </c>
       <c r="E243" s="5" t="s">
         <v>68</v>
@@ -23648,7 +23742,7 @@
         <v>6890</v>
       </c>
       <c r="D249" s="9" t="s">
-        <v>187</v>
+        <v>472</v>
       </c>
       <c r="E249" s="5" t="s">
         <v>68</v>
@@ -24188,7 +24282,7 @@
         <v>6890</v>
       </c>
       <c r="D261" s="9" t="s">
-        <v>187</v>
+        <v>472</v>
       </c>
       <c r="E261" s="5" t="s">
         <v>68</v>
@@ -25178,7 +25272,7 @@
         <v>6890</v>
       </c>
       <c r="D283" s="9" t="s">
-        <v>187</v>
+        <v>472</v>
       </c>
       <c r="E283" s="5" t="s">
         <v>68</v>
@@ -25313,7 +25407,7 @@
         <v>6890</v>
       </c>
       <c r="D286" s="9" t="s">
-        <v>187</v>
+        <v>472</v>
       </c>
       <c r="E286" s="5" t="s">
         <v>68</v>
@@ -30486,7 +30580,7 @@
         <v>6890</v>
       </c>
       <c r="D401" s="9" t="s">
-        <v>187</v>
+        <v>472</v>
       </c>
       <c r="E401" s="5" t="s">
         <v>67</v>
@@ -31521,7 +31615,7 @@
         <v>6890</v>
       </c>
       <c r="D424" s="9" t="s">
-        <v>187</v>
+        <v>472</v>
       </c>
       <c r="E424" s="5" t="s">
         <v>67</v>
@@ -54682,7 +54776,7 @@
         <v>31</v>
       </c>
       <c r="M938" s="15">
-        <f t="shared" ref="M938:M963" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
+        <f t="shared" ref="M938:M967" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
         <v>526900</v>
       </c>
       <c r="N938" s="19">
@@ -55814,8 +55908,189 @@
         <v>1120000</v>
       </c>
     </row>
+    <row r="964" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A964" s="4">
+        <v>46190</v>
+      </c>
+      <c r="B964" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C964" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="D964" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="E964" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F964" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G964" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H964" s="5">
+        <v>100</v>
+      </c>
+      <c r="I964" s="72">
+        <v>4309.5</v>
+      </c>
+      <c r="J964" s="9">
+        <v>0</v>
+      </c>
+      <c r="K964" s="9">
+        <v>0</v>
+      </c>
+      <c r="L964" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="M964" s="15">
+        <f t="shared" si="21"/>
+        <v>430950</v>
+      </c>
+      <c r="N964" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A965" s="4">
+        <v>46191</v>
+      </c>
+      <c r="B965" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C965" s="5">
+        <v>1488</v>
+      </c>
+      <c r="D965" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="E965" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F965" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G965" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H965" s="5">
+        <v>28</v>
+      </c>
+      <c r="I965" s="72">
+        <v>1814</v>
+      </c>
+      <c r="J965" s="9">
+        <v>0</v>
+      </c>
+      <c r="K965" s="9">
+        <v>0</v>
+      </c>
+      <c r="L965" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M965" s="15">
+        <f t="shared" si="21"/>
+        <v>50792</v>
+      </c>
+      <c r="N965" s="19">
+        <f>-5050-2800</f>
+        <v>-7850</v>
+      </c>
+    </row>
+    <row r="966" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A966" s="4">
+        <v>46191</v>
+      </c>
+      <c r="B966" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C966" s="5">
+        <v>3563</v>
+      </c>
+      <c r="D966" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="E966" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F966" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G966" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H966" s="5">
+        <v>100</v>
+      </c>
+      <c r="I966" s="72">
+        <v>9414</v>
+      </c>
+      <c r="J966" s="9">
+        <v>0</v>
+      </c>
+      <c r="K966" s="9">
+        <v>0</v>
+      </c>
+      <c r="L966" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M966" s="15">
+        <f t="shared" si="21"/>
+        <v>941400</v>
+      </c>
+      <c r="N966" s="19">
+        <v>-143600</v>
+      </c>
+    </row>
+    <row r="967" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A967" s="4">
+        <v>46192</v>
+      </c>
+      <c r="B967" s="4">
+        <v>46196</v>
+      </c>
+      <c r="C967" s="5">
+        <v>9984</v>
+      </c>
+      <c r="D967" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E967" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F967" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G967" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H967" s="5">
+        <v>100</v>
+      </c>
+      <c r="I967" s="72">
+        <v>7139</v>
+      </c>
+      <c r="J967" s="9">
+        <v>0</v>
+      </c>
+      <c r="K967" s="9">
+        <v>0</v>
+      </c>
+      <c r="L967" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="M967" s="15">
+        <f t="shared" si="21"/>
+        <v>713900</v>
+      </c>
+      <c r="N967" s="19">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N852" xr:uid="{00000000-0009-0000-0000-000002000000}">
+  <autoFilter ref="A1:N963" xr:uid="{00000000-0009-0000-0000-000002000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N562">
       <sortCondition ref="A1:A539"/>
     </sortState>
@@ -55831,7 +56106,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -59136,7 +59411,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="19">
-        <f t="shared" ref="H87:H94" si="18">F87*G87</f>
+        <f t="shared" ref="H87:H95" si="18">F87*G87</f>
         <v>8000</v>
       </c>
       <c r="I87" s="19">
@@ -59415,6 +59690,44 @@
       <c r="K94" s="19">
         <f t="shared" si="17"/>
         <v>6575</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A95" s="4">
+        <v>46191</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" s="5">
+        <v>1343</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="F95" s="9">
+        <v>23.7</v>
+      </c>
+      <c r="G95" s="5">
+        <v>50</v>
+      </c>
+      <c r="H95" s="19">
+        <f t="shared" si="18"/>
+        <v>1185</v>
+      </c>
+      <c r="I95" s="19">
+        <v>240</v>
+      </c>
+      <c r="J95" s="19">
+        <f t="shared" ref="J95" si="19">H95-I95</f>
+        <v>945</v>
+      </c>
+      <c r="K95" s="19">
+        <f t="shared" ref="K95" si="20">J95</f>
+        <v>945</v>
       </c>
     </row>
   </sheetData>

--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="636" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFBB58E5-5547-4B40-86D3-903162AF50F6}"/>
+  <xr:revisionPtr revIDLastSave="653" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC333871-D026-4D34-B7C9-C8F3DDF947DF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7432" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7522" uniqueCount="479">
   <si>
     <t>約定日</t>
   </si>
@@ -2118,6 +2118,16 @@
     <t>-</t>
     <phoneticPr fontId="18"/>
   </si>
+  <si>
+    <t>429A</t>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>任天堂</t>
+  </si>
 </sst>
 </file>
 
@@ -2838,7 +2848,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3004,22 +3014,16 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3043,6 +3047,12 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3054,9 +3064,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3336,31 +3343,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55" t="s">
         <v>216</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59" t="s">
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55" t="s">
         <v>218</v>
       </c>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="65" t="s">
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="63" t="s">
         <v>302</v>
       </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="67"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="65"/>
       <c r="S1" s="37" t="s">
         <v>219</v>
       </c>
@@ -3372,50 +3379,50 @@
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55" t="s">
+      <c r="C2" s="57"/>
+      <c r="D2" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55" t="s">
+      <c r="G2" s="57"/>
+      <c r="H2" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="55" t="s">
+      <c r="K2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="57" t="s">
+      <c r="L2" s="57"/>
+      <c r="M2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="N2" s="62" t="s">
+      <c r="N2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="O2" s="63" t="s">
+      <c r="O2" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="57" t="s">
+      <c r="P2" s="62"/>
+      <c r="Q2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="R2" s="62" t="s">
+      <c r="R2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="S2" s="61" t="s">
+      <c r="S2" s="59" t="s">
         <v>214</v>
       </c>
       <c r="U2" s="49">
@@ -3423,7 +3430,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46194</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3433,38 +3440,38 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="58"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="55"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
       <c r="K3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
       <c r="O3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="P3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="61"/>
-      <c r="U3" s="59" t="s">
+      <c r="Q3" s="58"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="59"/>
+      <c r="U3" s="55" t="s">
         <v>363</v>
       </c>
-      <c r="V3" s="59"/>
+      <c r="V3" s="55"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="34" t="s">
@@ -3476,35 +3483,35 @@
       </c>
       <c r="C4" s="20">
         <f>SUM(C5:C100)</f>
-        <v>-49300</v>
+        <v>-105940</v>
       </c>
       <c r="D4" s="20">
         <f>SUM(D5:D100)</f>
-        <v>501495</v>
+        <v>514445</v>
       </c>
       <c r="E4" s="35">
         <f>SUM(B4:D4)</f>
-        <v>3220795</v>
+        <v>3177105</v>
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>13397423</v>
+        <v>13664792</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
-        <v>-4721887</v>
+        <v>-5372687</v>
       </c>
       <c r="H4" s="20">
         <f>SUM(H5:H100)</f>
-        <v>851995</v>
+        <v>870235</v>
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>9527531</v>
+        <v>9162340</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>7592013.0773499999</v>
+        <v>7301010.6289999997</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -3540,13 +3547,13 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>10705685.3323</v>
-      </c>
-      <c r="U4" s="60">
+        <v>10370992.883950001</v>
+      </c>
+      <c r="U4" s="56">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.6136986301369864</v>
-      </c>
-      <c r="V4" s="60"/>
+        <v>5.6273972602739724</v>
+      </c>
+      <c r="V4" s="56"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="34" t="s">
@@ -3943,35 +3950,35 @@
       </c>
       <c r="C10" s="19">
         <f>SUMIFS(国内株式_NISA!$N$2:$N$996,国内株式_NISA!$B$2:$B$996,"&gt;=2026/1/1",国内株式_NISA!$B$2:$B$996,"&lt;=2026/12/31",国内株式_NISA!$N$2:$N$996,"&lt;0")</f>
-        <v>0</v>
+        <v>-56640</v>
       </c>
       <c r="D10" s="19">
         <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1004,国内株式_NISA_配当!$A$2:$A$1004,"&gt;=2026/1/1",国内株式_NISA_配当!$A$2:$A$1004,"&lt;=2026/12/31")</f>
-        <v>51200</v>
+        <v>64150</v>
       </c>
       <c r="E10" s="35">
         <f t="shared" si="7"/>
-        <v>51200</v>
+        <v>7510</v>
       </c>
       <c r="F10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
-        <v>5751030</v>
+        <v>6018399</v>
       </c>
       <c r="G10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
-        <v>-1296588</v>
+        <v>-1947388</v>
       </c>
       <c r="H10" s="19">
         <f>SUMIFS(国内株式_特定_配当!$H$2:$H$999,国内株式_特定_配当!$A$2:$A$999,"&gt;=2026/1/1",国内株式_特定_配当!$A$2:$A$999,"&lt;=2026/12/31")</f>
-        <v>49840</v>
+        <v>68080</v>
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>4504282</v>
+        <v>4139091</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>3589237.1117000002</v>
+        <v>3298234.66335</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -4007,7 +4014,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>3847689.8282000003</v>
+        <v>3512997.3798500001</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -4021,6 +4028,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="H2:H3"/>
@@ -4036,11 +4048,6 @@
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6830,49 +6837,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="55" t="s">
         <v>417</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55" t="s">
         <v>416</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
       <c r="K1" s="69" t="s">
         <v>219</v>
       </c>
       <c r="L1" s="69"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="55"/>
+      <c r="C2" s="57"/>
       <c r="D2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="55"/>
+      <c r="G2" s="57"/>
       <c r="H2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="61" t="s">
+      <c r="K2" s="59" t="s">
         <v>214</v>
       </c>
       <c r="L2" s="70" t="s">
@@ -6886,18 +6893,18 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="58"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="56"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="61"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
       <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -7256,7 +7263,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="11.296875" style="1" customWidth="1"/>
@@ -9363,7 +9370,7 @@
         <v>304</v>
       </c>
       <c r="M47" s="19">
-        <f t="shared" ref="M47:M62" si="1">H47*I47</f>
+        <f t="shared" ref="M47:M63" si="1">H47*I47</f>
         <v>245750</v>
       </c>
       <c r="N47" s="23">
@@ -10041,6 +10048,51 @@
       </c>
       <c r="N62" s="23">
         <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A63" s="4">
+        <v>46198</v>
+      </c>
+      <c r="B63" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C63" s="5">
+        <v>1542</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H63" s="5">
+        <v>6</v>
+      </c>
+      <c r="I63" s="25">
+        <v>26990</v>
+      </c>
+      <c r="J63" s="9">
+        <v>0</v>
+      </c>
+      <c r="K63" s="9">
+        <v>0</v>
+      </c>
+      <c r="L63" s="25" t="s">
+        <v>477</v>
+      </c>
+      <c r="M63" s="19">
+        <f t="shared" si="1"/>
+        <v>161940</v>
+      </c>
+      <c r="N63" s="30">
+        <v>-56640</v>
       </c>
     </row>
   </sheetData>
@@ -10060,7 +10112,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -12488,18 +12540,18 @@
         <v>100</v>
       </c>
       <c r="H64" s="19">
-        <f t="shared" ref="H64:H65" si="6">F64*G64</f>
+        <f t="shared" ref="H64:H67" si="6">F64*G64</f>
         <v>4000</v>
       </c>
       <c r="I64" s="19">
         <v>0</v>
       </c>
       <c r="J64" s="19">
-        <f t="shared" ref="J64:J65" si="7">H64-I64</f>
+        <f t="shared" ref="J64:J67" si="7">H64-I64</f>
         <v>4000</v>
       </c>
       <c r="K64" s="19">
-        <f t="shared" ref="K64:K65" si="8">J64</f>
+        <f t="shared" ref="K64:K67" si="8">J64</f>
         <v>4000</v>
       </c>
     </row>
@@ -12539,6 +12591,82 @@
       <c r="K65" s="19">
         <f t="shared" si="8"/>
         <v>20000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A66" s="4">
+        <v>46197</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D66" s="5">
+        <v>4732</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="F66" s="9">
+        <v>29.5</v>
+      </c>
+      <c r="G66" s="5">
+        <v>100</v>
+      </c>
+      <c r="H66" s="19">
+        <f t="shared" si="6"/>
+        <v>2950</v>
+      </c>
+      <c r="I66" s="19">
+        <v>0</v>
+      </c>
+      <c r="J66" s="19">
+        <f t="shared" si="7"/>
+        <v>2950</v>
+      </c>
+      <c r="K66" s="19">
+        <f t="shared" si="8"/>
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A67" s="4">
+        <v>46198</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D67" s="5">
+        <v>4502</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67" s="9">
+        <v>100</v>
+      </c>
+      <c r="G67" s="5">
+        <v>100</v>
+      </c>
+      <c r="H67" s="19">
+        <f t="shared" si="6"/>
+        <v>10000</v>
+      </c>
+      <c r="I67" s="19">
+        <v>0</v>
+      </c>
+      <c r="J67" s="19">
+        <f t="shared" si="7"/>
+        <v>10000</v>
+      </c>
+      <c r="K67" s="19">
+        <f t="shared" si="8"/>
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
@@ -12558,7 +12686,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O967"/>
+  <dimension ref="A1:O981"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -54776,7 +54904,7 @@
         <v>31</v>
       </c>
       <c r="M938" s="15">
-        <f t="shared" ref="M938:M967" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
+        <f t="shared" ref="M938:M981" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
         <v>526900</v>
       </c>
       <c r="N938" s="19">
@@ -55933,7 +56061,7 @@
       <c r="H964" s="5">
         <v>100</v>
       </c>
-      <c r="I964" s="72">
+      <c r="I964" s="7">
         <v>4309.5</v>
       </c>
       <c r="J964" s="9">
@@ -55978,7 +56106,7 @@
       <c r="H965" s="5">
         <v>28</v>
       </c>
-      <c r="I965" s="72">
+      <c r="I965" s="7">
         <v>1814</v>
       </c>
       <c r="J965" s="9">
@@ -56024,7 +56152,7 @@
       <c r="H966" s="5">
         <v>100</v>
       </c>
-      <c r="I966" s="72">
+      <c r="I966" s="7">
         <v>9414</v>
       </c>
       <c r="J966" s="9">
@@ -56069,7 +56197,7 @@
       <c r="H967" s="5">
         <v>100</v>
       </c>
-      <c r="I967" s="72">
+      <c r="I967" s="7">
         <v>7139</v>
       </c>
       <c r="J967" s="9">
@@ -56086,6 +56214,636 @@
         <v>713900</v>
       </c>
       <c r="N967" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="968" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A968" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B968" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C968" s="5">
+        <v>5801</v>
+      </c>
+      <c r="D968" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E968" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F968" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G968" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H968" s="5">
+        <v>100</v>
+      </c>
+      <c r="I968" s="7">
+        <v>54500</v>
+      </c>
+      <c r="J968" s="9">
+        <v>0</v>
+      </c>
+      <c r="K968" s="9">
+        <v>0</v>
+      </c>
+      <c r="L968" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M968" s="15">
+        <f t="shared" si="21"/>
+        <v>5450000</v>
+      </c>
+      <c r="N968" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="969" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A969" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B969" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C969" s="5">
+        <v>6324</v>
+      </c>
+      <c r="D969" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E969" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F969" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G969" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H969" s="5">
+        <v>100</v>
+      </c>
+      <c r="I969" s="7">
+        <v>8625</v>
+      </c>
+      <c r="J969" s="9">
+        <v>0</v>
+      </c>
+      <c r="K969" s="9">
+        <v>0</v>
+      </c>
+      <c r="L969" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M969" s="15">
+        <f t="shared" si="21"/>
+        <v>862500</v>
+      </c>
+      <c r="N969" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="970" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A970" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B970" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C970" s="5">
+        <v>5016</v>
+      </c>
+      <c r="D970" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E970" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F970" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G970" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H970" s="5">
+        <v>100</v>
+      </c>
+      <c r="I970" s="7">
+        <v>5115</v>
+      </c>
+      <c r="J970" s="9">
+        <v>0</v>
+      </c>
+      <c r="K970" s="9">
+        <v>0</v>
+      </c>
+      <c r="L970" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M970" s="15">
+        <f t="shared" si="21"/>
+        <v>511500</v>
+      </c>
+      <c r="N970" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="971" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A971" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B971" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C971" s="5">
+        <v>9984</v>
+      </c>
+      <c r="D971" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E971" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F971" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G971" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H971" s="5">
+        <v>100</v>
+      </c>
+      <c r="I971" s="7">
+        <v>7282</v>
+      </c>
+      <c r="J971" s="9">
+        <v>0</v>
+      </c>
+      <c r="K971" s="9">
+        <v>0</v>
+      </c>
+      <c r="L971" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M971" s="15">
+        <f t="shared" si="21"/>
+        <v>728200</v>
+      </c>
+      <c r="N971" s="19">
+        <v>14300</v>
+      </c>
+    </row>
+    <row r="972" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A972" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B972" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C972" s="5">
+        <v>6324</v>
+      </c>
+      <c r="D972" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E972" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F972" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G972" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H972" s="5">
+        <v>100</v>
+      </c>
+      <c r="I972" s="7">
+        <v>8800</v>
+      </c>
+      <c r="J972" s="9">
+        <v>0</v>
+      </c>
+      <c r="K972" s="9">
+        <v>0</v>
+      </c>
+      <c r="L972" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M972" s="15">
+        <f t="shared" si="21"/>
+        <v>880000</v>
+      </c>
+      <c r="N972" s="19">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="973" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A973" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B973" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C973" s="5">
+        <v>5016</v>
+      </c>
+      <c r="D973" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E973" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F973" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G973" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H973" s="5">
+        <v>100</v>
+      </c>
+      <c r="I973" s="7">
+        <v>5300</v>
+      </c>
+      <c r="J973" s="9">
+        <v>0</v>
+      </c>
+      <c r="K973" s="9">
+        <v>0</v>
+      </c>
+      <c r="L973" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M973" s="15">
+        <f t="shared" si="21"/>
+        <v>530000</v>
+      </c>
+      <c r="N973" s="19">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="974" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A974" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B974" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C974" s="5">
+        <v>6479</v>
+      </c>
+      <c r="D974" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="E974" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F974" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G974" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H974" s="5">
+        <v>100</v>
+      </c>
+      <c r="I974" s="7">
+        <v>5070</v>
+      </c>
+      <c r="J974" s="9">
+        <v>0</v>
+      </c>
+      <c r="K974" s="9">
+        <v>0</v>
+      </c>
+      <c r="L974" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M974" s="15">
+        <f t="shared" si="21"/>
+        <v>507000</v>
+      </c>
+      <c r="N974" s="19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="975" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A975" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B975" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C975" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="D975" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="E975" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F975" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G975" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H975" s="5">
+        <v>100</v>
+      </c>
+      <c r="I975" s="7">
+        <v>4490</v>
+      </c>
+      <c r="J975" s="9">
+        <v>0</v>
+      </c>
+      <c r="K975" s="9">
+        <v>0</v>
+      </c>
+      <c r="L975" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M975" s="15">
+        <f t="shared" si="21"/>
+        <v>449000</v>
+      </c>
+      <c r="N975" s="19">
+        <v>18050</v>
+      </c>
+    </row>
+    <row r="976" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A976" s="4">
+        <v>46196</v>
+      </c>
+      <c r="B976" s="4">
+        <v>46198</v>
+      </c>
+      <c r="C976" s="5">
+        <v>5801</v>
+      </c>
+      <c r="D976" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E976" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F976" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G976" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H976" s="5">
+        <v>100</v>
+      </c>
+      <c r="I976" s="7">
+        <v>55940</v>
+      </c>
+      <c r="J976" s="9">
+        <v>0</v>
+      </c>
+      <c r="K976" s="9">
+        <v>0</v>
+      </c>
+      <c r="L976" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M976" s="15">
+        <f t="shared" si="21"/>
+        <v>5594000</v>
+      </c>
+      <c r="N976" s="19">
+        <v>144000</v>
+      </c>
+    </row>
+    <row r="977" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A977" s="4">
+        <v>46197</v>
+      </c>
+      <c r="B977" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C977" s="5">
+        <v>5801</v>
+      </c>
+      <c r="D977" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E977" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F977" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G977" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H977" s="5">
+        <v>100</v>
+      </c>
+      <c r="I977" s="7">
+        <v>47800</v>
+      </c>
+      <c r="J977" s="9">
+        <v>0</v>
+      </c>
+      <c r="K977" s="9">
+        <v>0</v>
+      </c>
+      <c r="L977" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M977" s="15">
+        <f t="shared" si="21"/>
+        <v>4780000</v>
+      </c>
+      <c r="N977" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="978" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A978" s="4">
+        <v>46198</v>
+      </c>
+      <c r="B978" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C978" s="5">
+        <v>5801</v>
+      </c>
+      <c r="D978" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E978" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F978" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G978" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H978" s="5">
+        <v>100</v>
+      </c>
+      <c r="I978" s="7">
+        <v>48350</v>
+      </c>
+      <c r="J978" s="9">
+        <v>0</v>
+      </c>
+      <c r="K978" s="9">
+        <v>0</v>
+      </c>
+      <c r="L978" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M978" s="15">
+        <f t="shared" si="21"/>
+        <v>4835000</v>
+      </c>
+      <c r="N978" s="19">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="979" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A979" s="4">
+        <v>46198</v>
+      </c>
+      <c r="B979" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C979" s="5">
+        <v>7974</v>
+      </c>
+      <c r="D979" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="E979" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F979" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G979" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H979" s="5">
+        <v>100</v>
+      </c>
+      <c r="I979" s="7">
+        <v>6742</v>
+      </c>
+      <c r="J979" s="9">
+        <v>0</v>
+      </c>
+      <c r="K979" s="9">
+        <v>0</v>
+      </c>
+      <c r="L979" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M979" s="15">
+        <f t="shared" si="21"/>
+        <v>674200</v>
+      </c>
+      <c r="N979" s="19">
+        <v>-650800</v>
+      </c>
+    </row>
+    <row r="980" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A980" s="4">
+        <v>46199</v>
+      </c>
+      <c r="B980" s="4">
+        <v>46203</v>
+      </c>
+      <c r="C980" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D980" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E980" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F980" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G980" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H980" s="5">
+        <v>100</v>
+      </c>
+      <c r="I980" s="7">
+        <v>91580</v>
+      </c>
+      <c r="J980" s="9">
+        <v>0</v>
+      </c>
+      <c r="K980" s="9">
+        <v>0</v>
+      </c>
+      <c r="L980" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M980" s="15">
+        <f t="shared" si="21"/>
+        <v>9158000</v>
+      </c>
+      <c r="N980" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="981" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A981" s="4">
+        <v>46199</v>
+      </c>
+      <c r="B981" s="4">
+        <v>46203</v>
+      </c>
+      <c r="C981" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D981" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E981" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F981" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G981" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H981" s="5">
+        <v>100</v>
+      </c>
+      <c r="I981" s="7">
+        <v>91580</v>
+      </c>
+      <c r="J981" s="9">
+        <v>0</v>
+      </c>
+      <c r="K981" s="9">
+        <v>0</v>
+      </c>
+      <c r="L981" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M981" s="15">
+        <f t="shared" si="21"/>
+        <v>9158000</v>
+      </c>
+      <c r="N981" s="19">
         <v>0</v>
       </c>
     </row>
@@ -56106,7 +56864,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -59411,7 +60169,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="19">
-        <f t="shared" ref="H87:H95" si="18">F87*G87</f>
+        <f t="shared" ref="H87:H97" si="18">F87*G87</f>
         <v>8000</v>
       </c>
       <c r="I87" s="19">
@@ -59722,12 +60480,88 @@
         <v>240</v>
       </c>
       <c r="J95" s="19">
-        <f t="shared" ref="J95" si="19">H95-I95</f>
+        <f t="shared" ref="J95:J97" si="19">H95-I95</f>
         <v>945</v>
       </c>
       <c r="K95" s="19">
-        <f t="shared" ref="K95" si="20">J95</f>
+        <f t="shared" ref="K95:K97" si="20">J95</f>
         <v>945</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A96" s="4">
+        <v>46199</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" s="5">
+        <v>5602</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="F96" s="9">
+        <v>28.8</v>
+      </c>
+      <c r="G96" s="5">
+        <v>300</v>
+      </c>
+      <c r="H96" s="19">
+        <f t="shared" si="18"/>
+        <v>8640</v>
+      </c>
+      <c r="I96" s="19">
+        <v>1755</v>
+      </c>
+      <c r="J96" s="19">
+        <f t="shared" si="19"/>
+        <v>6885</v>
+      </c>
+      <c r="K96" s="19">
+        <f t="shared" si="20"/>
+        <v>6885</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A97" s="4">
+        <v>46199</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" s="5">
+        <v>7012</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F97" s="9">
+        <v>96</v>
+      </c>
+      <c r="G97" s="5">
+        <v>100</v>
+      </c>
+      <c r="H97" s="19">
+        <f t="shared" si="18"/>
+        <v>9600</v>
+      </c>
+      <c r="I97" s="19">
+        <v>1950</v>
+      </c>
+      <c r="J97" s="19">
+        <f t="shared" si="19"/>
+        <v>7650</v>
+      </c>
+      <c r="K97" s="19">
+        <f t="shared" si="20"/>
+        <v>7650</v>
       </c>
     </row>
   </sheetData>
@@ -72283,8 +73117,12 @@
       <c r="L59" s="9">
         <v>160.28</v>
       </c>
-      <c r="M59" s="9"/>
-      <c r="N59" s="9"/>
+      <c r="M59" s="9">
+        <v>0</v>
+      </c>
+      <c r="N59" s="9">
+        <v>0</v>
+      </c>
       <c r="O59" s="9" t="s">
         <v>471</v>
       </c>
